--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,412 +656,424 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3390000</v>
+        <v>3440700</v>
       </c>
       <c r="E8" s="3">
-        <v>3315900</v>
+        <v>3346000</v>
       </c>
       <c r="F8" s="3">
-        <v>3366600</v>
+        <v>3272900</v>
       </c>
       <c r="G8" s="3">
-        <v>3383700</v>
+        <v>3322900</v>
       </c>
       <c r="H8" s="3">
-        <v>3344500</v>
+        <v>3339800</v>
       </c>
       <c r="I8" s="3">
-        <v>3303200</v>
+        <v>3301000</v>
       </c>
       <c r="J8" s="3">
+        <v>3260300</v>
+      </c>
+      <c r="K8" s="3">
         <v>3293500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3221500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3161300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3093900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3043700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12065800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3643200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3728700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3738500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3746400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4059500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3904600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3944800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3655400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3391000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3489600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>123900</v>
+        <v>135100</v>
       </c>
       <c r="E9" s="3">
-        <v>128800</v>
+        <v>122300</v>
       </c>
       <c r="F9" s="3">
-        <v>132800</v>
+        <v>127100</v>
       </c>
       <c r="G9" s="3">
-        <v>123700</v>
+        <v>131100</v>
       </c>
       <c r="H9" s="3">
-        <v>138600</v>
+        <v>122100</v>
       </c>
       <c r="I9" s="3">
-        <v>142600</v>
+        <v>136800</v>
       </c>
       <c r="J9" s="3">
+        <v>140800</v>
+      </c>
+      <c r="K9" s="3">
         <v>145800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>141200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>138100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>137400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>143500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>578000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>155100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>167900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>163800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>162600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>163700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>165200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>172300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>136400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>171900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>183800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>180600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>190800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>197200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>187500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>199000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>153400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3266100</v>
+        <v>3305600</v>
       </c>
       <c r="E10" s="3">
-        <v>3187100</v>
+        <v>3223700</v>
       </c>
       <c r="F10" s="3">
-        <v>3233800</v>
+        <v>3145800</v>
       </c>
       <c r="G10" s="3">
-        <v>3260000</v>
+        <v>3191800</v>
       </c>
       <c r="H10" s="3">
-        <v>3205800</v>
+        <v>3217700</v>
       </c>
       <c r="I10" s="3">
-        <v>3160500</v>
+        <v>3164200</v>
       </c>
       <c r="J10" s="3">
+        <v>3119500</v>
+      </c>
+      <c r="K10" s="3">
         <v>3147600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3080300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3023100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2956500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2900200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11487800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3488100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3560800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3574700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3583800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3895800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3739400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3772400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3519000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3219100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3305800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,100 +1106,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>69700</v>
+        <v>89300</v>
       </c>
       <c r="E12" s="3">
-        <v>67700</v>
+        <v>68800</v>
       </c>
       <c r="F12" s="3">
-        <v>56700</v>
+        <v>66800</v>
       </c>
       <c r="G12" s="3">
-        <v>68900</v>
+        <v>55900</v>
       </c>
       <c r="H12" s="3">
-        <v>65200</v>
+        <v>68000</v>
       </c>
       <c r="I12" s="3">
-        <v>68300</v>
+        <v>64300</v>
       </c>
       <c r="J12" s="3">
+        <v>67400</v>
+      </c>
+      <c r="K12" s="3">
         <v>60100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>75800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>60300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>62000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>61800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>264900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>80700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>85000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>92700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>86500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>83300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>84700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>90800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>88900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>76200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>82500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>75100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>90300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>90800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>83500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>85200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>82100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1278,192 +1294,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>150500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>10300</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>54900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>214000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>52300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>689000</v>
+        <v>688700</v>
       </c>
       <c r="E15" s="3">
-        <v>703500</v>
+        <v>680000</v>
       </c>
       <c r="F15" s="3">
-        <v>693100</v>
+        <v>694400</v>
       </c>
       <c r="G15" s="3">
-        <v>694500</v>
+        <v>684100</v>
       </c>
       <c r="H15" s="3">
-        <v>693900</v>
+        <v>685500</v>
       </c>
       <c r="I15" s="3">
-        <v>698600</v>
+        <v>684900</v>
       </c>
       <c r="J15" s="3">
+        <v>689600</v>
+      </c>
+      <c r="K15" s="3">
         <v>701400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>691800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>696100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>684800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>672700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2748500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>775500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>807500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>827200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>912300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>856100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>818700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>810900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>676100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>621700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>644900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>660200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>696900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>684300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>674200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>685500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>695000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1493,192 +1518,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3006600</v>
+        <v>3222500</v>
       </c>
       <c r="E17" s="3">
-        <v>2959400</v>
+        <v>2967600</v>
       </c>
       <c r="F17" s="3">
-        <v>2985700</v>
+        <v>2921000</v>
       </c>
       <c r="G17" s="3">
-        <v>3200600</v>
+        <v>2946900</v>
       </c>
       <c r="H17" s="3">
-        <v>2986200</v>
+        <v>3159000</v>
       </c>
       <c r="I17" s="3">
-        <v>2949300</v>
+        <v>2947500</v>
       </c>
       <c r="J17" s="3">
+        <v>2911000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2960500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3055700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2866500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2797100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2766800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11279900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3367600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3449200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3485400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3664800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3790900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3622600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3651300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3680200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3145000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>383400</v>
+        <v>218300</v>
       </c>
       <c r="E18" s="3">
-        <v>356500</v>
+        <v>378400</v>
       </c>
       <c r="F18" s="3">
-        <v>380900</v>
+        <v>351900</v>
       </c>
       <c r="G18" s="3">
-        <v>183100</v>
+        <v>376000</v>
       </c>
       <c r="H18" s="3">
-        <v>358200</v>
+        <v>180800</v>
       </c>
       <c r="I18" s="3">
-        <v>353900</v>
+        <v>353600</v>
       </c>
       <c r="J18" s="3">
+        <v>349300</v>
+      </c>
+      <c r="K18" s="3">
         <v>332900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>165800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>294800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>296800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>276900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>785900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>275700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>279500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>253100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>81700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>268600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>282000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>293500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-24700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>246000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>289300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>272600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>220900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>345000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>368800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>367500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>266100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1711,468 +1743,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
-        <v>63700</v>
-      </c>
       <c r="F20" s="3">
-        <v>14800</v>
+        <v>62800</v>
       </c>
       <c r="G20" s="3">
-        <v>7000</v>
+        <v>14600</v>
       </c>
       <c r="H20" s="3">
-        <v>-21000</v>
+        <v>6900</v>
       </c>
       <c r="I20" s="3">
-        <v>14700</v>
+        <v>-20700</v>
       </c>
       <c r="J20" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-24200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>109100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>188000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>133700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>109700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>265700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>320200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>140700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>130200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>116400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>225300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>607100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>866100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>748000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>552300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>662700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>601900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>355900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>351300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>307600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1097700</v>
+        <v>958400</v>
       </c>
       <c r="E21" s="3">
-        <v>1150200</v>
+        <v>1083400</v>
       </c>
       <c r="F21" s="3">
-        <v>1115200</v>
+        <v>1135300</v>
       </c>
       <c r="G21" s="3">
-        <v>909900</v>
+        <v>1100700</v>
       </c>
       <c r="H21" s="3">
-        <v>1056000</v>
+        <v>898100</v>
       </c>
       <c r="I21" s="3">
-        <v>1092900</v>
+        <v>1042300</v>
       </c>
       <c r="J21" s="3">
+        <v>1078700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1037300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1019100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1111900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1261900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1175500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4023100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1338100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1435000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1250100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>956400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1291600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1253400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1367100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1293500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1766000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1714900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>75200</v>
+        <v>78500</v>
       </c>
       <c r="E22" s="3">
-        <v>73800</v>
+        <v>74200</v>
       </c>
       <c r="F22" s="3">
-        <v>71700</v>
+        <v>72800</v>
       </c>
       <c r="G22" s="3">
-        <v>79200</v>
+        <v>70700</v>
       </c>
       <c r="H22" s="3">
-        <v>58200</v>
+        <v>78200</v>
       </c>
       <c r="I22" s="3">
-        <v>58400</v>
+        <v>57500</v>
       </c>
       <c r="J22" s="3">
+        <v>57700</v>
+      </c>
+      <c r="K22" s="3">
         <v>56900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>53600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>53300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>216700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>143600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>155100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>84400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>89700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>87900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>87600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>93100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>75000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>57500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>60400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>63100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>68300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>63400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>66100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>67000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>66000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>308000</v>
+        <v>165200</v>
       </c>
       <c r="E23" s="3">
-        <v>346400</v>
+        <v>304000</v>
       </c>
       <c r="F23" s="3">
-        <v>324100</v>
+        <v>341900</v>
       </c>
       <c r="G23" s="3">
-        <v>110900</v>
+        <v>319900</v>
       </c>
       <c r="H23" s="3">
-        <v>279000</v>
+        <v>109500</v>
       </c>
       <c r="I23" s="3">
-        <v>310100</v>
+        <v>275400</v>
       </c>
       <c r="J23" s="3">
+        <v>306100</v>
+      </c>
+      <c r="K23" s="3">
         <v>251800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>221200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>269300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>433200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>360000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>678900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>397800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>444700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>309400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>311000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>310800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>425700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>507400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1054600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>977000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>761900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>815400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>883600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>658600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>651800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>507700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>70700</v>
+        <v>22800</v>
       </c>
       <c r="E24" s="3">
-        <v>78600</v>
+        <v>69800</v>
       </c>
       <c r="F24" s="3">
-        <v>91200</v>
+        <v>77600</v>
       </c>
       <c r="G24" s="3">
-        <v>-61400</v>
+        <v>90000</v>
       </c>
       <c r="H24" s="3">
-        <v>89900</v>
+        <v>-60600</v>
       </c>
       <c r="I24" s="3">
-        <v>111400</v>
+        <v>88700</v>
       </c>
       <c r="J24" s="3">
+        <v>109900</v>
+      </c>
+      <c r="K24" s="3">
         <v>82100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>62700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>71700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>102700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>96700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>165900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>96100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>94500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>52400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>31400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>66700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>82900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>85700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>108800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>204200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>208900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>179400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>234000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>185800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>112600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>126700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>80500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2263,192 +2311,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>237300</v>
+        <v>142500</v>
       </c>
       <c r="E26" s="3">
-        <v>267800</v>
+        <v>234300</v>
       </c>
       <c r="F26" s="3">
-        <v>232900</v>
+        <v>264300</v>
       </c>
       <c r="G26" s="3">
-        <v>172300</v>
+        <v>229900</v>
       </c>
       <c r="H26" s="3">
-        <v>189100</v>
+        <v>170000</v>
       </c>
       <c r="I26" s="3">
-        <v>198800</v>
+        <v>186700</v>
       </c>
       <c r="J26" s="3">
+        <v>196200</v>
+      </c>
+      <c r="K26" s="3">
         <v>169700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>158600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>197600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>330500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>263300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>513000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>301700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>350200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>257000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-39400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>244200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>228000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>340000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>398600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>850400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>768000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>582400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>581400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>697800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>546000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>525100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>427200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>225600</v>
+        <v>130000</v>
       </c>
       <c r="E27" s="3">
-        <v>250600</v>
+        <v>222700</v>
       </c>
       <c r="F27" s="3">
-        <v>220800</v>
+        <v>247400</v>
       </c>
       <c r="G27" s="3">
-        <v>160900</v>
+        <v>218000</v>
       </c>
       <c r="H27" s="3">
-        <v>177800</v>
+        <v>158800</v>
       </c>
       <c r="I27" s="3">
-        <v>192600</v>
+        <v>175500</v>
       </c>
       <c r="J27" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K27" s="3">
         <v>159800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>141700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>189900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>313600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>253300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>475400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>292100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>343200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>256100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-27200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>240900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>228500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>341700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>404200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>832400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>762900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>583800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>511800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>700300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>542500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>530200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>432400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2539,8 +2596,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2565,29 +2625,29 @@
       <c r="J29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="3">
         <v>80000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>395400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>257900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>157000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>641800</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2631,8 +2691,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2723,8 +2786,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2815,192 +2881,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
-        <v>-63700</v>
-      </c>
       <c r="F32" s="3">
-        <v>-14800</v>
+        <v>-62800</v>
       </c>
       <c r="G32" s="3">
-        <v>-7000</v>
+        <v>-14600</v>
       </c>
       <c r="H32" s="3">
-        <v>21000</v>
+        <v>-6900</v>
       </c>
       <c r="I32" s="3">
-        <v>-14700</v>
+        <v>20700</v>
       </c>
       <c r="J32" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="K32" s="3">
         <v>24200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-109100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-188000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-133700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-109700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-265700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-320200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-140700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-130200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-116400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-225300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-607100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-866100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-748000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>225600</v>
+        <v>130000</v>
       </c>
       <c r="E33" s="3">
-        <v>250600</v>
+        <v>222700</v>
       </c>
       <c r="F33" s="3">
-        <v>220800</v>
+        <v>247400</v>
       </c>
       <c r="G33" s="3">
-        <v>160900</v>
+        <v>218000</v>
       </c>
       <c r="H33" s="3">
-        <v>177800</v>
+        <v>158800</v>
       </c>
       <c r="I33" s="3">
-        <v>192600</v>
+        <v>175500</v>
       </c>
       <c r="J33" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K33" s="3">
         <v>159800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>221700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>585400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>571600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>410400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1117200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>292100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>343200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>256100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>240900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>228500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>341700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>404200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>832400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>762900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>583800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>511800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>700300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>542500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>530200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>432400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3091,197 +3166,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>225600</v>
+        <v>130000</v>
       </c>
       <c r="E35" s="3">
-        <v>250600</v>
+        <v>222700</v>
       </c>
       <c r="F35" s="3">
-        <v>220800</v>
+        <v>247400</v>
       </c>
       <c r="G35" s="3">
-        <v>160900</v>
+        <v>218000</v>
       </c>
       <c r="H35" s="3">
-        <v>177800</v>
+        <v>158800</v>
       </c>
       <c r="I35" s="3">
-        <v>192600</v>
+        <v>175500</v>
       </c>
       <c r="J35" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K35" s="3">
         <v>159800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>221700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>585400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>571600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>410400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1117200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>292100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>343200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>256100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>240900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>228500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>341700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>404200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>832400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>762900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>583800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>511800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>700300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>542500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>530200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>432400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3314,8 +3398,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3348,836 +3433,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>896500</v>
+        <v>1105700</v>
       </c>
       <c r="E41" s="3">
-        <v>1199600</v>
+        <v>884800</v>
       </c>
       <c r="F41" s="3">
-        <v>1305900</v>
+        <v>1184100</v>
       </c>
       <c r="G41" s="3">
-        <v>1449300</v>
+        <v>1288900</v>
       </c>
       <c r="H41" s="3">
-        <v>917400</v>
+        <v>1430500</v>
       </c>
       <c r="I41" s="3">
-        <v>887700</v>
+        <v>905500</v>
       </c>
       <c r="J41" s="3">
+        <v>876200</v>
+      </c>
+      <c r="K41" s="3">
         <v>688900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>654500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1118700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1154500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>911200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1027200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1450500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1212500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>938900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1080200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1147800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1277400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1871900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1265600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2238500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1508800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>331800</v>
+        <v>163700</v>
       </c>
       <c r="E42" s="3">
-        <v>273500</v>
+        <v>327500</v>
       </c>
       <c r="F42" s="3">
-        <v>171100</v>
+        <v>270000</v>
       </c>
       <c r="G42" s="3">
-        <v>121400</v>
+        <v>168900</v>
       </c>
       <c r="H42" s="3">
-        <v>498600</v>
+        <v>119900</v>
       </c>
       <c r="I42" s="3">
-        <v>530200</v>
+        <v>492100</v>
       </c>
       <c r="J42" s="3">
+        <v>523300</v>
+      </c>
+      <c r="K42" s="3">
         <v>378500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>325600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1264900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1186400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1078700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1109500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>840400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>795000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>903200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>766900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>866400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>728100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>733100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>975400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>318100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>452600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>540900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>590800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>626300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>647200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>612800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>437300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>2083300</v>
+        <v>1896500</v>
       </c>
       <c r="E43" s="3">
-        <v>1883600</v>
+        <v>2056200</v>
       </c>
       <c r="F43" s="3">
-        <v>1956600</v>
+        <v>1859200</v>
       </c>
       <c r="G43" s="3">
-        <v>2012900</v>
+        <v>1931200</v>
       </c>
       <c r="H43" s="3">
-        <v>2164700</v>
+        <v>1986800</v>
       </c>
       <c r="I43" s="3">
-        <v>2110900</v>
+        <v>2136600</v>
       </c>
       <c r="J43" s="3">
+        <v>2083500</v>
+      </c>
+      <c r="K43" s="3">
         <v>2117900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1957700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2772400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2584400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2644400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2528400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2663000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2649400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2902000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2886300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3122000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2860700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3116800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2605400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3040500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2736500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>144200</v>
+        <v>136700</v>
       </c>
       <c r="E44" s="3">
-        <v>128400</v>
+        <v>142400</v>
       </c>
       <c r="F44" s="3">
-        <v>154100</v>
+        <v>126700</v>
       </c>
       <c r="G44" s="3">
-        <v>128100</v>
+        <v>152100</v>
       </c>
       <c r="H44" s="3">
-        <v>151300</v>
+        <v>126400</v>
       </c>
       <c r="I44" s="3">
-        <v>141100</v>
+        <v>149400</v>
       </c>
       <c r="J44" s="3">
+        <v>139300</v>
+      </c>
+      <c r="K44" s="3">
         <v>172000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>153500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>148700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>158800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>163900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>166300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>165500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>174800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>138400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>178500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>197000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>239900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>242000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>208700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>217800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>213800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>239700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>219000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>231900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>223700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>233900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1637400</v>
+        <v>1702400</v>
       </c>
       <c r="E45" s="3">
-        <v>1678400</v>
+        <v>1616200</v>
       </c>
       <c r="F45" s="3">
-        <v>1811100</v>
+        <v>1656600</v>
       </c>
       <c r="G45" s="3">
-        <v>1847000</v>
+        <v>1787600</v>
       </c>
       <c r="H45" s="3">
-        <v>1903300</v>
+        <v>1823000</v>
       </c>
       <c r="I45" s="3">
-        <v>1767100</v>
+        <v>1878600</v>
       </c>
       <c r="J45" s="3">
+        <v>1744200</v>
+      </c>
+      <c r="K45" s="3">
         <v>1682200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1673200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1685000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1771500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1762000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1787600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1834500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1869300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1904400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2003300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1881800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1612400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1635700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1597000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1648400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>305100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>341700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>228600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>212400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>289400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5093200</v>
+        <v>5005100</v>
       </c>
       <c r="E46" s="3">
-        <v>5163600</v>
+        <v>5027100</v>
       </c>
       <c r="F46" s="3">
-        <v>5398800</v>
+        <v>5096500</v>
       </c>
       <c r="G46" s="3">
-        <v>5558800</v>
+        <v>5328700</v>
       </c>
       <c r="H46" s="3">
-        <v>5635400</v>
+        <v>5486600</v>
       </c>
       <c r="I46" s="3">
-        <v>5437100</v>
+        <v>5562200</v>
       </c>
       <c r="J46" s="3">
+        <v>5366500</v>
+      </c>
+      <c r="K46" s="3">
         <v>5039500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4764500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6989700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6855700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6560200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6581300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6954700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6691700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6823200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6875200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7196700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6675700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7597400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6685400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7310800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6564000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>3104200</v>
+        <v>3032000</v>
       </c>
       <c r="E47" s="3">
-        <v>3045100</v>
+        <v>3063900</v>
       </c>
       <c r="F47" s="3">
-        <v>2988300</v>
+        <v>3005600</v>
       </c>
       <c r="G47" s="3">
-        <v>2898500</v>
+        <v>2949500</v>
       </c>
       <c r="H47" s="3">
-        <v>2907600</v>
+        <v>2860800</v>
       </c>
       <c r="I47" s="3">
-        <v>2951500</v>
+        <v>2869800</v>
       </c>
       <c r="J47" s="3">
+        <v>2913200</v>
+      </c>
+      <c r="K47" s="3">
         <v>3235400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3194500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15039700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13968200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12464800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12336800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12316200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12493000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12472300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12502800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12994600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12402900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12830400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11621100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>10715900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>10427800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>9772300</v>
+        <v>9911200</v>
       </c>
       <c r="E48" s="3">
-        <v>9982000</v>
+        <v>9645400</v>
       </c>
       <c r="F48" s="3">
-        <v>9904700</v>
+        <v>9852300</v>
       </c>
       <c r="G48" s="3">
-        <v>10277700</v>
+        <v>9776000</v>
       </c>
       <c r="H48" s="3">
-        <v>9603300</v>
+        <v>10144200</v>
       </c>
       <c r="I48" s="3">
-        <v>9775000</v>
+        <v>9478500</v>
       </c>
       <c r="J48" s="3">
+        <v>9648000</v>
+      </c>
+      <c r="K48" s="3">
         <v>9698000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9670700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9855200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9932800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9546300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10032800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9386500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10160800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10069700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10993400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10310700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9942300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10188200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9003400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7678300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8009300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3799700</v>
+        <v>3751500</v>
       </c>
       <c r="E49" s="3">
-        <v>3922200</v>
+        <v>3750400</v>
       </c>
       <c r="F49" s="3">
-        <v>4032800</v>
+        <v>3871300</v>
       </c>
       <c r="G49" s="3">
-        <v>4157900</v>
+        <v>3980400</v>
       </c>
       <c r="H49" s="3">
-        <v>4186100</v>
+        <v>4103900</v>
       </c>
       <c r="I49" s="3">
-        <v>4310900</v>
+        <v>4131700</v>
       </c>
       <c r="J49" s="3">
+        <v>4254900</v>
+      </c>
+      <c r="K49" s="3">
         <v>4434400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4456700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5635200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5629100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5622000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5845300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6083200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6545900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6426000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6643300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7011600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7117600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7518000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7099700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4170600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4448600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4268,8 +4381,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4360,100 +4476,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1237600</v>
+        <v>1190900</v>
       </c>
       <c r="E52" s="3">
-        <v>1222300</v>
+        <v>1221500</v>
       </c>
       <c r="F52" s="3">
-        <v>1190900</v>
+        <v>1206500</v>
       </c>
       <c r="G52" s="3">
-        <v>1214500</v>
+        <v>1175400</v>
       </c>
       <c r="H52" s="3">
-        <v>1175600</v>
+        <v>1198700</v>
       </c>
       <c r="I52" s="3">
-        <v>1124800</v>
+        <v>1160400</v>
       </c>
       <c r="J52" s="3">
+        <v>1110200</v>
+      </c>
+      <c r="K52" s="3">
         <v>1135100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1097000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1238200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1157300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1150100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1134000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1186500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1333900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1439300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1407300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1632000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1341300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1311200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1180300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1055500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1073200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>707400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>521500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>530700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>521800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>693000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4544,100 +4666,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>23007000</v>
+        <v>22890600</v>
       </c>
       <c r="E54" s="3">
-        <v>23335300</v>
+        <v>22708200</v>
       </c>
       <c r="F54" s="3">
-        <v>23515600</v>
+        <v>23032200</v>
       </c>
       <c r="G54" s="3">
-        <v>24107400</v>
+        <v>23210200</v>
       </c>
       <c r="H54" s="3">
-        <v>23507900</v>
+        <v>23794300</v>
       </c>
       <c r="I54" s="3">
-        <v>23599300</v>
+        <v>23202600</v>
       </c>
       <c r="J54" s="3">
+        <v>23292800</v>
+      </c>
+      <c r="K54" s="3">
         <v>23542500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23183500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38758100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37543200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35343500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35930200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35927000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37225300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37230600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38422000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39145600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37479700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39445300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35590100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30931100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30522900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4670,8 +4798,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4704,560 +4833,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>98200</v>
+        <v>106300</v>
       </c>
       <c r="E57" s="3">
-        <v>78300</v>
+        <v>97000</v>
       </c>
       <c r="F57" s="3">
-        <v>107000</v>
+        <v>77200</v>
       </c>
       <c r="G57" s="3">
-        <v>68700</v>
+        <v>105600</v>
       </c>
       <c r="H57" s="3">
-        <v>114500</v>
+        <v>67800</v>
       </c>
       <c r="I57" s="3">
-        <v>87200</v>
+        <v>113100</v>
       </c>
       <c r="J57" s="3">
+        <v>86000</v>
+      </c>
+      <c r="K57" s="3">
         <v>116300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>142900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>253700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>228200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>249000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>279700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>285700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>327300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>372600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>405200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>332700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>283700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>320300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>217500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>221100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>204600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>309500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>226300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>219400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>237100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>362200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1277200</v>
+        <v>1515900</v>
       </c>
       <c r="E58" s="3">
-        <v>1491800</v>
+        <v>1260600</v>
       </c>
       <c r="F58" s="3">
-        <v>1856400</v>
+        <v>1472500</v>
       </c>
       <c r="G58" s="3">
-        <v>1922700</v>
+        <v>1832300</v>
       </c>
       <c r="H58" s="3">
-        <v>2183700</v>
+        <v>1897700</v>
       </c>
       <c r="I58" s="3">
-        <v>1945700</v>
+        <v>2155300</v>
       </c>
       <c r="J58" s="3">
+        <v>1920500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1409000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1344700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1420900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1244900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1236100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1056900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1029100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>963600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1234000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1198200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1223800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1310400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1605600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>894000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1002000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>856100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>944800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>802000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3649700</v>
+        <v>3693200</v>
       </c>
       <c r="E59" s="3">
-        <v>3557500</v>
+        <v>3602300</v>
       </c>
       <c r="F59" s="3">
-        <v>3582800</v>
+        <v>3511300</v>
       </c>
       <c r="G59" s="3">
-        <v>4204400</v>
+        <v>3536300</v>
       </c>
       <c r="H59" s="3">
-        <v>3422100</v>
+        <v>4149800</v>
       </c>
       <c r="I59" s="3">
-        <v>3800600</v>
+        <v>3377700</v>
       </c>
       <c r="J59" s="3">
+        <v>3751200</v>
+      </c>
+      <c r="K59" s="3">
         <v>3814800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3732700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4610800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4393200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4508600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4796900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4594700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4758600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4813200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5103100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4927800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4464800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5319400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4537700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3551200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3760600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>5025200</v>
+        <v>5315400</v>
       </c>
       <c r="E60" s="3">
-        <v>5127600</v>
+        <v>4959900</v>
       </c>
       <c r="F60" s="3">
-        <v>5546300</v>
+        <v>5061000</v>
       </c>
       <c r="G60" s="3">
-        <v>6195800</v>
+        <v>5474200</v>
       </c>
       <c r="H60" s="3">
-        <v>5720300</v>
+        <v>6115400</v>
       </c>
       <c r="I60" s="3">
-        <v>5833500</v>
+        <v>5646000</v>
       </c>
       <c r="J60" s="3">
+        <v>5757700</v>
+      </c>
+      <c r="K60" s="3">
         <v>5340200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5220300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6285400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5866300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5993700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6133500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5909400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6022700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6374500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6673900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6556800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6107900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7208600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5751900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4770700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4837800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>6760700</v>
+        <v>6582000</v>
       </c>
       <c r="E61" s="3">
-        <v>6941400</v>
+        <v>6672900</v>
       </c>
       <c r="F61" s="3">
-        <v>6756100</v>
+        <v>6851300</v>
       </c>
       <c r="G61" s="3">
-        <v>6612600</v>
+        <v>6668300</v>
       </c>
       <c r="H61" s="3">
-        <v>6324100</v>
+        <v>6526800</v>
       </c>
       <c r="I61" s="3">
-        <v>6387000</v>
+        <v>6241900</v>
       </c>
       <c r="J61" s="3">
+        <v>6304100</v>
+      </c>
+      <c r="K61" s="3">
         <v>6669800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6431400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8165900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8169800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7876200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8059700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7920900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8322200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8551200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8623500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8522600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7920200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8288300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7213600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5575400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5547400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1695000</v>
+        <v>1699600</v>
       </c>
       <c r="E62" s="3">
-        <v>1723200</v>
+        <v>1673000</v>
       </c>
       <c r="F62" s="3">
-        <v>1729400</v>
+        <v>1700800</v>
       </c>
       <c r="G62" s="3">
-        <v>1939400</v>
+        <v>1706900</v>
       </c>
       <c r="H62" s="3">
-        <v>1994800</v>
+        <v>1914200</v>
       </c>
       <c r="I62" s="3">
-        <v>2025900</v>
+        <v>1968900</v>
       </c>
       <c r="J62" s="3">
+        <v>1999600</v>
+      </c>
+      <c r="K62" s="3">
         <v>2085000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2280300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3919000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3702000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3292500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3439900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3368000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3426800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3363300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3730200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3901800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3713300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3819900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3851200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2626500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2574400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5348,8 +5496,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5440,8 +5591,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5532,100 +5686,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>14113800</v>
+        <v>14234900</v>
       </c>
       <c r="E66" s="3">
-        <v>14414700</v>
+        <v>13930500</v>
       </c>
       <c r="F66" s="3">
-        <v>14642800</v>
+        <v>14227500</v>
       </c>
       <c r="G66" s="3">
-        <v>15392300</v>
+        <v>14452600</v>
       </c>
       <c r="H66" s="3">
-        <v>14648800</v>
+        <v>15192400</v>
       </c>
       <c r="I66" s="3">
-        <v>14853400</v>
+        <v>14458600</v>
       </c>
       <c r="J66" s="3">
+        <v>14660500</v>
+      </c>
+      <c r="K66" s="3">
         <v>14683200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14498900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19056700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18415600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17659600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18122300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17605800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18193000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18168300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18914300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18899300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17654900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19205500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16714600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13198100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13130700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5658,8 +5818,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5750,8 +5911,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5842,8 +6006,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5934,8 +6101,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6026,100 +6196,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>17578000</v>
+        <v>17328000</v>
       </c>
       <c r="E72" s="3">
-        <v>17488300</v>
+        <v>17349800</v>
       </c>
       <c r="F72" s="3">
-        <v>17363300</v>
+        <v>17261200</v>
       </c>
       <c r="G72" s="3">
-        <v>17297100</v>
+        <v>17137800</v>
       </c>
       <c r="H72" s="3">
-        <v>17291900</v>
+        <v>17072400</v>
       </c>
       <c r="I72" s="3">
-        <v>17230100</v>
+        <v>17067300</v>
       </c>
       <c r="J72" s="3">
+        <v>17006300</v>
+      </c>
+      <c r="K72" s="3">
         <v>17168800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16828000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16730300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16259600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16928100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17236400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17398700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18050600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18362200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18894400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19871700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19470600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19870500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18601400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17574500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17434000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6210,8 +6386,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6302,8 +6481,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6394,100 +6576,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>8893200</v>
+        <v>8655700</v>
       </c>
       <c r="E76" s="3">
-        <v>8920600</v>
+        <v>8777700</v>
       </c>
       <c r="F76" s="3">
-        <v>8872800</v>
+        <v>8804800</v>
       </c>
       <c r="G76" s="3">
-        <v>8715100</v>
+        <v>8757500</v>
       </c>
       <c r="H76" s="3">
-        <v>8859100</v>
+        <v>8601900</v>
       </c>
       <c r="I76" s="3">
-        <v>8745900</v>
+        <v>8744000</v>
       </c>
       <c r="J76" s="3">
+        <v>8632300</v>
+      </c>
+      <c r="K76" s="3">
         <v>8859300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8684500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19701400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19127600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17683900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17807900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18321200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19032300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19062300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19507700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20246300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19824800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20239800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18875500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17732900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17392200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6578,197 +6766,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>225600</v>
+        <v>130000</v>
       </c>
       <c r="E81" s="3">
-        <v>250600</v>
+        <v>222700</v>
       </c>
       <c r="F81" s="3">
-        <v>220800</v>
+        <v>247400</v>
       </c>
       <c r="G81" s="3">
-        <v>160900</v>
+        <v>218000</v>
       </c>
       <c r="H81" s="3">
-        <v>177800</v>
+        <v>158800</v>
       </c>
       <c r="I81" s="3">
-        <v>192600</v>
+        <v>175500</v>
       </c>
       <c r="J81" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K81" s="3">
         <v>159800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>221700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>585400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>571600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>410400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1117200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>292100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>343200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>256100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>240900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>228500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>341700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>404200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>832400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>762900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>583800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>511800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>700300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>542500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>530200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>432400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6801,100 +6998,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>714500</v>
+        <v>714700</v>
       </c>
       <c r="E83" s="3">
-        <v>730100</v>
+        <v>705200</v>
       </c>
       <c r="F83" s="3">
-        <v>719500</v>
+        <v>720600</v>
       </c>
       <c r="G83" s="3">
-        <v>719800</v>
+        <v>710100</v>
       </c>
       <c r="H83" s="3">
-        <v>718800</v>
+        <v>710500</v>
       </c>
       <c r="I83" s="3">
-        <v>724400</v>
+        <v>709500</v>
       </c>
       <c r="J83" s="3">
+        <v>715000</v>
+      </c>
+      <c r="K83" s="3">
         <v>728600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>744200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>789300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>777100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>764800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3127500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>796700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>835300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>856200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>874600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>892700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>855000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>848400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>711200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>653900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>677500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>692100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>732200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>718700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>707600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>715200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>722200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6985,8 +7186,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7077,8 +7281,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7169,8 +7376,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7261,8 +7471,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7353,100 +7566,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1028400</v>
+        <v>922600</v>
       </c>
       <c r="E89" s="3">
-        <v>1057200</v>
+        <v>1015000</v>
       </c>
       <c r="F89" s="3">
-        <v>789100</v>
+        <v>1043500</v>
       </c>
       <c r="G89" s="3">
-        <v>1054800</v>
+        <v>778900</v>
       </c>
       <c r="H89" s="3">
-        <v>811000</v>
+        <v>1041100</v>
       </c>
       <c r="I89" s="3">
-        <v>1110000</v>
+        <v>800500</v>
       </c>
       <c r="J89" s="3">
+        <v>1095600</v>
+      </c>
+      <c r="K89" s="3">
         <v>996900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1011600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1053900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1039700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>659400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4366400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1263500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1549000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>816800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>975700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>746100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>907500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>881500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1389100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>382000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1024900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>829300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>828600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>969400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>776500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>837300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7479,100 +7698,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-985897000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-676260000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-634496000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-783990000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-415900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-558800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-742400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-526800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-878200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-969100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-796300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-571500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-629400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-789700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-622200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-383600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7663,8 +7886,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7755,100 +7981,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-698700</v>
+        <v>-580200</v>
       </c>
       <c r="E94" s="3">
-        <v>-692300</v>
+        <v>-689600</v>
       </c>
       <c r="F94" s="3">
-        <v>-602900</v>
+        <v>-683300</v>
       </c>
       <c r="G94" s="3">
-        <v>-344700</v>
+        <v>-595100</v>
       </c>
       <c r="H94" s="3">
-        <v>-597700</v>
+        <v>-340200</v>
       </c>
       <c r="I94" s="3">
-        <v>-603100</v>
+        <v>-590000</v>
       </c>
       <c r="J94" s="3">
+        <v>-595300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-616500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-583300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-874100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-764500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-387600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-907100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-515500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-404700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-292400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-356000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -7881,53 +8113,54 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-139600</v>
+        <v>-136500</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-137800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-139300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-139300</v>
+        <v>-137500</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-137500</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>-133400</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-556600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7935,11 +8168,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-64000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7947,11 +8180,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -7959,11 +8192,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -7971,10 +8204,13 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8065,8 +8301,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8157,8 +8396,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8249,280 +8491,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-634600</v>
+        <v>-117000</v>
       </c>
       <c r="E100" s="3">
-        <v>-471400</v>
+        <v>-626400</v>
       </c>
       <c r="F100" s="3">
-        <v>-331600</v>
+        <v>-465300</v>
       </c>
       <c r="G100" s="3">
-        <v>-169100</v>
+        <v>-327300</v>
       </c>
       <c r="H100" s="3">
-        <v>-191900</v>
+        <v>-166900</v>
       </c>
       <c r="I100" s="3">
-        <v>-313700</v>
+        <v>-189400</v>
       </c>
       <c r="J100" s="3">
+        <v>-309700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-364600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-892500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-220900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-43900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-377800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-725800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>83100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>324500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>120000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>19100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-163300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>696800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-746200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>30200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>19200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>1800</v>
+        <v>-4400</v>
       </c>
       <c r="E101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H101" s="3">
-        <v>8300</v>
+        <v>-8900</v>
       </c>
       <c r="I101" s="3">
-        <v>5700</v>
+        <v>8200</v>
       </c>
       <c r="J101" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-303200</v>
+        <v>220900</v>
       </c>
       <c r="E102" s="3">
-        <v>-106200</v>
+        <v>-299200</v>
       </c>
       <c r="F102" s="3">
-        <v>-143500</v>
+        <v>-104800</v>
       </c>
       <c r="G102" s="3">
-        <v>531900</v>
+        <v>-141600</v>
       </c>
       <c r="H102" s="3">
-        <v>29700</v>
+        <v>525000</v>
       </c>
       <c r="I102" s="3">
-        <v>198900</v>
+        <v>29300</v>
       </c>
       <c r="J102" s="3">
+        <v>196300</v>
+      </c>
+      <c r="K102" s="3">
         <v>16900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-464100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-35800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>231000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-102400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>74100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>297900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>307100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-128600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-144100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-532800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>500800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>783600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-75200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>359500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>184400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>63700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>581400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,424 +656,436 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3440700</v>
+        <v>3266500</v>
       </c>
       <c r="E8" s="3">
-        <v>3346000</v>
+        <v>3304900</v>
       </c>
       <c r="F8" s="3">
-        <v>3272900</v>
+        <v>3213900</v>
       </c>
       <c r="G8" s="3">
-        <v>3322900</v>
+        <v>3143700</v>
       </c>
       <c r="H8" s="3">
-        <v>3339800</v>
+        <v>3191700</v>
       </c>
       <c r="I8" s="3">
-        <v>3301000</v>
+        <v>3208000</v>
       </c>
       <c r="J8" s="3">
+        <v>3170700</v>
+      </c>
+      <c r="K8" s="3">
         <v>3260300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3293500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3221500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3161300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3093900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3043700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12065800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3643200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3728700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3738500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3746400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4059500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3904600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3944800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3655400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3391000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>135100</v>
+        <v>129100</v>
       </c>
       <c r="E9" s="3">
-        <v>122300</v>
+        <v>129800</v>
       </c>
       <c r="F9" s="3">
-        <v>127100</v>
+        <v>117500</v>
       </c>
       <c r="G9" s="3">
-        <v>131100</v>
+        <v>122100</v>
       </c>
       <c r="H9" s="3">
-        <v>122100</v>
+        <v>125900</v>
       </c>
       <c r="I9" s="3">
-        <v>136800</v>
+        <v>117300</v>
       </c>
       <c r="J9" s="3">
+        <v>131400</v>
+      </c>
+      <c r="K9" s="3">
         <v>140800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>145800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>141200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>138100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>137400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>143500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>578000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>155100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>167900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>163800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>162600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>163700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>165200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>172300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>136400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>171900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>183800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>180600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>190800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>197200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>187500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>199000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>153400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3305600</v>
+        <v>3137300</v>
       </c>
       <c r="E10" s="3">
-        <v>3223700</v>
+        <v>3175100</v>
       </c>
       <c r="F10" s="3">
-        <v>3145800</v>
+        <v>3096400</v>
       </c>
       <c r="G10" s="3">
-        <v>3191800</v>
+        <v>3021600</v>
       </c>
       <c r="H10" s="3">
-        <v>3217700</v>
+        <v>3065800</v>
       </c>
       <c r="I10" s="3">
-        <v>3164200</v>
+        <v>3090700</v>
       </c>
       <c r="J10" s="3">
+        <v>3039300</v>
+      </c>
+      <c r="K10" s="3">
         <v>3119500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3147600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3080300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3023100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2956500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2900200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11487800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3488100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3560800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3574700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3583800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3895800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3739400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3772400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3519000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3219100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1107,103 +1119,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>89300</v>
+        <v>64900</v>
       </c>
       <c r="E12" s="3">
-        <v>68800</v>
+        <v>85800</v>
       </c>
       <c r="F12" s="3">
-        <v>66800</v>
+        <v>66100</v>
       </c>
       <c r="G12" s="3">
-        <v>55900</v>
+        <v>64200</v>
       </c>
       <c r="H12" s="3">
-        <v>68000</v>
+        <v>53700</v>
       </c>
       <c r="I12" s="3">
-        <v>64300</v>
+        <v>65300</v>
       </c>
       <c r="J12" s="3">
+        <v>61800</v>
+      </c>
+      <c r="K12" s="3">
         <v>67400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>60100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>75800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>60300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>62000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>61800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>264900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>80700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>85000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>92700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>86500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>83300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>84700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>90800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>88900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>76200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>82500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>75100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>90300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>90800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>83500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>85200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>82100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,198 +1313,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>7500</v>
+      <c r="D14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
-        <v>12700</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>12200</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-3700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>150500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>10300</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>54900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>214000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>52300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>688700</v>
+        <v>654900</v>
       </c>
       <c r="E15" s="3">
-        <v>680000</v>
+        <v>661500</v>
       </c>
       <c r="F15" s="3">
-        <v>694400</v>
+        <v>653200</v>
       </c>
       <c r="G15" s="3">
-        <v>684100</v>
+        <v>667000</v>
       </c>
       <c r="H15" s="3">
+        <v>657100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>658400</v>
+      </c>
+      <c r="J15" s="3">
+        <v>657900</v>
+      </c>
+      <c r="K15" s="3">
+        <v>689600</v>
+      </c>
+      <c r="L15" s="3">
+        <v>701400</v>
+      </c>
+      <c r="M15" s="3">
+        <v>691800</v>
+      </c>
+      <c r="N15" s="3">
+        <v>696100</v>
+      </c>
+      <c r="O15" s="3">
+        <v>684800</v>
+      </c>
+      <c r="P15" s="3">
+        <v>672700</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>2748500</v>
+      </c>
+      <c r="R15" s="3">
+        <v>775500</v>
+      </c>
+      <c r="S15" s="3">
+        <v>807500</v>
+      </c>
+      <c r="T15" s="3">
+        <v>827200</v>
+      </c>
+      <c r="U15" s="3">
+        <v>912300</v>
+      </c>
+      <c r="V15" s="3">
+        <v>856100</v>
+      </c>
+      <c r="W15" s="3">
+        <v>818700</v>
+      </c>
+      <c r="X15" s="3">
+        <v>810900</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>676100</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>621700</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>644900</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>660200</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>696900</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>684300</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>674200</v>
+      </c>
+      <c r="AF15" s="3">
         <v>685500</v>
       </c>
-      <c r="I15" s="3">
-        <v>684900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>689600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>701400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>691800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>696100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>684800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>672700</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2748500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>775500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>807500</v>
-      </c>
-      <c r="S15" s="3">
-        <v>827200</v>
-      </c>
-      <c r="T15" s="3">
-        <v>912300</v>
-      </c>
-      <c r="U15" s="3">
-        <v>856100</v>
-      </c>
-      <c r="V15" s="3">
-        <v>818700</v>
-      </c>
-      <c r="W15" s="3">
-        <v>810900</v>
-      </c>
-      <c r="X15" s="3">
-        <v>676100</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>621700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>644900</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>660200</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>696900</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>684300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>674200</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>685500</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>695000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1519,198 +1544,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3222500</v>
+        <v>2902600</v>
       </c>
       <c r="E17" s="3">
-        <v>2967600</v>
+        <v>3095300</v>
       </c>
       <c r="F17" s="3">
-        <v>2921000</v>
+        <v>2850400</v>
       </c>
       <c r="G17" s="3">
-        <v>2946900</v>
+        <v>2805700</v>
       </c>
       <c r="H17" s="3">
-        <v>3159000</v>
+        <v>2830600</v>
       </c>
       <c r="I17" s="3">
-        <v>2947500</v>
+        <v>3034300</v>
       </c>
       <c r="J17" s="3">
+        <v>2831100</v>
+      </c>
+      <c r="K17" s="3">
         <v>2911000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2960500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3055700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2866500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2797100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2766800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11279900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3367600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3449200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3485400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3664800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3790900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3622600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3651300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3680200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3145000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>218300</v>
+        <v>363900</v>
       </c>
       <c r="E18" s="3">
-        <v>378400</v>
+        <v>209700</v>
       </c>
       <c r="F18" s="3">
-        <v>351900</v>
+        <v>363500</v>
       </c>
       <c r="G18" s="3">
-        <v>376000</v>
+        <v>338000</v>
       </c>
       <c r="H18" s="3">
-        <v>180800</v>
+        <v>361100</v>
       </c>
       <c r="I18" s="3">
-        <v>353600</v>
+        <v>173600</v>
       </c>
       <c r="J18" s="3">
+        <v>339600</v>
+      </c>
+      <c r="K18" s="3">
         <v>349300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>332900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>165800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>294800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>296800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>276900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>785900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>275700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>279500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>253100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>81700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>268600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>282000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>293500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>246000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>289300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>272600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>220900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>345000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>368800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>367500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>266100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1744,483 +1776,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>25500</v>
+        <v>34500</v>
       </c>
       <c r="E20" s="3">
+        <v>24500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>62800</v>
-      </c>
       <c r="G20" s="3">
-        <v>14600</v>
+        <v>60400</v>
       </c>
       <c r="H20" s="3">
-        <v>6900</v>
+        <v>14100</v>
       </c>
       <c r="I20" s="3">
-        <v>-20700</v>
+        <v>6600</v>
       </c>
       <c r="J20" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="K20" s="3">
         <v>14500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>109100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>188000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>133700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>109700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>265700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>320200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>140700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>130200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>116400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>225300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>607100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>866100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>748000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>552300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>662700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>601900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>355900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>351300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>307600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>958400</v>
+        <v>1078400</v>
       </c>
       <c r="E21" s="3">
-        <v>1083400</v>
+        <v>920600</v>
       </c>
       <c r="F21" s="3">
-        <v>1135300</v>
+        <v>1040600</v>
       </c>
       <c r="G21" s="3">
-        <v>1100700</v>
+        <v>1090500</v>
       </c>
       <c r="H21" s="3">
-        <v>898100</v>
+        <v>1057300</v>
       </c>
       <c r="I21" s="3">
-        <v>1042300</v>
+        <v>862700</v>
       </c>
       <c r="J21" s="3">
+        <v>1001200</v>
+      </c>
+      <c r="K21" s="3">
         <v>1078700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1037300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1019100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1111900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1261900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1175500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4023100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1338100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1435000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1250100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>956400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1291600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1253400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1367100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1293500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1766000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>78500</v>
+        <v>76700</v>
       </c>
       <c r="E22" s="3">
-        <v>74200</v>
+        <v>75400</v>
       </c>
       <c r="F22" s="3">
-        <v>72800</v>
+        <v>71200</v>
       </c>
       <c r="G22" s="3">
-        <v>70700</v>
+        <v>70000</v>
       </c>
       <c r="H22" s="3">
-        <v>78200</v>
+        <v>67900</v>
       </c>
       <c r="I22" s="3">
+        <v>75100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>55200</v>
+      </c>
+      <c r="K22" s="3">
+        <v>57700</v>
+      </c>
+      <c r="L22" s="3">
+        <v>56900</v>
+      </c>
+      <c r="M22" s="3">
+        <v>53600</v>
+      </c>
+      <c r="N22" s="3">
+        <v>53300</v>
+      </c>
+      <c r="O22" s="3">
+        <v>51600</v>
+      </c>
+      <c r="P22" s="3">
+        <v>50600</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>216700</v>
+      </c>
+      <c r="R22" s="3">
+        <v>143600</v>
+      </c>
+      <c r="S22" s="3">
+        <v>155100</v>
+      </c>
+      <c r="T22" s="3">
+        <v>84400</v>
+      </c>
+      <c r="U22" s="3">
+        <v>89700</v>
+      </c>
+      <c r="V22" s="3">
+        <v>87900</v>
+      </c>
+      <c r="W22" s="3">
+        <v>87600</v>
+      </c>
+      <c r="X22" s="3">
+        <v>93100</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>75000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>57500</v>
       </c>
-      <c r="J22" s="3">
-        <v>57700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>56900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>53600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>53300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>51600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>50600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>216700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>143600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>155100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>84400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>89700</v>
-      </c>
-      <c r="U22" s="3">
-        <v>87900</v>
-      </c>
-      <c r="V22" s="3">
-        <v>87600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>93100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>75000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>57500</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>60400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>63100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>68300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>63400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>66100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>67000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>66000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>165200</v>
+        <v>321700</v>
       </c>
       <c r="E23" s="3">
-        <v>304000</v>
+        <v>158700</v>
       </c>
       <c r="F23" s="3">
-        <v>341900</v>
+        <v>292000</v>
       </c>
       <c r="G23" s="3">
-        <v>319900</v>
+        <v>328400</v>
       </c>
       <c r="H23" s="3">
-        <v>109500</v>
+        <v>307300</v>
       </c>
       <c r="I23" s="3">
-        <v>275400</v>
+        <v>105100</v>
       </c>
       <c r="J23" s="3">
+        <v>264500</v>
+      </c>
+      <c r="K23" s="3">
         <v>306100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>251800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>221200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>269300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>433200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>360000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>678900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>397800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>444700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>309400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>311000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>310800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>425700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>507400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1054600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>977000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>761900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>815400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>883600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>658600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>651800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>507700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>22800</v>
+        <v>57500</v>
       </c>
       <c r="E24" s="3">
-        <v>69800</v>
+        <v>21900</v>
       </c>
       <c r="F24" s="3">
-        <v>77600</v>
+        <v>67000</v>
       </c>
       <c r="G24" s="3">
-        <v>90000</v>
+        <v>74500</v>
       </c>
       <c r="H24" s="3">
-        <v>-60600</v>
+        <v>86400</v>
       </c>
       <c r="I24" s="3">
-        <v>88700</v>
+        <v>-58200</v>
       </c>
       <c r="J24" s="3">
+        <v>85200</v>
+      </c>
+      <c r="K24" s="3">
         <v>109900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>82100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>71700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>102700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>96700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>96100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>94500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>52400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>66700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>82900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>85700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>204200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>208900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>179400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>234000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>185800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>112600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>126700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>80500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2314,198 +2362,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>142500</v>
+        <v>264200</v>
       </c>
       <c r="E26" s="3">
-        <v>234300</v>
+        <v>136800</v>
       </c>
       <c r="F26" s="3">
-        <v>264300</v>
+        <v>225000</v>
       </c>
       <c r="G26" s="3">
-        <v>229900</v>
+        <v>253900</v>
       </c>
       <c r="H26" s="3">
-        <v>170000</v>
+        <v>220800</v>
       </c>
       <c r="I26" s="3">
-        <v>186700</v>
+        <v>163300</v>
       </c>
       <c r="J26" s="3">
+        <v>179300</v>
+      </c>
+      <c r="K26" s="3">
         <v>196200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>169700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>158600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>197600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>330500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>263300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>513000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>301700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>350200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>257000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-39400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>244200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>228000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>340000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>398600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>850400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>768000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>582400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>581400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>697800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>546000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>525100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>427200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>130000</v>
+        <v>254100</v>
       </c>
       <c r="E27" s="3">
-        <v>222700</v>
+        <v>124900</v>
       </c>
       <c r="F27" s="3">
-        <v>247400</v>
+        <v>213900</v>
       </c>
       <c r="G27" s="3">
-        <v>218000</v>
+        <v>237600</v>
       </c>
       <c r="H27" s="3">
-        <v>158800</v>
+        <v>209400</v>
       </c>
       <c r="I27" s="3">
-        <v>175500</v>
+        <v>152500</v>
       </c>
       <c r="J27" s="3">
+        <v>168600</v>
+      </c>
+      <c r="K27" s="3">
         <v>190100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>159800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>189900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>313600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>253300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>475400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>292100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>343200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>256100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-27200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>240900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>228500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>341700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>404200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>832400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>762900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>583800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>511800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>700300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>542500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>530200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>432400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2599,8 +2656,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2628,29 +2688,29 @@
       <c r="K29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M29" s="3">
         <v>80000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>395400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>257900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>157000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>641800</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2694,8 +2754,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2789,8 +2852,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2884,198 +2950,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-25500</v>
+        <v>-34500</v>
       </c>
       <c r="E32" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>-62800</v>
-      </c>
       <c r="G32" s="3">
-        <v>-14600</v>
+        <v>-60400</v>
       </c>
       <c r="H32" s="3">
-        <v>-6900</v>
+        <v>-14100</v>
       </c>
       <c r="I32" s="3">
-        <v>20700</v>
+        <v>-6600</v>
       </c>
       <c r="J32" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-109100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-188000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-133700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-109700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-265700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-320200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-140700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-130200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-116400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-225300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-607100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-866100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>130000</v>
+        <v>254100</v>
       </c>
       <c r="E33" s="3">
-        <v>222700</v>
+        <v>124900</v>
       </c>
       <c r="F33" s="3">
-        <v>247400</v>
+        <v>213900</v>
       </c>
       <c r="G33" s="3">
-        <v>218000</v>
+        <v>237600</v>
       </c>
       <c r="H33" s="3">
-        <v>158800</v>
+        <v>209400</v>
       </c>
       <c r="I33" s="3">
-        <v>175500</v>
+        <v>152500</v>
       </c>
       <c r="J33" s="3">
+        <v>168600</v>
+      </c>
+      <c r="K33" s="3">
         <v>190100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>159800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>221700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>585400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>571600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>410400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1117200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>292100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>343200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>256100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>240900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>228500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>341700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>404200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>832400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>762900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>583800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>511800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>700300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>542500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>530200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>432400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3169,203 +3244,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>130000</v>
+        <v>254100</v>
       </c>
       <c r="E35" s="3">
-        <v>222700</v>
+        <v>124900</v>
       </c>
       <c r="F35" s="3">
-        <v>247400</v>
+        <v>213900</v>
       </c>
       <c r="G35" s="3">
-        <v>218000</v>
+        <v>237600</v>
       </c>
       <c r="H35" s="3">
-        <v>158800</v>
+        <v>209400</v>
       </c>
       <c r="I35" s="3">
-        <v>175500</v>
+        <v>152500</v>
       </c>
       <c r="J35" s="3">
+        <v>168600</v>
+      </c>
+      <c r="K35" s="3">
         <v>190100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>159800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>221700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>585400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>571600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>410400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1117200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>292100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>343200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>256100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>240900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>228500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>341700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>404200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>832400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>762900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>583800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>511800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>700300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>542500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>530200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>432400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3399,8 +3483,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3434,863 +3519,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1105700</v>
+        <v>1254900</v>
       </c>
       <c r="E41" s="3">
-        <v>884800</v>
+        <v>1062100</v>
       </c>
       <c r="F41" s="3">
-        <v>1184100</v>
+        <v>849900</v>
       </c>
       <c r="G41" s="3">
-        <v>1288900</v>
+        <v>1137300</v>
       </c>
       <c r="H41" s="3">
-        <v>1430500</v>
+        <v>1238000</v>
       </c>
       <c r="I41" s="3">
-        <v>905500</v>
+        <v>1374000</v>
       </c>
       <c r="J41" s="3">
+        <v>869800</v>
+      </c>
+      <c r="K41" s="3">
         <v>876200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>688900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>654500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1118700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1154500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>911200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1027200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1450500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1212500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>938900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1080200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1147800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1277400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1871900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1265600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2238500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>163700</v>
+        <v>258900</v>
       </c>
       <c r="E42" s="3">
-        <v>327500</v>
+        <v>157300</v>
       </c>
       <c r="F42" s="3">
-        <v>270000</v>
+        <v>314600</v>
       </c>
       <c r="G42" s="3">
-        <v>168900</v>
+        <v>259300</v>
       </c>
       <c r="H42" s="3">
-        <v>119900</v>
+        <v>162300</v>
       </c>
       <c r="I42" s="3">
-        <v>492100</v>
+        <v>115100</v>
       </c>
       <c r="J42" s="3">
+        <v>472700</v>
+      </c>
+      <c r="K42" s="3">
         <v>523300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>378500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>325600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1264900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1186400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1078700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1109500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>840400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>795000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>903200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>766900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>866400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>728100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>733100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>975400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>318100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>452600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>540900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>590800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>626300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>647200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>612800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>437300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1896500</v>
+        <v>1924700</v>
       </c>
       <c r="E43" s="3">
-        <v>2056200</v>
+        <v>1821600</v>
       </c>
       <c r="F43" s="3">
-        <v>1859200</v>
+        <v>1975100</v>
       </c>
       <c r="G43" s="3">
-        <v>1931200</v>
+        <v>1785800</v>
       </c>
       <c r="H43" s="3">
-        <v>1986800</v>
+        <v>1854900</v>
       </c>
       <c r="I43" s="3">
-        <v>2136600</v>
+        <v>1908400</v>
       </c>
       <c r="J43" s="3">
+        <v>2052200</v>
+      </c>
+      <c r="K43" s="3">
         <v>2083500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2117900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1957700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2772400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2584400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2644400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2528400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2663000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2649400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2902000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2886300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3122000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2860700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3116800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2605400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3040500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>131300</v>
+      </c>
+      <c r="F44" s="3">
         <v>136700</v>
       </c>
-      <c r="E44" s="3">
-        <v>142400</v>
-      </c>
-      <c r="F44" s="3">
-        <v>126700</v>
-      </c>
       <c r="G44" s="3">
-        <v>152100</v>
+        <v>121700</v>
       </c>
       <c r="H44" s="3">
-        <v>126400</v>
+        <v>146100</v>
       </c>
       <c r="I44" s="3">
-        <v>149400</v>
+        <v>121400</v>
       </c>
       <c r="J44" s="3">
+        <v>143500</v>
+      </c>
+      <c r="K44" s="3">
         <v>139300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>172000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>153500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>148700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>158800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>163900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>128600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>166300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>165500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>174800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>138400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>178500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>197000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>239900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>242000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>208700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>217800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>213800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>239700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>219000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>231900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>223700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>233900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1702400</v>
+        <v>1598000</v>
       </c>
       <c r="E45" s="3">
-        <v>1616200</v>
+        <v>1635200</v>
       </c>
       <c r="F45" s="3">
-        <v>1656600</v>
+        <v>1552400</v>
       </c>
       <c r="G45" s="3">
+        <v>1591200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1717100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1804400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1744200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1682200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1673200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1771500</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1787600</v>
       </c>
-      <c r="H45" s="3">
-        <v>1823000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1878600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1744200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1682200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1673200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1685000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1771500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1762000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1787600</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1834500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1869300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1904400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2003300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1881800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1612400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1635700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1597000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1505000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>305100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>341700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>228600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>212400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>289400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5005100</v>
+        <v>5190000</v>
       </c>
       <c r="E46" s="3">
-        <v>5027100</v>
+        <v>4807500</v>
       </c>
       <c r="F46" s="3">
-        <v>5096500</v>
+        <v>4828600</v>
       </c>
       <c r="G46" s="3">
-        <v>5328700</v>
+        <v>4895400</v>
       </c>
       <c r="H46" s="3">
-        <v>5486600</v>
+        <v>5118400</v>
       </c>
       <c r="I46" s="3">
-        <v>5562200</v>
+        <v>5270000</v>
       </c>
       <c r="J46" s="3">
+        <v>5342600</v>
+      </c>
+      <c r="K46" s="3">
         <v>5366500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5039500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4764500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6989700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6855700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6560200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6581300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6954700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6691700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6823200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6875200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7196700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6675700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7597400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6685400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7310800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>3032000</v>
+        <v>3048200</v>
       </c>
       <c r="E47" s="3">
-        <v>3063900</v>
+        <v>2912400</v>
       </c>
       <c r="F47" s="3">
-        <v>3005600</v>
+        <v>2942900</v>
       </c>
       <c r="G47" s="3">
-        <v>2949500</v>
+        <v>2886900</v>
       </c>
       <c r="H47" s="3">
-        <v>2860800</v>
+        <v>2833100</v>
       </c>
       <c r="I47" s="3">
-        <v>2869800</v>
+        <v>2747900</v>
       </c>
       <c r="J47" s="3">
+        <v>2756600</v>
+      </c>
+      <c r="K47" s="3">
         <v>2913200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3235400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3194500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15039700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13968200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12464800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12336800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12316200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12493000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12472300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12502800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12994600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12402900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12830400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>11621100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>10715900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>9911200</v>
+        <v>9238300</v>
       </c>
       <c r="E48" s="3">
-        <v>9645400</v>
+        <v>9519900</v>
       </c>
       <c r="F48" s="3">
-        <v>9852300</v>
+        <v>9264600</v>
       </c>
       <c r="G48" s="3">
-        <v>9776000</v>
+        <v>9463400</v>
       </c>
       <c r="H48" s="3">
-        <v>10144200</v>
+        <v>9390100</v>
       </c>
       <c r="I48" s="3">
-        <v>9478500</v>
+        <v>9743800</v>
       </c>
       <c r="J48" s="3">
+        <v>9104400</v>
+      </c>
+      <c r="K48" s="3">
         <v>9648000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9698000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9670700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9855200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9932800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9546300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10032800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9386500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10160800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10069700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10993400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10310700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9942300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10188200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9003400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7678300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3751500</v>
+        <v>3493300</v>
       </c>
       <c r="E49" s="3">
-        <v>3750400</v>
+        <v>3603400</v>
       </c>
       <c r="F49" s="3">
-        <v>3871300</v>
+        <v>3602300</v>
       </c>
       <c r="G49" s="3">
-        <v>3980400</v>
+        <v>3718500</v>
       </c>
       <c r="H49" s="3">
-        <v>4103900</v>
+        <v>3823300</v>
       </c>
       <c r="I49" s="3">
-        <v>4131700</v>
+        <v>3941900</v>
       </c>
       <c r="J49" s="3">
+        <v>3968600</v>
+      </c>
+      <c r="K49" s="3">
         <v>4254900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4434400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4456700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5635200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5629100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5622000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5845300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6083200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6545900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6426000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6643300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7011600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7117600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7518000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7099700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4170600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4384,8 +4497,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4479,103 +4595,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1190900</v>
+        <v>1146700</v>
       </c>
       <c r="E52" s="3">
-        <v>1221500</v>
+        <v>1143900</v>
       </c>
       <c r="F52" s="3">
-        <v>1206500</v>
+        <v>1173300</v>
       </c>
       <c r="G52" s="3">
-        <v>1175400</v>
+        <v>1158800</v>
       </c>
       <c r="H52" s="3">
-        <v>1198700</v>
+        <v>1129000</v>
       </c>
       <c r="I52" s="3">
-        <v>1160400</v>
+        <v>1151400</v>
       </c>
       <c r="J52" s="3">
+        <v>1114600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1110200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1135100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1097000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1238200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1157300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1150100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1186500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1333900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1439300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1407300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1632000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1341300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1311200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1180300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1055500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>707400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>521500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>530700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>521800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>693000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4669,103 +4791,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>22890600</v>
+        <v>22116500</v>
       </c>
       <c r="E54" s="3">
-        <v>22708200</v>
+        <v>21987000</v>
       </c>
       <c r="F54" s="3">
-        <v>23032200</v>
+        <v>21811900</v>
       </c>
       <c r="G54" s="3">
-        <v>23210200</v>
+        <v>22123100</v>
       </c>
       <c r="H54" s="3">
-        <v>23794300</v>
+        <v>22294000</v>
       </c>
       <c r="I54" s="3">
-        <v>23202600</v>
+        <v>22855000</v>
       </c>
       <c r="J54" s="3">
+        <v>22286700</v>
+      </c>
+      <c r="K54" s="3">
         <v>23292800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23542500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23183500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38758100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37543200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35343500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35930200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35927000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37225300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37230600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38422000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39145600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37479700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39445300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35590100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30931100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4799,8 +4927,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4834,578 +4963,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>106300</v>
+        <v>105800</v>
       </c>
       <c r="E57" s="3">
-        <v>97000</v>
+        <v>102100</v>
       </c>
       <c r="F57" s="3">
-        <v>77200</v>
+        <v>93100</v>
       </c>
       <c r="G57" s="3">
-        <v>105600</v>
+        <v>74200</v>
       </c>
       <c r="H57" s="3">
-        <v>67800</v>
+        <v>101500</v>
       </c>
       <c r="I57" s="3">
-        <v>113100</v>
+        <v>65200</v>
       </c>
       <c r="J57" s="3">
+        <v>108600</v>
+      </c>
+      <c r="K57" s="3">
         <v>86000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>142900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>253700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>228200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>249000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>279700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>285700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>327300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>372600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>405200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>332700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>283700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>320300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>217500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>221100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>204600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>309500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>226300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>219400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>237100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>362200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1515900</v>
+        <v>1693400</v>
       </c>
       <c r="E58" s="3">
-        <v>1260600</v>
+        <v>1456100</v>
       </c>
       <c r="F58" s="3">
-        <v>1472500</v>
+        <v>1210800</v>
       </c>
       <c r="G58" s="3">
-        <v>1832300</v>
+        <v>1414300</v>
       </c>
       <c r="H58" s="3">
-        <v>1897700</v>
+        <v>1760000</v>
       </c>
       <c r="I58" s="3">
-        <v>2155300</v>
+        <v>1822800</v>
       </c>
       <c r="J58" s="3">
+        <v>2070200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1920500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1409000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1344700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1420900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1244900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1236100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1056900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1029100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>963600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1234000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1198200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1223800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1310400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1605600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>894000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1002000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>856100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>944800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>802000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3693200</v>
+        <v>3499400</v>
       </c>
       <c r="E59" s="3">
-        <v>3602300</v>
+        <v>3547400</v>
       </c>
       <c r="F59" s="3">
-        <v>3511300</v>
+        <v>3460100</v>
       </c>
       <c r="G59" s="3">
-        <v>3536300</v>
+        <v>3372700</v>
       </c>
       <c r="H59" s="3">
-        <v>4149800</v>
+        <v>3396700</v>
       </c>
       <c r="I59" s="3">
-        <v>3377700</v>
+        <v>3986000</v>
       </c>
       <c r="J59" s="3">
+        <v>3244300</v>
+      </c>
+      <c r="K59" s="3">
         <v>3751200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3814800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3732700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4610800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4393200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4508600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4796900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4594700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4758600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4813200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5103100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4927800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4464800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5319400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4537700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3551200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>5315400</v>
+        <v>5298600</v>
       </c>
       <c r="E60" s="3">
-        <v>4959900</v>
+        <v>5105600</v>
       </c>
       <c r="F60" s="3">
-        <v>5061000</v>
+        <v>4764100</v>
       </c>
       <c r="G60" s="3">
-        <v>5474200</v>
+        <v>4861200</v>
       </c>
       <c r="H60" s="3">
-        <v>6115400</v>
+        <v>5258100</v>
       </c>
       <c r="I60" s="3">
-        <v>5646000</v>
+        <v>5874000</v>
       </c>
       <c r="J60" s="3">
+        <v>5423100</v>
+      </c>
+      <c r="K60" s="3">
         <v>5757700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5340200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5220300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6285400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5866300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5993700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6133500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5909400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6022700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6374500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6673900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6556800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6107900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7208600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5751900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4770700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>6582000</v>
+        <v>6301200</v>
       </c>
       <c r="E61" s="3">
-        <v>6672900</v>
+        <v>6322200</v>
       </c>
       <c r="F61" s="3">
-        <v>6851300</v>
+        <v>6409500</v>
       </c>
       <c r="G61" s="3">
-        <v>6668300</v>
+        <v>6580800</v>
       </c>
       <c r="H61" s="3">
-        <v>6526800</v>
+        <v>6405100</v>
       </c>
       <c r="I61" s="3">
-        <v>6241900</v>
+        <v>6269100</v>
       </c>
       <c r="J61" s="3">
+        <v>5995600</v>
+      </c>
+      <c r="K61" s="3">
         <v>6304100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6669800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6431400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8165900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8169800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7876200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8059700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7920900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8322200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8551200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8623500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8522600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7920200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8288300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7213600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5575400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1699600</v>
+        <v>1426000</v>
       </c>
       <c r="E62" s="3">
-        <v>1673000</v>
+        <v>1632500</v>
       </c>
       <c r="F62" s="3">
-        <v>1700800</v>
+        <v>1607000</v>
       </c>
       <c r="G62" s="3">
-        <v>1706900</v>
+        <v>1633700</v>
       </c>
       <c r="H62" s="3">
-        <v>1914200</v>
+        <v>1639500</v>
       </c>
       <c r="I62" s="3">
-        <v>1968900</v>
+        <v>1838600</v>
       </c>
       <c r="J62" s="3">
+        <v>1891200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1999600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2085000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2280300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3919000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3702000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3292500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3439900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3368000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3426800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3363300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3730200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3901800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3713300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3819900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3851200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2626500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5499,8 +5647,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5594,8 +5745,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5689,103 +5843,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>14234900</v>
+        <v>13606000</v>
       </c>
       <c r="E66" s="3">
-        <v>13930500</v>
+        <v>13673000</v>
       </c>
       <c r="F66" s="3">
-        <v>14227500</v>
+        <v>13380600</v>
       </c>
       <c r="G66" s="3">
-        <v>14452600</v>
+        <v>13665900</v>
       </c>
       <c r="H66" s="3">
-        <v>15192400</v>
+        <v>13882100</v>
       </c>
       <c r="I66" s="3">
-        <v>14458600</v>
+        <v>14592700</v>
       </c>
       <c r="J66" s="3">
+        <v>13887800</v>
+      </c>
+      <c r="K66" s="3">
         <v>14660500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14683200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14498900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19056700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18415600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17659600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18122300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17605800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18193000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18168300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18914300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18899300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17654900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19205500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16714600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13198100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5819,8 +5979,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5914,8 +6075,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6009,8 +6173,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6104,8 +6271,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6199,103 +6369,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>17328000</v>
+        <v>16591400</v>
       </c>
       <c r="E72" s="3">
-        <v>17349800</v>
+        <v>16644000</v>
       </c>
       <c r="F72" s="3">
-        <v>17261200</v>
+        <v>16664900</v>
       </c>
       <c r="G72" s="3">
-        <v>17137800</v>
+        <v>16579800</v>
       </c>
       <c r="H72" s="3">
-        <v>17072400</v>
+        <v>16461300</v>
       </c>
       <c r="I72" s="3">
-        <v>17067300</v>
+        <v>16398500</v>
       </c>
       <c r="J72" s="3">
+        <v>16393600</v>
+      </c>
+      <c r="K72" s="3">
         <v>17006300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17168800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16828000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16730300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16259600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16928100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17236400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17398700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18050600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18362200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18894400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19871700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19470600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19870500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18601400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17574500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6389,8 +6565,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6484,8 +6663,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6579,103 +6761,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>8655700</v>
+        <v>8510400</v>
       </c>
       <c r="E76" s="3">
-        <v>8777700</v>
+        <v>8314000</v>
       </c>
       <c r="F76" s="3">
-        <v>8804800</v>
+        <v>8431200</v>
       </c>
       <c r="G76" s="3">
-        <v>8757500</v>
+        <v>8457200</v>
       </c>
       <c r="H76" s="3">
-        <v>8601900</v>
+        <v>8411800</v>
       </c>
       <c r="I76" s="3">
-        <v>8744000</v>
+        <v>8262400</v>
       </c>
       <c r="J76" s="3">
+        <v>8398900</v>
+      </c>
+      <c r="K76" s="3">
         <v>8632300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8859300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8684500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19701400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19127600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17683900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17807900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18321200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19032300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19062300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19507700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20246300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19824800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20239800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18875500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17732900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6769,203 +6957,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>130000</v>
+        <v>254100</v>
       </c>
       <c r="E81" s="3">
-        <v>222700</v>
+        <v>124900</v>
       </c>
       <c r="F81" s="3">
-        <v>247400</v>
+        <v>213900</v>
       </c>
       <c r="G81" s="3">
-        <v>218000</v>
+        <v>237600</v>
       </c>
       <c r="H81" s="3">
-        <v>158800</v>
+        <v>209400</v>
       </c>
       <c r="I81" s="3">
-        <v>175500</v>
+        <v>152500</v>
       </c>
       <c r="J81" s="3">
+        <v>168600</v>
+      </c>
+      <c r="K81" s="3">
         <v>190100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>159800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>221700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>585400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>571600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>410400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1117200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>292100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>343200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>256100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>240900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>228500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>341700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>404200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>832400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>762900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>583800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>511800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>700300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>542500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>530200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>432400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6999,103 +7196,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>714700</v>
+        <v>680000</v>
       </c>
       <c r="E83" s="3">
-        <v>705200</v>
+        <v>686500</v>
       </c>
       <c r="F83" s="3">
-        <v>720600</v>
+        <v>677400</v>
       </c>
       <c r="G83" s="3">
-        <v>710100</v>
+        <v>692100</v>
       </c>
       <c r="H83" s="3">
-        <v>710500</v>
+        <v>682100</v>
       </c>
       <c r="I83" s="3">
-        <v>709500</v>
+        <v>682400</v>
       </c>
       <c r="J83" s="3">
+        <v>681500</v>
+      </c>
+      <c r="K83" s="3">
         <v>715000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>728600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>744200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>789300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>777100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>764800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3127500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>796700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>835300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>856200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>874600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>892700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>855000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>848400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>711200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>653900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>677500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>692100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>732200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>718700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>707600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>715200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>722200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7189,8 +7390,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7284,8 +7488,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7379,8 +7586,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7474,8 +7684,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7569,103 +7782,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>922600</v>
+        <v>816700</v>
       </c>
       <c r="E89" s="3">
-        <v>1015000</v>
+        <v>886100</v>
       </c>
       <c r="F89" s="3">
-        <v>1043500</v>
+        <v>974900</v>
       </c>
       <c r="G89" s="3">
-        <v>778900</v>
+        <v>1002300</v>
       </c>
       <c r="H89" s="3">
-        <v>1041100</v>
+        <v>748100</v>
       </c>
       <c r="I89" s="3">
-        <v>800500</v>
+        <v>1000000</v>
       </c>
       <c r="J89" s="3">
+        <v>768900</v>
+      </c>
+      <c r="K89" s="3">
         <v>1095600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>996900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1011600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1053900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1039700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>659400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4366400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1263500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1549000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>816800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>975700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>746100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>907500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>881500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1389100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>382000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>829300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>828600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>969400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>776500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>837300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7699,103 +7918,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-590523000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-985897000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-676260000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-634496000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-783990000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-415900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-558800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-742400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-526800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-878200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-969100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-796300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-571500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-629400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-789700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-622200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7889,8 +8112,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7984,103 +8210,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-580200</v>
+        <v>-469900</v>
       </c>
       <c r="E94" s="3">
-        <v>-689600</v>
+        <v>-557300</v>
       </c>
       <c r="F94" s="3">
-        <v>-683300</v>
+        <v>-662400</v>
       </c>
       <c r="G94" s="3">
-        <v>-595100</v>
+        <v>-656400</v>
       </c>
       <c r="H94" s="3">
-        <v>-340200</v>
+        <v>-571600</v>
       </c>
       <c r="I94" s="3">
-        <v>-590000</v>
+        <v>-326800</v>
       </c>
       <c r="J94" s="3">
+        <v>-566700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-595300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-616500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-583300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-874100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-764500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-387600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-907100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-515500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-404700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-292400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8114,56 +8346,57 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-136500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-137800</v>
+        <v>-131100</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-132400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-137500</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-137500</v>
+        <v>-132100</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-132100</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-133400</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-556600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-56300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8171,11 +8404,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-64000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -8183,11 +8416,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8195,11 +8428,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8207,10 +8440,13 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8304,8 +8540,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8399,8 +8638,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8494,289 +8736,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-117000</v>
+        <v>-158500</v>
       </c>
       <c r="E100" s="3">
-        <v>-626400</v>
+        <v>-112400</v>
       </c>
       <c r="F100" s="3">
-        <v>-465300</v>
+        <v>-601700</v>
       </c>
       <c r="G100" s="3">
-        <v>-327300</v>
+        <v>-446900</v>
       </c>
       <c r="H100" s="3">
-        <v>-166900</v>
+        <v>-314300</v>
       </c>
       <c r="I100" s="3">
-        <v>-189400</v>
+        <v>-160300</v>
       </c>
       <c r="J100" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-309700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-364600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-892500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-220900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-377800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-56600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-725800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>83100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>324500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>120000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>19100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-163300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>696800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>30200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>19200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-4400</v>
+        <v>4400</v>
       </c>
       <c r="E101" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
-        <v>1900</v>
-      </c>
       <c r="H101" s="3">
-        <v>-8900</v>
+        <v>1800</v>
       </c>
       <c r="I101" s="3">
-        <v>8200</v>
+        <v>-8600</v>
       </c>
       <c r="J101" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K101" s="3">
         <v>5600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>220900</v>
+        <v>192700</v>
       </c>
       <c r="E102" s="3">
-        <v>-299200</v>
+        <v>212200</v>
       </c>
       <c r="F102" s="3">
-        <v>-104800</v>
+        <v>-287400</v>
       </c>
       <c r="G102" s="3">
-        <v>-141600</v>
+        <v>-100700</v>
       </c>
       <c r="H102" s="3">
-        <v>525000</v>
+        <v>-136000</v>
       </c>
       <c r="I102" s="3">
-        <v>29300</v>
+        <v>504300</v>
       </c>
       <c r="J102" s="3">
+        <v>28100</v>
+      </c>
+      <c r="K102" s="3">
         <v>196300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-464100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-35800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>231000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-102400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>74100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>297900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>307100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-128600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-144100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-532800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>500800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>783600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>359500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>184400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>63700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>581400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,436 +656,448 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3266500</v>
+        <v>3316800</v>
       </c>
       <c r="E8" s="3">
-        <v>3304900</v>
+        <v>3356000</v>
       </c>
       <c r="F8" s="3">
-        <v>3213900</v>
+        <v>3395500</v>
       </c>
       <c r="G8" s="3">
-        <v>3143700</v>
+        <v>3302000</v>
       </c>
       <c r="H8" s="3">
-        <v>3191700</v>
+        <v>3229800</v>
       </c>
       <c r="I8" s="3">
-        <v>3208000</v>
+        <v>3279200</v>
       </c>
       <c r="J8" s="3">
+        <v>3295800</v>
+      </c>
+      <c r="K8" s="3">
         <v>3170700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3260300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3293500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3221500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3161300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3093900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3043700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12065800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3643200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3728700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3738500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3746400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4059500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3904600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3944800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3655400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>129100</v>
+        <v>127100</v>
       </c>
       <c r="E9" s="3">
-        <v>129800</v>
+        <v>132700</v>
       </c>
       <c r="F9" s="3">
-        <v>117500</v>
+        <v>133400</v>
       </c>
       <c r="G9" s="3">
-        <v>122100</v>
+        <v>120700</v>
       </c>
       <c r="H9" s="3">
-        <v>125900</v>
+        <v>125400</v>
       </c>
       <c r="I9" s="3">
-        <v>117300</v>
+        <v>129400</v>
       </c>
       <c r="J9" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K9" s="3">
         <v>131400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>140800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>145800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>141200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>138100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>137400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>143500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>578000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>155100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>167900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>163800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>162600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>163700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>165200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>172300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>136400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>171900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>183800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>180600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>190800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>197200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>187500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>199000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>153400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3137300</v>
+        <v>3189700</v>
       </c>
       <c r="E10" s="3">
-        <v>3175100</v>
+        <v>3223300</v>
       </c>
       <c r="F10" s="3">
-        <v>3096400</v>
+        <v>3262100</v>
       </c>
       <c r="G10" s="3">
-        <v>3021600</v>
+        <v>3181300</v>
       </c>
       <c r="H10" s="3">
-        <v>3065800</v>
+        <v>3104400</v>
       </c>
       <c r="I10" s="3">
-        <v>3090700</v>
+        <v>3149800</v>
       </c>
       <c r="J10" s="3">
+        <v>3175400</v>
+      </c>
+      <c r="K10" s="3">
         <v>3039300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3119500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3147600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3080300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3023100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2956500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2900200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11487800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3488100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3560800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3574700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3583800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3895800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3739400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3772400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3519000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,106 +1132,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>64900</v>
+        <v>73100</v>
       </c>
       <c r="E12" s="3">
-        <v>85800</v>
+        <v>66700</v>
       </c>
       <c r="F12" s="3">
-        <v>66100</v>
+        <v>88200</v>
       </c>
       <c r="G12" s="3">
-        <v>64200</v>
+        <v>67900</v>
       </c>
       <c r="H12" s="3">
-        <v>53700</v>
+        <v>65900</v>
       </c>
       <c r="I12" s="3">
-        <v>65300</v>
+        <v>55200</v>
       </c>
       <c r="J12" s="3">
+        <v>67100</v>
+      </c>
+      <c r="K12" s="3">
         <v>61800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>67400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>60100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>75800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>60300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>62000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>61800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>264900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>80700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>85000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>92700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>86500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>83300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>84700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>90800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>88900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>76200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>82500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>75100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>90300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>90800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>83500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>85200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>82100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1316,204 +1332,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="3">
-        <v>7200</v>
-      </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>150500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>10300</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>54900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>214000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>52300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>654900</v>
+        <v>662900</v>
       </c>
       <c r="E15" s="3">
-        <v>661500</v>
+        <v>672900</v>
       </c>
       <c r="F15" s="3">
-        <v>653200</v>
+        <v>679600</v>
       </c>
       <c r="G15" s="3">
-        <v>667000</v>
+        <v>671100</v>
       </c>
       <c r="H15" s="3">
-        <v>657100</v>
+        <v>685200</v>
       </c>
       <c r="I15" s="3">
-        <v>658400</v>
+        <v>675100</v>
       </c>
       <c r="J15" s="3">
+        <v>676400</v>
+      </c>
+      <c r="K15" s="3">
         <v>657900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>689600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>701400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>691800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>696100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>684800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>672700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2748500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>775500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>807500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>827200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>912300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>856100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>818700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>810900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>676100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>621700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>644900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>660200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>696900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>684300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>674200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>685500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>695000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1545,204 +1570,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2902600</v>
+        <v>2913600</v>
       </c>
       <c r="E17" s="3">
-        <v>3095300</v>
+        <v>2982100</v>
       </c>
       <c r="F17" s="3">
-        <v>2850400</v>
+        <v>3180100</v>
       </c>
       <c r="G17" s="3">
-        <v>2805700</v>
+        <v>2928500</v>
       </c>
       <c r="H17" s="3">
-        <v>2830600</v>
+        <v>2882500</v>
       </c>
       <c r="I17" s="3">
-        <v>3034300</v>
+        <v>2908100</v>
       </c>
       <c r="J17" s="3">
+        <v>3117500</v>
+      </c>
+      <c r="K17" s="3">
         <v>2831100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2911000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2960500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3055700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2866500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2797100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2766800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11279900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3367600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3449200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3485400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3664800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3790900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3622600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3651300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3680200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>363900</v>
+        <v>403100</v>
       </c>
       <c r="E18" s="3">
-        <v>209700</v>
+        <v>373900</v>
       </c>
       <c r="F18" s="3">
-        <v>363500</v>
+        <v>215400</v>
       </c>
       <c r="G18" s="3">
-        <v>338000</v>
+        <v>373400</v>
       </c>
       <c r="H18" s="3">
-        <v>361100</v>
+        <v>347300</v>
       </c>
       <c r="I18" s="3">
-        <v>173600</v>
+        <v>371000</v>
       </c>
       <c r="J18" s="3">
+        <v>178400</v>
+      </c>
+      <c r="K18" s="3">
         <v>339600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>349300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>332900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>165800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>294800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>296800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>276900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>785900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>275700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>279500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>253100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>81700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>268600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>282000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>293500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>246000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>289300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>272600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>220900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>345000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>368800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>367500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>266100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1777,498 +1809,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>34500</v>
+        <v>29800</v>
       </c>
       <c r="E20" s="3">
-        <v>24500</v>
+        <v>35500</v>
       </c>
       <c r="F20" s="3">
+        <v>25100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>60400</v>
-      </c>
       <c r="H20" s="3">
-        <v>14100</v>
+        <v>62000</v>
       </c>
       <c r="I20" s="3">
-        <v>6600</v>
+        <v>14400</v>
       </c>
       <c r="J20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-19900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>109100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>188000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>133700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>109700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>265700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>320200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>140700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>130200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>116400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>225300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>607100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>866100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>748000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>552300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>662700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>601900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>355900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>351300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>307600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1078400</v>
+        <v>1121700</v>
       </c>
       <c r="E21" s="3">
-        <v>920600</v>
+        <v>1108000</v>
       </c>
       <c r="F21" s="3">
-        <v>1040600</v>
+        <v>945800</v>
       </c>
       <c r="G21" s="3">
-        <v>1090500</v>
+        <v>1069100</v>
       </c>
       <c r="H21" s="3">
-        <v>1057300</v>
+        <v>1120400</v>
       </c>
       <c r="I21" s="3">
-        <v>862700</v>
+        <v>1086300</v>
       </c>
       <c r="J21" s="3">
+        <v>886300</v>
+      </c>
+      <c r="K21" s="3">
         <v>1001200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1078700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1037300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1019100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1111900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1261900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1175500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4023100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1338100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1435000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1250100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>956400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1291600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1253400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1367100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1293500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>76700</v>
+        <v>74300</v>
       </c>
       <c r="E22" s="3">
-        <v>75400</v>
+        <v>78800</v>
       </c>
       <c r="F22" s="3">
-        <v>71200</v>
+        <v>77500</v>
       </c>
       <c r="G22" s="3">
-        <v>70000</v>
+        <v>73200</v>
       </c>
       <c r="H22" s="3">
-        <v>67900</v>
+        <v>71900</v>
       </c>
       <c r="I22" s="3">
-        <v>75100</v>
+        <v>69800</v>
       </c>
       <c r="J22" s="3">
+        <v>77200</v>
+      </c>
+      <c r="K22" s="3">
         <v>55200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>57700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>53600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>53300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>216700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>143600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>155100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>84400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>89700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>87900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>87600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>93100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>75000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>57500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>63100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>68300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>63400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>66100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>67000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>66000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>321700</v>
+        <v>358600</v>
       </c>
       <c r="E23" s="3">
-        <v>158700</v>
+        <v>330600</v>
       </c>
       <c r="F23" s="3">
-        <v>292000</v>
+        <v>163000</v>
       </c>
       <c r="G23" s="3">
-        <v>328400</v>
+        <v>300000</v>
       </c>
       <c r="H23" s="3">
-        <v>307300</v>
+        <v>337400</v>
       </c>
       <c r="I23" s="3">
-        <v>105100</v>
+        <v>315700</v>
       </c>
       <c r="J23" s="3">
+        <v>108000</v>
+      </c>
+      <c r="K23" s="3">
         <v>264500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>306100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>251800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>221200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>269300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>433200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>360000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>678900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>397800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>444700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>309400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>311000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>310800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>425700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>507400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>977000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>761900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>815400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>883600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>658600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>651800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>507700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>57500</v>
+        <v>96000</v>
       </c>
       <c r="E24" s="3">
-        <v>21900</v>
+        <v>59100</v>
       </c>
       <c r="F24" s="3">
-        <v>67000</v>
+        <v>22500</v>
       </c>
       <c r="G24" s="3">
-        <v>74500</v>
+        <v>68900</v>
       </c>
       <c r="H24" s="3">
-        <v>86400</v>
+        <v>76600</v>
       </c>
       <c r="I24" s="3">
-        <v>-58200</v>
+        <v>88800</v>
       </c>
       <c r="J24" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="K24" s="3">
         <v>85200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>109900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>82100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>62700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>71700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>102700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>96700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>165900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>96100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>94500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>52400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>31400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>66700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>82900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>85700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>108800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>204200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>208900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>179400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>234000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>185800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>112600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>126700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>80500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2365,204 +2413,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>264200</v>
+        <v>262600</v>
       </c>
       <c r="E26" s="3">
-        <v>136800</v>
+        <v>271500</v>
       </c>
       <c r="F26" s="3">
-        <v>225000</v>
+        <v>140600</v>
       </c>
       <c r="G26" s="3">
-        <v>253900</v>
+        <v>231200</v>
       </c>
       <c r="H26" s="3">
-        <v>220800</v>
+        <v>260800</v>
       </c>
       <c r="I26" s="3">
-        <v>163300</v>
+        <v>226900</v>
       </c>
       <c r="J26" s="3">
+        <v>167800</v>
+      </c>
+      <c r="K26" s="3">
         <v>179300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>196200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>169700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>158600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>197600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>330500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>263300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>513000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>301700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>350200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>257000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-39400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>244200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>228000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>340000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>398600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>850400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>768000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>582400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>581400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>697800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>546000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>525100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>427200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>254100</v>
+        <v>249300</v>
       </c>
       <c r="E27" s="3">
-        <v>124900</v>
+        <v>261000</v>
       </c>
       <c r="F27" s="3">
-        <v>213900</v>
+        <v>128300</v>
       </c>
       <c r="G27" s="3">
-        <v>237600</v>
+        <v>219700</v>
       </c>
       <c r="H27" s="3">
-        <v>209400</v>
+        <v>244100</v>
       </c>
       <c r="I27" s="3">
-        <v>152500</v>
+        <v>215100</v>
       </c>
       <c r="J27" s="3">
+        <v>156700</v>
+      </c>
+      <c r="K27" s="3">
         <v>168600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>190100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>159800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>141700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>189900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>313600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>253300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>475400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>292100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>343200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>256100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-27200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>240900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>228500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>341700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>404200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>832400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>762900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>583800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>511800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>700300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>542500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>530200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>432400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2659,8 +2716,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2691,29 +2751,29 @@
       <c r="L29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N29" s="3">
         <v>80000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>395400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>257900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>157000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>641800</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2757,8 +2817,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2855,8 +2918,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2953,204 +3019,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-34500</v>
+        <v>-29800</v>
       </c>
       <c r="E32" s="3">
-        <v>-24500</v>
+        <v>-35500</v>
       </c>
       <c r="F32" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-60400</v>
-      </c>
       <c r="H32" s="3">
-        <v>-14100</v>
+        <v>-62000</v>
       </c>
       <c r="I32" s="3">
-        <v>-6600</v>
+        <v>-14400</v>
       </c>
       <c r="J32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="K32" s="3">
         <v>19900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-109100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-188000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-133700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-109700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-265700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-320200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-140700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-130200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-116400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-225300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-607100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>254100</v>
+        <v>249300</v>
       </c>
       <c r="E33" s="3">
-        <v>124900</v>
+        <v>261000</v>
       </c>
       <c r="F33" s="3">
-        <v>213900</v>
+        <v>128300</v>
       </c>
       <c r="G33" s="3">
-        <v>237600</v>
+        <v>219700</v>
       </c>
       <c r="H33" s="3">
-        <v>209400</v>
+        <v>244100</v>
       </c>
       <c r="I33" s="3">
-        <v>152500</v>
+        <v>215100</v>
       </c>
       <c r="J33" s="3">
+        <v>156700</v>
+      </c>
+      <c r="K33" s="3">
         <v>168600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>190100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>159800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>221700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>585400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>571600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>410400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1117200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>292100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>343200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>256100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>240900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>228500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>341700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>404200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>832400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>762900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>583800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>511800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>700300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>542500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>530200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>432400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3247,209 +3322,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>254100</v>
+        <v>249300</v>
       </c>
       <c r="E35" s="3">
-        <v>124900</v>
+        <v>261000</v>
       </c>
       <c r="F35" s="3">
-        <v>213900</v>
+        <v>128300</v>
       </c>
       <c r="G35" s="3">
-        <v>237600</v>
+        <v>219700</v>
       </c>
       <c r="H35" s="3">
-        <v>209400</v>
+        <v>244100</v>
       </c>
       <c r="I35" s="3">
-        <v>152500</v>
+        <v>215100</v>
       </c>
       <c r="J35" s="3">
+        <v>156700</v>
+      </c>
+      <c r="K35" s="3">
         <v>168600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>190100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>159800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>221700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>585400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>571600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>410400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1117200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>292100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>343200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>256100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>240900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>228500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>341700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>404200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>832400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>762900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>583800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>511800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>700300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>542500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>530200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>432400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3484,8 +3568,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3520,890 +3605,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1254900</v>
+        <v>1180100</v>
       </c>
       <c r="E41" s="3">
-        <v>1062100</v>
+        <v>1289200</v>
       </c>
       <c r="F41" s="3">
-        <v>849900</v>
+        <v>1091200</v>
       </c>
       <c r="G41" s="3">
-        <v>1137300</v>
+        <v>873200</v>
       </c>
       <c r="H41" s="3">
-        <v>1238000</v>
+        <v>1168500</v>
       </c>
       <c r="I41" s="3">
-        <v>1374000</v>
+        <v>1272000</v>
       </c>
       <c r="J41" s="3">
+        <v>1411700</v>
+      </c>
+      <c r="K41" s="3">
         <v>869800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>876200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>688900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>654500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1118700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1154500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>911200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1027200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1450500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1212500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>938900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1080200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1147800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1277400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1871900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1265600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>258900</v>
+        <v>164900</v>
       </c>
       <c r="E42" s="3">
-        <v>157300</v>
+        <v>266000</v>
       </c>
       <c r="F42" s="3">
-        <v>314600</v>
+        <v>161600</v>
       </c>
       <c r="G42" s="3">
-        <v>259300</v>
+        <v>323200</v>
       </c>
       <c r="H42" s="3">
-        <v>162300</v>
+        <v>266400</v>
       </c>
       <c r="I42" s="3">
-        <v>115100</v>
+        <v>166700</v>
       </c>
       <c r="J42" s="3">
+        <v>118300</v>
+      </c>
+      <c r="K42" s="3">
         <v>472700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>523300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>378500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>325600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1264900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1186400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1078700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1109500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>840400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>795000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>903200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>766900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>866400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>728100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>733100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>975400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>318100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>452600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>540900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>590800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>626300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>647200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>612800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>437300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1924700</v>
+        <v>1965700</v>
       </c>
       <c r="E43" s="3">
-        <v>1821600</v>
+        <v>1977500</v>
       </c>
       <c r="F43" s="3">
-        <v>1975100</v>
+        <v>1871600</v>
       </c>
       <c r="G43" s="3">
-        <v>1785800</v>
+        <v>2029200</v>
       </c>
       <c r="H43" s="3">
-        <v>1854900</v>
+        <v>1834700</v>
       </c>
       <c r="I43" s="3">
-        <v>1908400</v>
+        <v>1905800</v>
       </c>
       <c r="J43" s="3">
+        <v>1960600</v>
+      </c>
+      <c r="K43" s="3">
         <v>2052200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2083500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2117900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1957700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2772400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2584400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2644400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2528400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2663000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2649400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2902000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2886300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3122000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2860700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3116800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2605400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>159900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>157700</v>
+      </c>
+      <c r="F44" s="3">
+        <v>134900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>140500</v>
+      </c>
+      <c r="H44" s="3">
+        <v>125100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>150100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>124800</v>
+      </c>
+      <c r="K44" s="3">
+        <v>143500</v>
+      </c>
+      <c r="L44" s="3">
+        <v>139300</v>
+      </c>
+      <c r="M44" s="3">
+        <v>172000</v>
+      </c>
+      <c r="N44" s="3">
         <v>153500</v>
       </c>
-      <c r="E44" s="3">
-        <v>131300</v>
-      </c>
-      <c r="F44" s="3">
-        <v>136700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>121700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>146100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>121400</v>
-      </c>
-      <c r="J44" s="3">
-        <v>143500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>139300</v>
-      </c>
-      <c r="L44" s="3">
-        <v>172000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>153500</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>148700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>158800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>163900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>128600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>166300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>165500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>174800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>138400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>178500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>197000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>239900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>242000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>208700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>217800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>213800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>239700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>219000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>231900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>223700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>233900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1598000</v>
+        <v>1679200</v>
       </c>
       <c r="E45" s="3">
-        <v>1635200</v>
+        <v>1641800</v>
       </c>
       <c r="F45" s="3">
-        <v>1552400</v>
+        <v>1680000</v>
       </c>
       <c r="G45" s="3">
-        <v>1591200</v>
+        <v>1594900</v>
       </c>
       <c r="H45" s="3">
-        <v>1717100</v>
+        <v>1634800</v>
       </c>
       <c r="I45" s="3">
-        <v>1751000</v>
+        <v>1764100</v>
       </c>
       <c r="J45" s="3">
+        <v>1799000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1804400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1744200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1682200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1673200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1685000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1771500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1762000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1787600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1834500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1869300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1904400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2003300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1881800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1612400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1635700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1597000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>305100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>341700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>228600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>212400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>289400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5190000</v>
+        <v>5149800</v>
       </c>
       <c r="E46" s="3">
-        <v>4807500</v>
+        <v>5332200</v>
       </c>
       <c r="F46" s="3">
-        <v>4828600</v>
+        <v>4939200</v>
       </c>
       <c r="G46" s="3">
-        <v>4895400</v>
+        <v>4960900</v>
       </c>
       <c r="H46" s="3">
-        <v>5118400</v>
+        <v>5029500</v>
       </c>
       <c r="I46" s="3">
-        <v>5270000</v>
+        <v>5258600</v>
       </c>
       <c r="J46" s="3">
+        <v>5414400</v>
+      </c>
+      <c r="K46" s="3">
         <v>5342600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5366500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5039500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4764500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6989700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6855700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6560200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6581300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6954700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6691700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6823200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6875200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7196700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6675700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7597400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6685400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>3048200</v>
+        <v>3053200</v>
       </c>
       <c r="E47" s="3">
-        <v>2912400</v>
+        <v>3131700</v>
       </c>
       <c r="F47" s="3">
-        <v>2942900</v>
+        <v>2992200</v>
       </c>
       <c r="G47" s="3">
-        <v>2886900</v>
+        <v>3023600</v>
       </c>
       <c r="H47" s="3">
-        <v>2833100</v>
+        <v>2966000</v>
       </c>
       <c r="I47" s="3">
-        <v>2747900</v>
+        <v>2910700</v>
       </c>
       <c r="J47" s="3">
+        <v>2823200</v>
+      </c>
+      <c r="K47" s="3">
         <v>2756600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2913200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3235400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3194500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15039700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13968200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12464800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12336800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12316200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12493000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12472300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12502800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12994600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12402900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12830400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>11621100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>9238300</v>
+        <v>9271600</v>
       </c>
       <c r="E48" s="3">
-        <v>9519900</v>
+        <v>9491400</v>
       </c>
       <c r="F48" s="3">
-        <v>9264600</v>
+        <v>9780800</v>
       </c>
       <c r="G48" s="3">
-        <v>9463400</v>
+        <v>9518500</v>
       </c>
       <c r="H48" s="3">
-        <v>9390100</v>
+        <v>9722700</v>
       </c>
       <c r="I48" s="3">
-        <v>9743800</v>
+        <v>9647400</v>
       </c>
       <c r="J48" s="3">
+        <v>10010700</v>
+      </c>
+      <c r="K48" s="3">
         <v>9104400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9648000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9698000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9670700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9855200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9932800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9546300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10032800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9386500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10160800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10069700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10993400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10310700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9942300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10188200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9003400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3493300</v>
+        <v>3448900</v>
       </c>
       <c r="E49" s="3">
-        <v>3603400</v>
+        <v>3589000</v>
       </c>
       <c r="F49" s="3">
-        <v>3602300</v>
+        <v>3702100</v>
       </c>
       <c r="G49" s="3">
-        <v>3718500</v>
+        <v>3701000</v>
       </c>
       <c r="H49" s="3">
-        <v>3823300</v>
+        <v>3820400</v>
       </c>
       <c r="I49" s="3">
-        <v>3941900</v>
+        <v>3928100</v>
       </c>
       <c r="J49" s="3">
+        <v>4049900</v>
+      </c>
+      <c r="K49" s="3">
         <v>3968600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4254900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4434400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4456700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5635200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5629100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5622000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5845300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6083200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6545900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6426000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6643300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7011600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7117600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7518000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7099700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4500,8 +4613,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4598,106 +4714,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1146700</v>
+        <v>1165300</v>
       </c>
       <c r="E52" s="3">
-        <v>1143900</v>
+        <v>1178100</v>
       </c>
       <c r="F52" s="3">
-        <v>1173300</v>
+        <v>1175200</v>
       </c>
       <c r="G52" s="3">
-        <v>1158800</v>
+        <v>1205400</v>
       </c>
       <c r="H52" s="3">
-        <v>1129000</v>
+        <v>1190600</v>
       </c>
       <c r="I52" s="3">
-        <v>1151400</v>
+        <v>1160000</v>
       </c>
       <c r="J52" s="3">
+        <v>1182900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1114600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1110200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1135100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1097000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1238200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1157300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1150100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1134000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1186500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1333900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1439300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1407300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1632000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1341300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1311200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1180300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>707400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>521500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>530700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>521800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>693000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4794,106 +4916,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>22116500</v>
+        <v>22088800</v>
       </c>
       <c r="E54" s="3">
-        <v>21987000</v>
+        <v>22722400</v>
       </c>
       <c r="F54" s="3">
-        <v>21811900</v>
+        <v>22589400</v>
       </c>
       <c r="G54" s="3">
-        <v>22123100</v>
+        <v>22409500</v>
       </c>
       <c r="H54" s="3">
-        <v>22294000</v>
+        <v>22729200</v>
       </c>
       <c r="I54" s="3">
-        <v>22855000</v>
+        <v>22904800</v>
       </c>
       <c r="J54" s="3">
+        <v>23481200</v>
+      </c>
+      <c r="K54" s="3">
         <v>22286700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23292800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23542500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23183500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38758100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37543200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35343500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35930200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35927000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37225300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37230600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38422000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39145600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37479700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39445300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35590100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4928,8 +5056,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4964,596 +5093,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>105800</v>
+        <v>69600</v>
       </c>
       <c r="E57" s="3">
-        <v>102100</v>
+        <v>108700</v>
       </c>
       <c r="F57" s="3">
-        <v>93100</v>
+        <v>104900</v>
       </c>
       <c r="G57" s="3">
-        <v>74200</v>
+        <v>95700</v>
       </c>
       <c r="H57" s="3">
-        <v>101500</v>
+        <v>76200</v>
       </c>
       <c r="I57" s="3">
-        <v>65200</v>
+        <v>104200</v>
       </c>
       <c r="J57" s="3">
+        <v>66900</v>
+      </c>
+      <c r="K57" s="3">
         <v>108600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>86000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>142900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>253700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>228200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>249000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>279700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>285700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>327300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>372600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>405200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>332700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>283700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>320300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>217500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>221100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>204600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>309500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>226300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>219400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>237100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>362200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1693400</v>
+        <v>1929100</v>
       </c>
       <c r="E58" s="3">
-        <v>1456100</v>
+        <v>1739800</v>
       </c>
       <c r="F58" s="3">
-        <v>1210800</v>
+        <v>1496000</v>
       </c>
       <c r="G58" s="3">
-        <v>1414300</v>
+        <v>1244000</v>
       </c>
       <c r="H58" s="3">
-        <v>1760000</v>
+        <v>1453100</v>
       </c>
       <c r="I58" s="3">
-        <v>1822800</v>
+        <v>1808200</v>
       </c>
       <c r="J58" s="3">
+        <v>1872800</v>
+      </c>
+      <c r="K58" s="3">
         <v>2070200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1920500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1409000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1344700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1420900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1244900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1236100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1056900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1029100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>963600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1234000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1198200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1223800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1310400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1605600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>894000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>856100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>944800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>802000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3499400</v>
+        <v>3308400</v>
       </c>
       <c r="E59" s="3">
-        <v>3547400</v>
+        <v>3595200</v>
       </c>
       <c r="F59" s="3">
-        <v>3460100</v>
+        <v>3644600</v>
       </c>
       <c r="G59" s="3">
-        <v>3372700</v>
+        <v>3554900</v>
       </c>
       <c r="H59" s="3">
-        <v>3396700</v>
+        <v>3465100</v>
       </c>
       <c r="I59" s="3">
-        <v>3986000</v>
+        <v>3489800</v>
       </c>
       <c r="J59" s="3">
+        <v>4095200</v>
+      </c>
+      <c r="K59" s="3">
         <v>3244300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3751200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3814800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3732700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4610800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4393200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4508600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4796900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4594700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4758600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4813200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5103100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4927800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4464800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5319400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4537700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>5298600</v>
+        <v>5307100</v>
       </c>
       <c r="E60" s="3">
-        <v>5105600</v>
+        <v>5443700</v>
       </c>
       <c r="F60" s="3">
-        <v>4764100</v>
+        <v>5245500</v>
       </c>
       <c r="G60" s="3">
-        <v>4861200</v>
+        <v>4894600</v>
       </c>
       <c r="H60" s="3">
-        <v>5258100</v>
+        <v>4994400</v>
       </c>
       <c r="I60" s="3">
-        <v>5874000</v>
+        <v>5402200</v>
       </c>
       <c r="J60" s="3">
+        <v>6034900</v>
+      </c>
+      <c r="K60" s="3">
         <v>5423100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5757700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5340200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5220300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6285400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5866300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5993700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6133500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5909400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6022700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6374500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6673900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6556800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6107900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7208600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5751900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>6301200</v>
+        <v>5902500</v>
       </c>
       <c r="E61" s="3">
-        <v>6322200</v>
+        <v>6473900</v>
       </c>
       <c r="F61" s="3">
-        <v>6409500</v>
+        <v>6495400</v>
       </c>
       <c r="G61" s="3">
-        <v>6580800</v>
+        <v>6585100</v>
       </c>
       <c r="H61" s="3">
-        <v>6405100</v>
+        <v>6761100</v>
       </c>
       <c r="I61" s="3">
-        <v>6269100</v>
+        <v>6580600</v>
       </c>
       <c r="J61" s="3">
+        <v>6440900</v>
+      </c>
+      <c r="K61" s="3">
         <v>5995600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6304100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6669800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6431400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8165900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8169800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7876200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8059700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7920900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8322200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8551200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8623500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8522600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7920200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8288300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7213600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1426000</v>
+        <v>1439200</v>
       </c>
       <c r="E62" s="3">
-        <v>1632500</v>
+        <v>1465000</v>
       </c>
       <c r="F62" s="3">
-        <v>1607000</v>
+        <v>1677300</v>
       </c>
       <c r="G62" s="3">
-        <v>1633700</v>
+        <v>1651000</v>
       </c>
       <c r="H62" s="3">
-        <v>1639500</v>
+        <v>1678400</v>
       </c>
       <c r="I62" s="3">
-        <v>1838600</v>
+        <v>1684400</v>
       </c>
       <c r="J62" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1891200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1999600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2085000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2280300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3919000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3702000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3292500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3439900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3368000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3426800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3363300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3730200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3901800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3713300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3819900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3851200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5650,8 +5798,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5748,8 +5899,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5846,106 +6000,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>13606000</v>
+        <v>13254100</v>
       </c>
       <c r="E66" s="3">
-        <v>13673000</v>
+        <v>13978800</v>
       </c>
       <c r="F66" s="3">
-        <v>13380600</v>
+        <v>14047600</v>
       </c>
       <c r="G66" s="3">
-        <v>13665900</v>
+        <v>13747200</v>
       </c>
       <c r="H66" s="3">
-        <v>13882100</v>
+        <v>14040300</v>
       </c>
       <c r="I66" s="3">
-        <v>14592700</v>
+        <v>14262500</v>
       </c>
       <c r="J66" s="3">
+        <v>14992500</v>
+      </c>
+      <c r="K66" s="3">
         <v>13887800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14660500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14683200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14498900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19056700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18415600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17659600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18122300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17605800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18193000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18168300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18914300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18899300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17654900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19205500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16714600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5980,8 +6140,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6078,8 +6239,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6176,8 +6340,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6274,8 +6441,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6372,106 +6542,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>16591400</v>
+        <v>17122800</v>
       </c>
       <c r="E72" s="3">
-        <v>16644000</v>
+        <v>17045900</v>
       </c>
       <c r="F72" s="3">
-        <v>16664900</v>
+        <v>17100000</v>
       </c>
       <c r="G72" s="3">
-        <v>16579800</v>
+        <v>17121500</v>
       </c>
       <c r="H72" s="3">
-        <v>16461300</v>
+        <v>17034100</v>
       </c>
       <c r="I72" s="3">
-        <v>16398500</v>
+        <v>16912300</v>
       </c>
       <c r="J72" s="3">
+        <v>16847800</v>
+      </c>
+      <c r="K72" s="3">
         <v>16393600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17006300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17168800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16828000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16730300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16259600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16928100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17236400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17398700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18050600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18362200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18894400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19871700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19470600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19870500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18601400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6568,8 +6744,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6666,8 +6845,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6764,106 +6946,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>8510400</v>
+        <v>8834700</v>
       </c>
       <c r="E76" s="3">
-        <v>8314000</v>
+        <v>8743600</v>
       </c>
       <c r="F76" s="3">
-        <v>8431200</v>
+        <v>8541800</v>
       </c>
       <c r="G76" s="3">
-        <v>8457200</v>
+        <v>8662200</v>
       </c>
       <c r="H76" s="3">
-        <v>8411800</v>
+        <v>8688900</v>
       </c>
       <c r="I76" s="3">
-        <v>8262400</v>
+        <v>8642300</v>
       </c>
       <c r="J76" s="3">
+        <v>8488700</v>
+      </c>
+      <c r="K76" s="3">
         <v>8398900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8632300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8859300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8684500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19701400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19127600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17683900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17807900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18321200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19032300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19062300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19507700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20246300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19824800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20239800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18875500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6960,209 +7148,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>254100</v>
+        <v>249300</v>
       </c>
       <c r="E81" s="3">
-        <v>124900</v>
+        <v>261000</v>
       </c>
       <c r="F81" s="3">
-        <v>213900</v>
+        <v>128300</v>
       </c>
       <c r="G81" s="3">
-        <v>237600</v>
+        <v>219700</v>
       </c>
       <c r="H81" s="3">
-        <v>209400</v>
+        <v>244100</v>
       </c>
       <c r="I81" s="3">
-        <v>152500</v>
+        <v>215100</v>
       </c>
       <c r="J81" s="3">
+        <v>156700</v>
+      </c>
+      <c r="K81" s="3">
         <v>168600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>190100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>159800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>221700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>585400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>571600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>410400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1117200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>292100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>343200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>256100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>240900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>228500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>341700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>404200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>832400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>762900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>583800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>511800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>700300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>542500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>530200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>432400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7197,106 +7394,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>680000</v>
+        <v>688700</v>
       </c>
       <c r="E83" s="3">
-        <v>686500</v>
+        <v>698600</v>
       </c>
       <c r="F83" s="3">
-        <v>677400</v>
+        <v>705300</v>
       </c>
       <c r="G83" s="3">
+        <v>695900</v>
+      </c>
+      <c r="H83" s="3">
+        <v>711100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>700800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>701100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>681500</v>
+      </c>
+      <c r="L83" s="3">
+        <v>715000</v>
+      </c>
+      <c r="M83" s="3">
+        <v>728600</v>
+      </c>
+      <c r="N83" s="3">
+        <v>744200</v>
+      </c>
+      <c r="O83" s="3">
+        <v>789300</v>
+      </c>
+      <c r="P83" s="3">
+        <v>777100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>764800</v>
+      </c>
+      <c r="R83" s="3">
+        <v>3127500</v>
+      </c>
+      <c r="S83" s="3">
+        <v>796700</v>
+      </c>
+      <c r="T83" s="3">
+        <v>835300</v>
+      </c>
+      <c r="U83" s="3">
+        <v>856200</v>
+      </c>
+      <c r="V83" s="3">
+        <v>874600</v>
+      </c>
+      <c r="W83" s="3">
+        <v>892700</v>
+      </c>
+      <c r="X83" s="3">
+        <v>855000</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>848400</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>711200</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>653900</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>677500</v>
+      </c>
+      <c r="AC83" s="3">
         <v>692100</v>
       </c>
-      <c r="H83" s="3">
-        <v>682100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>682400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>681500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>715000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>728600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>744200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>789300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>777100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>764800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3127500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>796700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>835300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>856200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>874600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>892700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>855000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>848400</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>711200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>653900</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>677500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>692100</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>732200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>718700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>707600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>715200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>722200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7393,8 +7594,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7491,8 +7695,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7589,8 +7796,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7687,8 +7897,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7785,106 +7998,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>816700</v>
+        <v>952600</v>
       </c>
       <c r="E89" s="3">
-        <v>886100</v>
+        <v>839000</v>
       </c>
       <c r="F89" s="3">
-        <v>974900</v>
+        <v>910400</v>
       </c>
       <c r="G89" s="3">
-        <v>1002300</v>
+        <v>1001700</v>
       </c>
       <c r="H89" s="3">
-        <v>748100</v>
+        <v>1029700</v>
       </c>
       <c r="I89" s="3">
-        <v>1000000</v>
+        <v>768600</v>
       </c>
       <c r="J89" s="3">
+        <v>1027400</v>
+      </c>
+      <c r="K89" s="3">
         <v>768900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1095600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>996900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1011600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1053900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1039700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>659400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4366400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1263500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1549000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>816800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>975700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>746100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>907500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>881500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1389100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>382000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>829300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>828600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>969400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>776500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>837300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7919,106 +8138,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-527297000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-590523000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-985897000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-676260000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-634496000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-783990000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-415900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-558800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-742400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-526800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-878200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-969100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-796300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-571500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-629400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-789700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8115,8 +8338,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8213,106 +8439,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-469900</v>
+        <v>-267900</v>
       </c>
       <c r="E94" s="3">
-        <v>-557300</v>
+        <v>-482700</v>
       </c>
       <c r="F94" s="3">
-        <v>-662400</v>
+        <v>-572500</v>
       </c>
       <c r="G94" s="3">
-        <v>-656400</v>
+        <v>-680500</v>
       </c>
       <c r="H94" s="3">
-        <v>-571600</v>
+        <v>-674300</v>
       </c>
       <c r="I94" s="3">
-        <v>-326800</v>
+        <v>-587300</v>
       </c>
       <c r="J94" s="3">
+        <v>-335700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-566700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-595300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-616500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-583300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-874100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-764500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-387600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-907100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-515500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-404700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8347,8 +8579,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8356,50 +8589,50 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-131100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-132400</v>
+        <v>-134700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-136000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-135700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-132100</v>
       </c>
-      <c r="J96" s="3">
-        <v>-132100</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>-133400</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-556600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-56300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8407,11 +8640,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-64000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -8419,11 +8652,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8431,11 +8664,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -8443,10 +8676,13 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8543,8 +8779,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8641,8 +8880,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8739,298 +8981,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-158500</v>
+        <v>-796800</v>
       </c>
       <c r="E100" s="3">
-        <v>-112400</v>
+        <v>-162800</v>
       </c>
       <c r="F100" s="3">
-        <v>-601700</v>
+        <v>-115500</v>
       </c>
       <c r="G100" s="3">
-        <v>-446900</v>
+        <v>-618200</v>
       </c>
       <c r="H100" s="3">
-        <v>-314300</v>
+        <v>-459200</v>
       </c>
       <c r="I100" s="3">
-        <v>-160300</v>
+        <v>-322900</v>
       </c>
       <c r="J100" s="3">
+        <v>-164700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-182000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-309700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-364600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-892500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-220900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-43900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-377800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-56600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-725800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>83100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>324500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>120000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>19100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-163300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>696800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>30200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>19200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="E101" s="3">
-        <v>-4200</v>
+        <v>4500</v>
       </c>
       <c r="F101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G101" s="3">
         <v>1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
-        <v>1800</v>
-      </c>
       <c r="I101" s="3">
-        <v>-8600</v>
+        <v>1900</v>
       </c>
       <c r="J101" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K101" s="3">
         <v>7900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-11300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>192700</v>
+        <v>-109100</v>
       </c>
       <c r="E102" s="3">
-        <v>212200</v>
+        <v>198000</v>
       </c>
       <c r="F102" s="3">
-        <v>-287400</v>
+        <v>218000</v>
       </c>
       <c r="G102" s="3">
-        <v>-100700</v>
+        <v>-295300</v>
       </c>
       <c r="H102" s="3">
-        <v>-136000</v>
+        <v>-103500</v>
       </c>
       <c r="I102" s="3">
-        <v>504300</v>
+        <v>-139800</v>
       </c>
       <c r="J102" s="3">
+        <v>518100</v>
+      </c>
+      <c r="K102" s="3">
         <v>28100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>196300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-464100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-35800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>231000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-102400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>74100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>297900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>307100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-128600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-144100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-532800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>500800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>783600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>359500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>9300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>184400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>63700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>581400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,448 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3316800</v>
+        <v>3450600</v>
       </c>
       <c r="E8" s="3">
-        <v>3356000</v>
+        <v>3209300</v>
       </c>
       <c r="F8" s="3">
-        <v>3395500</v>
+        <v>3329500</v>
       </c>
       <c r="G8" s="3">
-        <v>3302000</v>
+        <v>3491200</v>
       </c>
       <c r="H8" s="3">
-        <v>3229800</v>
+        <v>3270500</v>
       </c>
       <c r="I8" s="3">
-        <v>3279200</v>
+        <v>3269600</v>
       </c>
       <c r="J8" s="3">
+        <v>3353300</v>
+      </c>
+      <c r="K8" s="3">
         <v>3295800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3170700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3260300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3293500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3221500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3161300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3093900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3043700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12065800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3643200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3728700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3738500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3746400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4059500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3904600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3944800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>127100</v>
+        <v>355700</v>
       </c>
       <c r="E9" s="3">
-        <v>132700</v>
+        <v>291500</v>
       </c>
       <c r="F9" s="3">
-        <v>133400</v>
+        <v>323200</v>
       </c>
       <c r="G9" s="3">
-        <v>120700</v>
+        <v>871300</v>
       </c>
       <c r="H9" s="3">
-        <v>125400</v>
+        <v>303400</v>
       </c>
       <c r="I9" s="3">
-        <v>129400</v>
+        <v>291300</v>
       </c>
       <c r="J9" s="3">
+        <v>317000</v>
+      </c>
+      <c r="K9" s="3">
         <v>120500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>131400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>140800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>145800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>141200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>138100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>137400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>143500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>578000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>155100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>167900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>163800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>162600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>163700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>165200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>172300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>136400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>171900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>183800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>180600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>190800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>197200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>187500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>199000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>153400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3189700</v>
+        <v>3094900</v>
       </c>
       <c r="E10" s="3">
-        <v>3223300</v>
+        <v>2917800</v>
       </c>
       <c r="F10" s="3">
-        <v>3262100</v>
+        <v>3006200</v>
       </c>
       <c r="G10" s="3">
-        <v>3181300</v>
+        <v>2619900</v>
       </c>
       <c r="H10" s="3">
-        <v>3104400</v>
+        <v>2967100</v>
       </c>
       <c r="I10" s="3">
-        <v>3149800</v>
+        <v>2978300</v>
       </c>
       <c r="J10" s="3">
+        <v>3036200</v>
+      </c>
+      <c r="K10" s="3">
         <v>3175400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3039300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3119500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3147600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3080300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3023100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2956500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2900200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11487800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3488100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3560800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3574700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3583800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3895800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3739400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3772400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1133,109 +1151,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>73100</v>
+        <v>78000</v>
       </c>
       <c r="E12" s="3">
+        <v>70700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>66200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>90600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>67200</v>
+      </c>
+      <c r="I12" s="3">
         <v>66700</v>
       </c>
-      <c r="F12" s="3">
-        <v>88200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>67900</v>
-      </c>
-      <c r="H12" s="3">
-        <v>65900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>55200</v>
-      </c>
       <c r="J12" s="3">
+        <v>56400</v>
+      </c>
+      <c r="K12" s="3">
         <v>67100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>61800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>60100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>75800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>60300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>62000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>61800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>264900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>80700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>85000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>92700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>86500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>83300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>84700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>90800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>88900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>76200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>82500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>75100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>90300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>90800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>83500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>85200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>82100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1335,210 +1357,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>91</v>
+        <v>72900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1900</v>
       </c>
       <c r="F14" s="3">
-        <v>7400</v>
+        <v>-14500</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>12500</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>12500</v>
-      </c>
-      <c r="K14" s="3">
-        <v>300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-3700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>150500</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>10300</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>54900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>214000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>52300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>662900</v>
+        <v>675500</v>
       </c>
       <c r="E15" s="3">
-        <v>672900</v>
+        <v>641400</v>
       </c>
       <c r="F15" s="3">
-        <v>679600</v>
+        <v>667600</v>
       </c>
       <c r="G15" s="3">
-        <v>671100</v>
+        <v>698800</v>
       </c>
       <c r="H15" s="3">
-        <v>685200</v>
+        <v>664700</v>
       </c>
       <c r="I15" s="3">
-        <v>675100</v>
+        <v>693700</v>
       </c>
       <c r="J15" s="3">
+        <v>690400</v>
+      </c>
+      <c r="K15" s="3">
         <v>676400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>657900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>689600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>701400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>691800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>696100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>684800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>672700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2748500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>775500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>807500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>827200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>912300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>856100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>818700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>810900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>676100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>621700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>644900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>660200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>696900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>684300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>674200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>685500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>695000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1571,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2913600</v>
+        <v>3045100</v>
       </c>
       <c r="E17" s="3">
-        <v>2982100</v>
+        <v>2819900</v>
       </c>
       <c r="F17" s="3">
-        <v>3180100</v>
+        <v>2959600</v>
       </c>
       <c r="G17" s="3">
-        <v>2928500</v>
+        <v>3262200</v>
       </c>
       <c r="H17" s="3">
-        <v>2882500</v>
+        <v>2902100</v>
       </c>
       <c r="I17" s="3">
-        <v>2908100</v>
+        <v>2918400</v>
       </c>
       <c r="J17" s="3">
+        <v>2975200</v>
+      </c>
+      <c r="K17" s="3">
         <v>3117500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2831100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2911000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2960500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3055700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2866500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2797100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2766800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11279900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3367600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3449200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3485400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3664800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3790900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3622600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3651300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>403100</v>
+        <v>405600</v>
       </c>
       <c r="E18" s="3">
-        <v>373900</v>
+        <v>389400</v>
       </c>
       <c r="F18" s="3">
-        <v>215400</v>
+        <v>369900</v>
       </c>
       <c r="G18" s="3">
-        <v>373400</v>
+        <v>229100</v>
       </c>
       <c r="H18" s="3">
-        <v>347300</v>
+        <v>368300</v>
       </c>
       <c r="I18" s="3">
-        <v>371000</v>
+        <v>351200</v>
       </c>
       <c r="J18" s="3">
+        <v>378100</v>
+      </c>
+      <c r="K18" s="3">
         <v>178400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>339600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>349300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>332900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>165800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>294800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>296800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>276900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>785900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>275700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>279500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>253100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>81700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>268600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>282000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>293500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>246000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>289300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>272600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>220900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>345000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>368800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>367500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>266100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1810,513 +1848,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>29800</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>35500</v>
+        <v>-8700</v>
       </c>
       <c r="F20" s="3">
-        <v>25100</v>
+        <v>5100</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>62000</v>
+        <v>10900</v>
       </c>
       <c r="I20" s="3">
-        <v>14400</v>
+        <v>4500</v>
       </c>
       <c r="J20" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K20" s="3">
         <v>6800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-19900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>109100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>188000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>133700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>109700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>265700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>320200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>140700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>130200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>116400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>225300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>607100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>866100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>748000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>552300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>662700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>601900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>355900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>351300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>307600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1121700</v>
+        <v>1080800</v>
       </c>
       <c r="E21" s="3">
-        <v>1108000</v>
+        <v>1039400</v>
       </c>
       <c r="F21" s="3">
-        <v>945800</v>
+        <v>1032300</v>
       </c>
       <c r="G21" s="3">
-        <v>1069100</v>
+        <v>929900</v>
       </c>
       <c r="H21" s="3">
-        <v>1120400</v>
+        <v>1022100</v>
       </c>
       <c r="I21" s="3">
-        <v>1086300</v>
+        <v>1040400</v>
       </c>
       <c r="J21" s="3">
+        <v>1048100</v>
+      </c>
+      <c r="K21" s="3">
         <v>886300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1001200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1078700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1037300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1019100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1111900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1261900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1175500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4023100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1338100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1435000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1250100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>956400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1291600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1253400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1367100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>74300</v>
+        <v>74200</v>
       </c>
       <c r="E22" s="3">
-        <v>78800</v>
+        <v>71900</v>
       </c>
       <c r="F22" s="3">
-        <v>77500</v>
+        <v>78200</v>
       </c>
       <c r="G22" s="3">
-        <v>73200</v>
+        <v>79700</v>
       </c>
       <c r="H22" s="3">
-        <v>71900</v>
+        <v>72500</v>
       </c>
       <c r="I22" s="3">
-        <v>69800</v>
+        <v>72800</v>
       </c>
       <c r="J22" s="3">
+        <v>71400</v>
+      </c>
+      <c r="K22" s="3">
         <v>77200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>55200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>57700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>56900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>53600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>53300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>51600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>216700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>143600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>155100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>84400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>89700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>87900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>87600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>93100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>75000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>57500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>60400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>63100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>68300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>63400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>66100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>67000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>66000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>358600</v>
+        <v>277700</v>
       </c>
       <c r="E23" s="3">
-        <v>330600</v>
+        <v>347000</v>
       </c>
       <c r="F23" s="3">
-        <v>163000</v>
+        <v>327900</v>
       </c>
       <c r="G23" s="3">
-        <v>300000</v>
+        <v>167600</v>
       </c>
       <c r="H23" s="3">
-        <v>337400</v>
+        <v>297200</v>
       </c>
       <c r="I23" s="3">
-        <v>315700</v>
+        <v>341500</v>
       </c>
       <c r="J23" s="3">
+        <v>322800</v>
+      </c>
+      <c r="K23" s="3">
         <v>108000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>264500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>306100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>251800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>221200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>269300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>433200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>360000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>678900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>397800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>444700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>309400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>311000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>310800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>425700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>507400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>977000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>761900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>815400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>883600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>658600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>651800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>507700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>96000</v>
+        <v>64400</v>
       </c>
       <c r="E24" s="3">
-        <v>59100</v>
+        <v>92900</v>
       </c>
       <c r="F24" s="3">
-        <v>22500</v>
+        <v>58600</v>
       </c>
       <c r="G24" s="3">
-        <v>68900</v>
+        <v>23100</v>
       </c>
       <c r="H24" s="3">
-        <v>76600</v>
+        <v>68200</v>
       </c>
       <c r="I24" s="3">
-        <v>88800</v>
+        <v>77500</v>
       </c>
       <c r="J24" s="3">
+        <v>90800</v>
+      </c>
+      <c r="K24" s="3">
         <v>-59800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>85200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>109900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>82100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>62700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>71700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>102700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>96700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>165900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>96100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>94500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>52400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>66700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>82900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>85700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>108800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>204200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>208900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>179400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>234000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>185800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>112600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>126700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>80500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2416,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>262600</v>
+        <v>213300</v>
       </c>
       <c r="E26" s="3">
-        <v>271500</v>
+        <v>254100</v>
       </c>
       <c r="F26" s="3">
-        <v>140600</v>
+        <v>269300</v>
       </c>
       <c r="G26" s="3">
-        <v>231200</v>
+        <v>144500</v>
       </c>
       <c r="H26" s="3">
-        <v>260800</v>
+        <v>229000</v>
       </c>
       <c r="I26" s="3">
-        <v>226900</v>
+        <v>264000</v>
       </c>
       <c r="J26" s="3">
+        <v>232000</v>
+      </c>
+      <c r="K26" s="3">
         <v>167800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>179300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>196200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>169700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>158600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>197600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>330500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>263300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>513000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>301700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>350200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>257000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-39400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>244200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>228000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>340000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>398600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>850400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>768000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>582400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>581400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>697800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>546000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>525100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>427200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>249300</v>
+        <v>201000</v>
       </c>
       <c r="E27" s="3">
-        <v>261000</v>
+        <v>241300</v>
       </c>
       <c r="F27" s="3">
-        <v>128300</v>
+        <v>259000</v>
       </c>
       <c r="G27" s="3">
-        <v>219700</v>
+        <v>131900</v>
       </c>
       <c r="H27" s="3">
-        <v>244100</v>
+        <v>217600</v>
       </c>
       <c r="I27" s="3">
-        <v>215100</v>
+        <v>247100</v>
       </c>
       <c r="J27" s="3">
+        <v>220000</v>
+      </c>
+      <c r="K27" s="3">
         <v>156700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>168600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>190100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>159800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>141700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>189900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>313600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>253300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>475400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>292100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>343200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>256100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-27200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>240900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>228500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>341700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>404200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>832400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>762900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>583800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>511800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>542500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>530200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>432400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,31 +2782,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>91</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>91</v>
@@ -2754,29 +2820,29 @@
       <c r="M29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29" s="3">
         <v>80000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>395400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>257900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>157000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>641800</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2820,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2921,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3022,210 +3094,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-29800</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>-35500</v>
+        <v>8700</v>
       </c>
       <c r="F32" s="3">
-        <v>-25100</v>
+        <v>-5100</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-62000</v>
+        <v>-10900</v>
       </c>
       <c r="I32" s="3">
-        <v>-14400</v>
+        <v>-4500</v>
       </c>
       <c r="J32" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>19900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-109100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-133700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-109700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-265700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-320200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-140700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-130200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-116400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-225300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>249300</v>
+        <v>204700</v>
       </c>
       <c r="E33" s="3">
-        <v>261000</v>
+        <v>244900</v>
       </c>
       <c r="F33" s="3">
-        <v>128300</v>
+        <v>262700</v>
       </c>
       <c r="G33" s="3">
-        <v>219700</v>
+        <v>135700</v>
       </c>
       <c r="H33" s="3">
-        <v>244100</v>
+        <v>221300</v>
       </c>
       <c r="I33" s="3">
-        <v>215100</v>
+        <v>249900</v>
       </c>
       <c r="J33" s="3">
+        <v>222800</v>
+      </c>
+      <c r="K33" s="3">
         <v>156700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>168600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>190100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>159800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>221700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>585400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>571600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>410400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1117200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>292100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>343200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>256100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>240900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>228500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>341700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>404200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>832400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>762900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>583800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>511800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>700300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>542500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>530200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>432400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3325,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>249300</v>
+        <v>204700</v>
       </c>
       <c r="E35" s="3">
-        <v>261000</v>
+        <v>244900</v>
       </c>
       <c r="F35" s="3">
-        <v>128300</v>
+        <v>262700</v>
       </c>
       <c r="G35" s="3">
-        <v>219700</v>
+        <v>135700</v>
       </c>
       <c r="H35" s="3">
-        <v>244100</v>
+        <v>221300</v>
       </c>
       <c r="I35" s="3">
-        <v>215100</v>
+        <v>249900</v>
       </c>
       <c r="J35" s="3">
+        <v>222800</v>
+      </c>
+      <c r="K35" s="3">
         <v>156700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>168600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>190100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>159800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>221700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>585400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>571600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>410400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1117200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>292100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>343200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>256100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>240900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>228500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>341700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>404200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>832400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>762900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>583800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>511800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>700300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>542500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>530200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>432400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3569,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3606,917 +3697,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1180100</v>
+        <v>1497100</v>
       </c>
       <c r="E41" s="3">
-        <v>1289200</v>
+        <v>1141900</v>
       </c>
       <c r="F41" s="3">
-        <v>1091200</v>
+        <v>1279100</v>
       </c>
       <c r="G41" s="3">
-        <v>873200</v>
+        <v>1122000</v>
       </c>
       <c r="H41" s="3">
-        <v>1168500</v>
+        <v>864900</v>
       </c>
       <c r="I41" s="3">
-        <v>1272000</v>
+        <v>1182900</v>
       </c>
       <c r="J41" s="3">
+        <v>1300700</v>
+      </c>
+      <c r="K41" s="3">
         <v>1411700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>869800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>876200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>688900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>654500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1118700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1154500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>911200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1027200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1450500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1212500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>938900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1080200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1147800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1277400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1871900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>164900</v>
+        <v>206100</v>
       </c>
       <c r="E42" s="3">
-        <v>266000</v>
+        <v>159600</v>
       </c>
       <c r="F42" s="3">
-        <v>161600</v>
+        <v>263900</v>
       </c>
       <c r="G42" s="3">
-        <v>323200</v>
+        <v>173100</v>
       </c>
       <c r="H42" s="3">
-        <v>266400</v>
+        <v>320100</v>
       </c>
       <c r="I42" s="3">
-        <v>166700</v>
+        <v>269700</v>
       </c>
       <c r="J42" s="3">
+        <v>170500</v>
+      </c>
+      <c r="K42" s="3">
         <v>118300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>472700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>523300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>378500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>325600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1264900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1186400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1078700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1109500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>840400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>795000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>903200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>766900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>866400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>728100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>733100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>975400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>318100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>452600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>540900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>590800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>626300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>647200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>612800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>437300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1965700</v>
+        <v>1974800</v>
       </c>
       <c r="E43" s="3">
-        <v>1977500</v>
+        <v>1836300</v>
       </c>
       <c r="F43" s="3">
-        <v>1871600</v>
+        <v>1897100</v>
       </c>
       <c r="G43" s="3">
-        <v>2029200</v>
+        <v>1920900</v>
       </c>
       <c r="H43" s="3">
-        <v>1834700</v>
+        <v>2006600</v>
       </c>
       <c r="I43" s="3">
-        <v>1905800</v>
+        <v>1790200</v>
       </c>
       <c r="J43" s="3">
+        <v>1884400</v>
+      </c>
+      <c r="K43" s="3">
         <v>1960600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2052200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2083500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2117900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1957700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2772400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2584400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2644400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2528400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2663000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2649400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2902000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2886300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3122000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2860700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3116800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>159900</v>
+        <v>169300</v>
       </c>
       <c r="E44" s="3">
-        <v>157700</v>
+        <v>154700</v>
       </c>
       <c r="F44" s="3">
-        <v>134900</v>
+        <v>156500</v>
       </c>
       <c r="G44" s="3">
-        <v>140500</v>
+        <v>138700</v>
       </c>
       <c r="H44" s="3">
-        <v>125100</v>
+        <v>139200</v>
       </c>
       <c r="I44" s="3">
-        <v>150100</v>
+        <v>126600</v>
       </c>
       <c r="J44" s="3">
+        <v>153500</v>
+      </c>
+      <c r="K44" s="3">
         <v>124800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>143500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>139300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>172000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>153500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>148700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>158800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>163900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>128600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>166300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>165500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>174800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>138400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>178500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>197000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>239900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>242000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>208700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>217800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>213800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>239700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>219000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>231900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>223700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>233900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1679200</v>
+        <v>255400</v>
       </c>
       <c r="E45" s="3">
-        <v>1641800</v>
+        <v>250600</v>
       </c>
       <c r="F45" s="3">
-        <v>1680000</v>
+        <v>208800</v>
       </c>
       <c r="G45" s="3">
-        <v>1594900</v>
+        <v>1668800</v>
       </c>
       <c r="H45" s="3">
-        <v>1634800</v>
+        <v>1521300</v>
       </c>
       <c r="I45" s="3">
-        <v>1764100</v>
+        <v>216000</v>
       </c>
       <c r="J45" s="3">
+        <v>336400</v>
+      </c>
+      <c r="K45" s="3">
         <v>1799000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1804400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1744200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1682200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1673200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1685000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1771500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1762000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1787600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1834500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1869300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1904400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2003300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1881800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1612400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1635700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>305100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>341700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>228600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>212400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>289400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5149800</v>
+        <v>5608100</v>
       </c>
       <c r="E46" s="3">
-        <v>5332200</v>
+        <v>4978700</v>
       </c>
       <c r="F46" s="3">
-        <v>4939200</v>
+        <v>5284500</v>
       </c>
       <c r="G46" s="3">
-        <v>4960900</v>
+        <v>5078500</v>
       </c>
       <c r="H46" s="3">
-        <v>5029500</v>
+        <v>4913600</v>
       </c>
       <c r="I46" s="3">
-        <v>5258600</v>
+        <v>5087400</v>
       </c>
       <c r="J46" s="3">
+        <v>5373300</v>
+      </c>
+      <c r="K46" s="3">
         <v>5414400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5342600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5366500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5039500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4764500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6989700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6855700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6560200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6581300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6954700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6691700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6823200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6875200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7196700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6675700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7597400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>3053200</v>
+        <v>2705000</v>
       </c>
       <c r="E47" s="3">
-        <v>3131700</v>
+        <v>2687900</v>
       </c>
       <c r="F47" s="3">
-        <v>2992200</v>
+        <v>2809100</v>
       </c>
       <c r="G47" s="3">
-        <v>3023600</v>
+        <v>2817400</v>
       </c>
       <c r="H47" s="3">
-        <v>2966000</v>
+        <v>2678500</v>
       </c>
       <c r="I47" s="3">
-        <v>2910700</v>
+        <v>2679100</v>
       </c>
       <c r="J47" s="3">
+        <v>2633400</v>
+      </c>
+      <c r="K47" s="3">
         <v>2823200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2756600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2913200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3235400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3194500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15039700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13968200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12464800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12336800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12316200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12493000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12472300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12502800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12994600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12402900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12830400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>9271600</v>
+        <v>9225600</v>
       </c>
       <c r="E48" s="3">
-        <v>9491400</v>
+        <v>8947900</v>
       </c>
       <c r="F48" s="3">
-        <v>9780800</v>
+        <v>9391300</v>
       </c>
       <c r="G48" s="3">
-        <v>9518500</v>
+        <v>10037800</v>
       </c>
       <c r="H48" s="3">
-        <v>9722700</v>
+        <v>9401300</v>
       </c>
       <c r="I48" s="3">
-        <v>9647400</v>
+        <v>9813700</v>
       </c>
       <c r="J48" s="3">
+        <v>9833400</v>
+      </c>
+      <c r="K48" s="3">
         <v>10010700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9104400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9648000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9698000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9670700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9855200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9932800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9546300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10032800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9386500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10160800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10069700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10993400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10310700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9942300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10188200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3448900</v>
+        <v>3367400</v>
       </c>
       <c r="E49" s="3">
-        <v>3589000</v>
+        <v>3337100</v>
       </c>
       <c r="F49" s="3">
-        <v>3702100</v>
+        <v>3560700</v>
       </c>
       <c r="G49" s="3">
-        <v>3701000</v>
+        <v>3806500</v>
       </c>
       <c r="H49" s="3">
-        <v>3820400</v>
+        <v>3665700</v>
       </c>
       <c r="I49" s="3">
-        <v>3928100</v>
+        <v>3867500</v>
       </c>
       <c r="J49" s="3">
+        <v>4016700</v>
+      </c>
+      <c r="K49" s="3">
         <v>4049900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3968600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4254900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4434400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4456700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5635200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5629100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5622000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5845300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6083200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6545900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6426000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6643300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7011600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7117600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7518000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4616,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4717,109 +4839,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1165300</v>
+        <v>1485400</v>
       </c>
       <c r="E52" s="3">
-        <v>1178100</v>
+        <v>1376800</v>
       </c>
       <c r="F52" s="3">
-        <v>1175200</v>
+        <v>1465900</v>
       </c>
       <c r="G52" s="3">
-        <v>1205400</v>
+        <v>624900</v>
       </c>
       <c r="H52" s="3">
-        <v>1190600</v>
+        <v>716100</v>
       </c>
       <c r="I52" s="3">
-        <v>1160000</v>
+        <v>1526000</v>
       </c>
       <c r="J52" s="3">
+        <v>1530700</v>
+      </c>
+      <c r="K52" s="3">
         <v>1182900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1114600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1110200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1135100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1097000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1238200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1157300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1150100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1134000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1186500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1333900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1439300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1407300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1632000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1341300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1311200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>707400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>521500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>530700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>521800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>693000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4919,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>22088800</v>
+        <v>22439900</v>
       </c>
       <c r="E54" s="3">
-        <v>22722400</v>
+        <v>21372800</v>
       </c>
       <c r="F54" s="3">
-        <v>22589400</v>
+        <v>22543100</v>
       </c>
       <c r="G54" s="3">
-        <v>22409500</v>
+        <v>23226500</v>
       </c>
       <c r="H54" s="3">
-        <v>22729200</v>
+        <v>22195800</v>
       </c>
       <c r="I54" s="3">
-        <v>22904800</v>
+        <v>23009700</v>
       </c>
       <c r="J54" s="3">
+        <v>23422300</v>
+      </c>
+      <c r="K54" s="3">
         <v>23481200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22286700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23292800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23542500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23183500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38758100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37543200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35343500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35930200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35927000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37225300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37230600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38422000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39145600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37479700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39445300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5057,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5094,614 +5229,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>69600</v>
+        <v>126000</v>
       </c>
       <c r="E57" s="3">
-        <v>108700</v>
+        <v>67400</v>
       </c>
       <c r="F57" s="3">
-        <v>104900</v>
+        <v>107900</v>
       </c>
       <c r="G57" s="3">
-        <v>95700</v>
+        <v>107900</v>
       </c>
       <c r="H57" s="3">
-        <v>76200</v>
+        <v>94800</v>
       </c>
       <c r="I57" s="3">
-        <v>104200</v>
+        <v>77200</v>
       </c>
       <c r="J57" s="3">
+        <v>106600</v>
+      </c>
+      <c r="K57" s="3">
         <v>66900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>108600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>86000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>142900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>253700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>228200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>249000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>279700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>285700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>327300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>372600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>405200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>332700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>283700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>320300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>217500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>221100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>204600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>309500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>226300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>219400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>237100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>362200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1929100</v>
+        <v>2527000</v>
       </c>
       <c r="E58" s="3">
-        <v>1739800</v>
+        <v>2131100</v>
       </c>
       <c r="F58" s="3">
-        <v>1496000</v>
+        <v>1996200</v>
       </c>
       <c r="G58" s="3">
-        <v>1244000</v>
+        <v>1538200</v>
       </c>
       <c r="H58" s="3">
-        <v>1453100</v>
+        <v>1232100</v>
       </c>
       <c r="I58" s="3">
-        <v>1808200</v>
+        <v>1747900</v>
       </c>
       <c r="J58" s="3">
+        <v>2127500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1872800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2070200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1920500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1409000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1344700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1420900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1244900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1236100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1056900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1029100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>963600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1234000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1198200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1223800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1310400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1605600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>894000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>856100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>944800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>802000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3308400</v>
+        <v>2406500</v>
       </c>
       <c r="E59" s="3">
-        <v>3595200</v>
+        <v>1952900</v>
       </c>
       <c r="F59" s="3">
-        <v>3644600</v>
+        <v>2398900</v>
       </c>
       <c r="G59" s="3">
-        <v>3554900</v>
+        <v>2637100</v>
       </c>
       <c r="H59" s="3">
-        <v>3465100</v>
+        <v>2406000</v>
       </c>
       <c r="I59" s="3">
-        <v>3489800</v>
+        <v>2169000</v>
       </c>
       <c r="J59" s="3">
+        <v>2298100</v>
+      </c>
+      <c r="K59" s="3">
         <v>4095200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3244300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3751200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3814800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3732700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4610800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4393200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4508600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4796900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4594700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4758600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4813200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5103100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4927800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4464800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5319400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>5307100</v>
+        <v>6188000</v>
       </c>
       <c r="E60" s="3">
-        <v>5443700</v>
+        <v>5135100</v>
       </c>
       <c r="F60" s="3">
-        <v>5245500</v>
+        <v>5400800</v>
       </c>
       <c r="G60" s="3">
-        <v>4894600</v>
+        <v>5393400</v>
       </c>
       <c r="H60" s="3">
-        <v>4994400</v>
+        <v>4848000</v>
       </c>
       <c r="I60" s="3">
-        <v>5402200</v>
+        <v>5056000</v>
       </c>
       <c r="J60" s="3">
+        <v>5524300</v>
+      </c>
+      <c r="K60" s="3">
         <v>6034900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5423100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5757700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5340200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5220300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6285400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5866300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5993700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6133500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5909400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6022700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6374500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6673900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6556800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6107900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7208600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>5902500</v>
+        <v>5490100</v>
       </c>
       <c r="E61" s="3">
-        <v>6473900</v>
+        <v>5711200</v>
       </c>
       <c r="F61" s="3">
-        <v>6495400</v>
+        <v>6422800</v>
       </c>
       <c r="G61" s="3">
-        <v>6585100</v>
+        <v>6678600</v>
       </c>
       <c r="H61" s="3">
-        <v>6761100</v>
+        <v>6522300</v>
       </c>
       <c r="I61" s="3">
-        <v>6580600</v>
+        <v>6844600</v>
       </c>
       <c r="J61" s="3">
+        <v>6729300</v>
+      </c>
+      <c r="K61" s="3">
         <v>6440900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5995600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6304100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6669800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6431400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8165900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8169800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7876200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8059700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7920900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8322200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8551200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8623500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8522600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7920200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8288300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1439200</v>
+        <v>571200</v>
       </c>
       <c r="E62" s="3">
-        <v>1465000</v>
+        <v>759700</v>
       </c>
       <c r="F62" s="3">
-        <v>1677300</v>
+        <v>779300</v>
       </c>
       <c r="G62" s="3">
-        <v>1651000</v>
+        <v>1038900</v>
       </c>
       <c r="H62" s="3">
-        <v>1678400</v>
+        <v>997600</v>
       </c>
       <c r="I62" s="3">
-        <v>1684400</v>
+        <v>1072500</v>
       </c>
       <c r="J62" s="3">
+        <v>1076600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1889000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1891200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1999600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2085000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2280300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3919000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3702000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3292500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3439900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3368000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3426800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3363300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3730200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3901800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3713300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3819900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5801,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5902,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6003,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>13254100</v>
+        <v>12875900</v>
       </c>
       <c r="E66" s="3">
-        <v>13978800</v>
+        <v>12238800</v>
       </c>
       <c r="F66" s="3">
-        <v>14047600</v>
+        <v>13277000</v>
       </c>
       <c r="G66" s="3">
-        <v>13747200</v>
+        <v>13796600</v>
       </c>
       <c r="H66" s="3">
-        <v>14040300</v>
+        <v>13005600</v>
       </c>
       <c r="I66" s="3">
-        <v>14262500</v>
+        <v>13599700</v>
       </c>
       <c r="J66" s="3">
+        <v>13976100</v>
+      </c>
+      <c r="K66" s="3">
         <v>14992500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13887800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14660500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14683200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14498900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19056700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18415600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17659600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18122300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17605800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18193000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18168300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18914300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18899300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17654900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19205500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6141,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6242,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6343,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6444,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6545,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>17122800</v>
+        <v>17451400</v>
       </c>
       <c r="E72" s="3">
-        <v>17045900</v>
+        <v>16567800</v>
       </c>
       <c r="F72" s="3">
-        <v>17100000</v>
+        <v>16911400</v>
       </c>
       <c r="G72" s="3">
-        <v>17121500</v>
+        <v>17582300</v>
       </c>
       <c r="H72" s="3">
-        <v>17034100</v>
+        <v>16958200</v>
       </c>
       <c r="I72" s="3">
-        <v>16912300</v>
+        <v>17244300</v>
       </c>
       <c r="J72" s="3">
+        <v>17294500</v>
+      </c>
+      <c r="K72" s="3">
         <v>16847800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16393600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17006300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17168800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16828000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16730300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16259600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16928100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17236400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17398700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18050600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18362200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18894400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19871700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19470600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19870500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6747,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6848,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6949,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>8834700</v>
+        <v>8940700</v>
       </c>
       <c r="E76" s="3">
-        <v>8743600</v>
+        <v>8548300</v>
       </c>
       <c r="F76" s="3">
-        <v>8541800</v>
+        <v>8674600</v>
       </c>
       <c r="G76" s="3">
-        <v>8662200</v>
+        <v>8782700</v>
       </c>
       <c r="H76" s="3">
-        <v>8688900</v>
+        <v>8579600</v>
       </c>
       <c r="I76" s="3">
-        <v>8642300</v>
+        <v>8796100</v>
       </c>
       <c r="J76" s="3">
+        <v>8837600</v>
+      </c>
+      <c r="K76" s="3">
         <v>8488700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8398900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8632300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8859300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8684500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19701400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19127600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17683900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17807900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18321200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19032300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19062300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19507700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20246300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19824800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20239800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7151,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>249300</v>
+        <v>204700</v>
       </c>
       <c r="E81" s="3">
-        <v>261000</v>
+        <v>244900</v>
       </c>
       <c r="F81" s="3">
-        <v>128300</v>
+        <v>262700</v>
       </c>
       <c r="G81" s="3">
-        <v>219700</v>
+        <v>135700</v>
       </c>
       <c r="H81" s="3">
-        <v>244100</v>
+        <v>221300</v>
       </c>
       <c r="I81" s="3">
-        <v>215100</v>
+        <v>249900</v>
       </c>
       <c r="J81" s="3">
+        <v>222800</v>
+      </c>
+      <c r="K81" s="3">
         <v>156700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>168600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>190100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>159800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>221700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>585400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>571600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>410400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1117200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>292100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>343200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>256100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>240900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>228500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>341700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>404200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>832400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>762900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>583800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>511800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>700300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>542500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>530200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>432400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7395,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>688700</v>
+        <v>689300</v>
       </c>
       <c r="E83" s="3">
-        <v>698600</v>
+        <v>719900</v>
       </c>
       <c r="F83" s="3">
-        <v>705300</v>
+        <v>716600</v>
       </c>
       <c r="G83" s="3">
-        <v>695900</v>
+        <v>575500</v>
       </c>
       <c r="H83" s="3">
-        <v>711100</v>
+        <v>199500</v>
       </c>
       <c r="I83" s="3">
-        <v>700800</v>
+        <v>726100</v>
       </c>
       <c r="J83" s="3">
+        <v>779000</v>
+      </c>
+      <c r="K83" s="3">
         <v>701100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>681500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>715000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>728600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>744200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>789300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>777100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>764800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3127500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>796700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>835300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>856200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>874600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>892700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>855000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>848400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>711200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>653900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>677500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>692100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>732200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>718700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>707600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>715200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>722200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7597,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7698,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7799,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7900,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8001,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>952600</v>
+        <v>1086900</v>
       </c>
       <c r="E89" s="3">
-        <v>839000</v>
+        <v>921700</v>
       </c>
       <c r="F89" s="3">
-        <v>910400</v>
+        <v>832400</v>
       </c>
       <c r="G89" s="3">
-        <v>1001700</v>
+        <v>936100</v>
       </c>
       <c r="H89" s="3">
-        <v>1029700</v>
+        <v>992100</v>
       </c>
       <c r="I89" s="3">
-        <v>768600</v>
+        <v>1042400</v>
       </c>
       <c r="J89" s="3">
+        <v>786000</v>
+      </c>
+      <c r="K89" s="3">
         <v>1027400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>768900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1095600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>996900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1011600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1053900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1039700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>659400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4366400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1263500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1549000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>816800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>975700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>746100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>907500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>881500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>382000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>829300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>828600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>969400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>776500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>837300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8139,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-527297000</v>
+        <v>-375000</v>
       </c>
       <c r="E91" s="3">
-        <v>-590523000</v>
+        <v>-375900</v>
       </c>
       <c r="F91" s="3">
-        <v>-985897000</v>
+        <v>-429000</v>
       </c>
       <c r="G91" s="3">
-        <v>-676260000</v>
+        <v>-707800</v>
       </c>
       <c r="H91" s="3">
-        <v>-634496000</v>
+        <v>-488500</v>
       </c>
       <c r="I91" s="3">
-        <v>-783990000</v>
+        <v>-472100</v>
       </c>
       <c r="J91" s="3">
+        <v>-595700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-415900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-558800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-742400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-526800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-878200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-969100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-796300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-571500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-629400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8341,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8442,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-267900</v>
+        <v>-425200</v>
       </c>
       <c r="E94" s="3">
-        <v>-482700</v>
+        <v>-259200</v>
       </c>
       <c r="F94" s="3">
-        <v>-572500</v>
+        <v>-478900</v>
       </c>
       <c r="G94" s="3">
-        <v>-680500</v>
+        <v>-588700</v>
       </c>
       <c r="H94" s="3">
-        <v>-674300</v>
+        <v>-674000</v>
       </c>
       <c r="I94" s="3">
-        <v>-587300</v>
+        <v>-682700</v>
       </c>
       <c r="J94" s="3">
+        <v>-600600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-335700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-566700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-595300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-616500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-583300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-874100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-764500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-387600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-907100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-515500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-404700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8580,62 +8818,63 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-134700</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G96" s="3">
-        <v>-136000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>142400</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K96" s="3">
         <v>-135700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-132100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>-133400</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-556600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-56300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8643,11 +8882,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-64000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8655,11 +8894,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8667,11 +8906,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -8679,10 +8918,13 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8782,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8883,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8984,307 +9232,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-796800</v>
+        <v>-357300</v>
       </c>
       <c r="E100" s="3">
-        <v>-162800</v>
+        <v>-771000</v>
       </c>
       <c r="F100" s="3">
-        <v>-115500</v>
+        <v>-161500</v>
       </c>
       <c r="G100" s="3">
-        <v>-618200</v>
+        <v>-118700</v>
       </c>
       <c r="H100" s="3">
-        <v>-459200</v>
+        <v>-612300</v>
       </c>
       <c r="I100" s="3">
-        <v>-322900</v>
+        <v>-464800</v>
       </c>
       <c r="J100" s="3">
+        <v>-330200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-164700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-182000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-309700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-364600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-892500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-220900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-43900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-377800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-56600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-725800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>83100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>324500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>120000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>19100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>696800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>30200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>19200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="E101" s="3">
-        <v>4500</v>
+        <v>300</v>
       </c>
       <c r="F101" s="3">
-        <v>-4400</v>
+        <v>1900</v>
       </c>
       <c r="G101" s="3">
-        <v>1700</v>
+        <v>-9300</v>
       </c>
       <c r="H101" s="3">
-        <v>300</v>
+        <v>7500</v>
       </c>
       <c r="I101" s="3">
-        <v>1900</v>
+        <v>5700</v>
       </c>
       <c r="J101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-8800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-109100</v>
+        <v>299100</v>
       </c>
       <c r="E102" s="3">
-        <v>198000</v>
+        <v>-105600</v>
       </c>
       <c r="F102" s="3">
-        <v>218000</v>
+        <v>196400</v>
       </c>
       <c r="G102" s="3">
-        <v>-295300</v>
+        <v>224200</v>
       </c>
       <c r="H102" s="3">
-        <v>-103500</v>
+        <v>-292500</v>
       </c>
       <c r="I102" s="3">
-        <v>-139800</v>
+        <v>-104700</v>
       </c>
       <c r="J102" s="3">
+        <v>-142900</v>
+      </c>
+      <c r="K102" s="3">
         <v>518100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>196300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-464100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-35800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>231000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-102400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>74100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>297900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>307100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-128600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-144100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-532800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>500800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>783600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>359500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>184400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>63700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>581400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,466 +656,478 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3054000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3450600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3209300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3329500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3491200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3270500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3269600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3353300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3295800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3170700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3260300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3293500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3221500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3161300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3093900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3043700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12065800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3643200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3728700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3738500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3746400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4059500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3904600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1054000</v>
+      </c>
+      <c r="E9" s="3">
         <v>355700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>291500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>323200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>871300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>303400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>291300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>317000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>120500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>131400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>140800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>145800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>141200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>138100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>137400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>143500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>578000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>155100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>167900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>163800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>162600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>163700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>165200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>172300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>136400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>171900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>183800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>180600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>190800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>197200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>187500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>199000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>153400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3094900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2917800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3006200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2619900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2967100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2978300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3036200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3175400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3039300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3119500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3147600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3080300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3023100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2956500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2900200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11487800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3488100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3560800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3574700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3583800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3895800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3739400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,112 +1164,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E12" s="3">
         <v>78000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>70700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>66200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>90600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>67200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>66700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>56400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>67100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>61800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>60100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>75800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>60300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>62000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>61800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>264900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>80700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>85000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>92700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>86500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>83300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>84700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>90800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>88900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>76200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>82500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>75100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>90300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>90800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>83500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>85200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>82100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1360,216 +1376,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E14" s="3">
         <v>72900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-14500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-47900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-3700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>150500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>10300</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>54900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>214000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>52300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>536700</v>
+      </c>
+      <c r="E15" s="3">
         <v>675500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>641400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>667600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>698800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>664700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>693700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>690400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>676400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>657900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>689600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>701400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>691800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>696100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>684800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>672700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2748500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>775500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>807500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>827200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>912300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>856100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>818700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>810900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>676100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>621700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>644900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>660200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>696900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>684300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>674200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>685500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>695000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2881900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3045100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2819900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2959600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3262200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2902100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2918400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2975200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3117500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2831100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2911000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2960500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3055700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2866500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2797100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2766800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11279900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3367600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3449200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3485400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3664800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3790900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3622600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E18" s="3">
         <v>405600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>389400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>369900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>229100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>368300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>351200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>378100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>178400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>339600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>349300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>332900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>165800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>294800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>296800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>276900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>785900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>275700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>279500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>253100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>81700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>268600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>282000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>293500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>246000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>289300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>272600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>220900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>345000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>368800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>367500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>266100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1849,528 +1881,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-391800</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-19900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-24200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>109100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>188000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>133700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>265700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>320200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>140700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>130200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>116400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>225300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>607100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>866100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>748000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>552300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>662700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>601900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>355900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>351300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>307600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1100500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1080800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1039400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1032300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>929900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1022100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1040400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1048100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>886300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1001200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1078700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1037300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1019100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1111900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1261900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1175500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4023100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1338100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1435000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1250100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>956400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1291600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1253400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>272900</v>
+      </c>
+      <c r="E22" s="3">
         <v>74200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>71900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>78200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>79700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>71400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>55200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>57700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>56900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>53600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>51600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>216700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>143600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>155100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>84400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>89700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>87900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>87600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>93100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>75000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>57500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>60400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>63100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>68300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>63400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>66100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>67000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>323600</v>
+      </c>
+      <c r="E23" s="3">
         <v>277700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>347000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>327900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>167600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>297200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>341500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>322800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>108000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>264500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>306100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>251800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>221200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>269300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>433200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>360000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>678900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>397800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>444700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>309400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>311000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>310800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>425700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>507400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>977000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>761900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>815400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>883600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>658600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>651800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>507700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E24" s="3">
         <v>64400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>92900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>58600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>23100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>77500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>90800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-59800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>85200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>109900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>82100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>62700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>71700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>102700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>96700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>165900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>96100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>94500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>52400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>66700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>82900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>85700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>108800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>204200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>208900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>179400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>234000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>185800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>112600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>126700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>80500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2473,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>267200</v>
+      </c>
+      <c r="E26" s="3">
         <v>213300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>254100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>269300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>144500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>229000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>264000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>232000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>167800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>179300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>196200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>169700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>158600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>197600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>330500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>263300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>513000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>301700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>350200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>257000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-39400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>244200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>228000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>340000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>398600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>850400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>768000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>582400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>581400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>697800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>546000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>525100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>427200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>183500</v>
+      </c>
+      <c r="E27" s="3">
         <v>201000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>241300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>259000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>131900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>217600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>247100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>156700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>168600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>190100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>159800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>141700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>189900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>313600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>253300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>475400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>292100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>343200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>256100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-27200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>240900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>228500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>341700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>404200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>832400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>762900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>583800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>511800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>542500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>530200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>432400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2811,8 +2871,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>91</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>91</v>
@@ -2823,29 +2883,29 @@
       <c r="N29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P29" s="3">
         <v>80000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>395400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>257900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>157000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>641800</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2889,8 +2949,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3097,216 +3163,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>391800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>19900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>24200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-109100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-188000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-133700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-265700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-320200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-140700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-130200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-116400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E33" s="3">
         <v>204700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>244900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>262700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>135700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>221300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>249900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>222800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>156700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>168600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>190100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>159800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>221700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>585400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>571600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>410400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1117200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>292100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>343200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>256100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-27200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>240900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>228500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>341700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>404200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>832400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>762900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>583800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>511800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>700300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>542500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>530200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>432400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E35" s="3">
         <v>204700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>244900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>262700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>135700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>221300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>249900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>222800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>156700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>168600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>190100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>159800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>221700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>585400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>571600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>410400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1117200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>292100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>343200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>256100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-27200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>240900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>228500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>341700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>404200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>832400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>762900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>583800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>511800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>700300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>542500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>530200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>432400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3698,944 +3783,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1369900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1497100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1141900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1279100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1122000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>864900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1182900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1411700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>869800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>876200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>688900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>654500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1118700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1154500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>911200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1027200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1450500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1212500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>938900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1080200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1147800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1277400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>246300</v>
+      </c>
+      <c r="E42" s="3">
         <v>206100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>159600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>263900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>173100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>320100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>269700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>170500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>118300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>472700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>523300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>378500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>325600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1264900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1186400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1078700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1109500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>840400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>795000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>903200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>766900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>866400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>728100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>733100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>975400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>318100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>452600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>540900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>590800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>626300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>647200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>612800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>437300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1701900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1974800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1836300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1897100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1920900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2006600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1790200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1884400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1960600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2052200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2083500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2117900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1957700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2772400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2584400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2644400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2528400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2663000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2649400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2902000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2886300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3122000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2860700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E44" s="3">
         <v>169300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>154700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>156500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>138700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>139200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>126600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>153500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>124800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>143500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>139300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>172000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>153500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>148700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>158800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>163900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>128600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>166300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>165500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>174800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>138400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>178500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>197000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>239900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>242000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>208700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>217800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>213800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>239700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>219000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>231900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>223700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>233900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1557800</v>
+      </c>
+      <c r="E45" s="3">
         <v>255400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>250600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>208800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1668800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1521300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>216000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>336400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1799000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1804400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1744200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1682200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1673200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1685000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1771500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1762000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1787600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1834500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1869300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1904400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2003300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1881800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1612400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>305100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>341700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>228600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>212400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>289400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5061200</v>
+      </c>
+      <c r="E46" s="3">
         <v>5608100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4978700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5284500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5078500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4913600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5087400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5373300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5414400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5342600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5366500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5039500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4764500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6989700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6855700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6560200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6581300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6954700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6691700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6823200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6875200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7196700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6675700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2906200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2705000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2687900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2809100</v>
       </c>
-      <c r="G47" s="3">
-        <v>2817400</v>
-      </c>
       <c r="H47" s="3">
+        <v>2771800</v>
+      </c>
+      <c r="I47" s="3">
         <v>2678500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2679100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2633400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2823200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2756600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2913200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3235400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3194500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15039700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13968200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12464800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12336800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12316200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12493000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12472300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12502800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12994600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12402900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8547100</v>
+      </c>
+      <c r="E48" s="3">
         <v>9225600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8947900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9391300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10037800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9401300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9813700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9833400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10010700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9104400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9648000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9698000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9670700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9855200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9932800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9546300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10032800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9386500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10160800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10069700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10993400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10310700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9942300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2886700</v>
+      </c>
+      <c r="E49" s="3">
         <v>3367400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3337100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3560700</v>
       </c>
-      <c r="G49" s="3">
-        <v>3806500</v>
-      </c>
       <c r="H49" s="3">
+        <v>3795100</v>
+      </c>
+      <c r="I49" s="3">
         <v>3665700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3867500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4016700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4049900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3968600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4254900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4434400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4456700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5635200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5629100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5622000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5845300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6083200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6545900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6426000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6643300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7011600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7117600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4842,112 +4958,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>488600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1485400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1376800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1465900</v>
       </c>
-      <c r="G52" s="3">
-        <v>624900</v>
-      </c>
       <c r="H52" s="3">
+        <v>670500</v>
+      </c>
+      <c r="I52" s="3">
         <v>716100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1526000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1530700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1182900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1114600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1110200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1135100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1097000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1238200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1157300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1150100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1134000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1186500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1333900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1439300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1407300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1632000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1341300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>707400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>521500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>530700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>521800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>693000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5050,112 +5172,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>20656800</v>
+      </c>
+      <c r="E54" s="3">
         <v>22439900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21372800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22543100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23226500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22195800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23009700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23422300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23481200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22286700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23292800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23542500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23183500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38758100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37543200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35343500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35930200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35927000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37225300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37230600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38422000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39145600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>37479700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5230,632 +5359,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E57" s="3">
         <v>126000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>107900</v>
       </c>
       <c r="G57" s="3">
         <v>107900</v>
       </c>
       <c r="H57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="I57" s="3">
         <v>94800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>77200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>106600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>108600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>86000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>142900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>253700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>228200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>249000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>279700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>285700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>327300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>372600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>405200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>332700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>283700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>320300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>217500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>221100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>204600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>309500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>226300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>219400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>237100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>362200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1970900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2527000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2131100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1996200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1538200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1232100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1747900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2127500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1872800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2070200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1920500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1409000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1344700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1420900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1244900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1236100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1056900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1029100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>963600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1234000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1198200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1223800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1310400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>894000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>856100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>944800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>802000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3156900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2406500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1952900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2398900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2637100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2406000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2169000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2298100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4095200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3244300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3751200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3814800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3732700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4610800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4393200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4508600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4796900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4594700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4758600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4813200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5103100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4927800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4464800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>6244200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6188000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5135100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5400800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5393400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4848000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5056000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5524300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6034900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5423100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5757700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5340200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5220300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6285400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5866300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5993700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6133500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5909400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6022700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6374500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6673900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6556800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6107900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5316200</v>
+      </c>
+      <c r="E61" s="3">
         <v>5490100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5711200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6422800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6678600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6522300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6844600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6729300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6440900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5995600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6304100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6669800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6431400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8165900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8169800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7876200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8059700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7920900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8322200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8551200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8623500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8522600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7920200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>470600</v>
+      </c>
+      <c r="E62" s="3">
         <v>571200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>759700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>779300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1038900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>997600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1072500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1076600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1889000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1891200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1999600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2085000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2280300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3919000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3702000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3292500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3439900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3368000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3426800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3363300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3730200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3901800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3713300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6166,112 +6320,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>12650300</v>
+      </c>
+      <c r="E66" s="3">
         <v>12875900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12238800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13277000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13796600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13005600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13599700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13976100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14992500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13887800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14660500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14683200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14498900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19056700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18415600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17659600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18122300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17605800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18193000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18168300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18914300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18899300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17654900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6724,112 +6894,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>15553300</v>
+      </c>
+      <c r="E72" s="3">
         <v>17451400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16567800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16911400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17582300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16958200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17244300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17294500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16847800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16393600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17006300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17168800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16828000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16730300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16259600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16928100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17236400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17398700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18050600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18362200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18894400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19871700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19470600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7140,112 +7322,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>7919200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8940700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8548300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8674600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8782700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8579600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8796100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8837600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8488700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8398900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8632300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8859300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8684500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19701400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19127600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17683900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17807900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18321200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19032300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19062300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19507700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20246300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19824800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7348,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E81" s="3">
         <v>204700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>244900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>262700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>135700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>221300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>249900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>222800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>156700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>168600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>190100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>159800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>221700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>585400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>571600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>410400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1117200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>292100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>343200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>256100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-27200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>240900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>228500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>341700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>404200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>832400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>762900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>583800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>511800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>700300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>542500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>530200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>432400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7599,112 +7796,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>560400</v>
+      </c>
+      <c r="E83" s="3">
         <v>689300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>719900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>716600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>575500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>199500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>726100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>779000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>701100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>681500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>715000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>728600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>744200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>789300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>777100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>764800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3127500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>796700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>835300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>856200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>874600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>892700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>855000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>848400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>711200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>653900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>677500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>692100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>732200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>718700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>707600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>715200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>722200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>860300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1086900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>921700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>832400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>936100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>992100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1042400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>786000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1027400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>768900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1095600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>996900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1011600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1053900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1039700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>659400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4366400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1263500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1549000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>816800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>975700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>746100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>907500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>881500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>382000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>829300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>828600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>969400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>776500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>837300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8365,112 +8584,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-609400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-375000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-375900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-429000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-707800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-488500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-472100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-595700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-415900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-558800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-742400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-526800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-878200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-969100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-796300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-571500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8677,112 +8903,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-780200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-425200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-259200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-478900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-588700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-674000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-682700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-335700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-566700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-595300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-616500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-583300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-874100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-764500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-387600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-907100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-515500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-404700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8819,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8833,11 +9066,11 @@
       <c r="F96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G96" s="3">
-        <v>142400</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="H96" s="3">
+        <v>103400</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>91</v>
@@ -8845,39 +9078,39 @@
       <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L96" s="3">
         <v>-135700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-132100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>-133400</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-556600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8885,11 +9118,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-64000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8897,11 +9130,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8909,11 +9142,11 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -8921,10 +9154,13 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9235,316 +9477,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-357300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-771000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-161500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-118700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-612300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-464800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-330200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-164700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-182000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-309700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-364600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-892500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-220900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-43900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-377800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-56600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-725800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>83100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>324500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>120000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>19100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>696800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>30200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>19200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E101" s="3">
         <v>1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>6100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E102" s="3">
         <v>299100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>196400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>224200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-292500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-104700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-142900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>518100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>196300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-464100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>231000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-102400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>74100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>297900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>307100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-128600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-144100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-532800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>500800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>783600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>359500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>184400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>63700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>581400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,478 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3054000</v>
+        <v>3024200</v>
       </c>
       <c r="E8" s="3">
+        <v>3077700</v>
+      </c>
+      <c r="F8" s="3">
         <v>3450600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3209300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3329500</v>
       </c>
-      <c r="H8" s="3">
-        <v>3491200</v>
-      </c>
       <c r="I8" s="3">
+        <v>3513200</v>
+      </c>
+      <c r="J8" s="3">
         <v>3270500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3269600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3353300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3295800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3170700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3260300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3293500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3221500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3161300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3093900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3043700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12065800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3643200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3728700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3738500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3746400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4059500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3904600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>836200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1054000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>355700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>291500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>323200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>871300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>303400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>291300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>317000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>120500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>131400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>140800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>145800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>141200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>138100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>137400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>143500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>578000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>155100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>167900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>163800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>162600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>163700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>165200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>172300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>136400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>171900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>183800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>180600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>190800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>197200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>187500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>199000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>153400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2000000</v>
+        <v>2188000</v>
       </c>
       <c r="E10" s="3">
+        <v>2023700</v>
+      </c>
+      <c r="F10" s="3">
         <v>3094900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2917800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3006200</v>
       </c>
-      <c r="H10" s="3">
-        <v>2619900</v>
-      </c>
       <c r="I10" s="3">
+        <v>2641900</v>
+      </c>
+      <c r="J10" s="3">
         <v>2967100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2978300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3036200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3175400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3039300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3119500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3147600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3080300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3023100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2956500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2900200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11487800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3488100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3560800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3574700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3583800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3895800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3739400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1165,115 +1178,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>255900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>78000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>70700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>66200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>90600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>67200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>66700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>56400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>61800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>67400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>60100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>75800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>60300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>62000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>61800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>264900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>80700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>85000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>92700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>86500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>83300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>84700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>90800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>88900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>76200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>82500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>75100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>90300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>90800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>83500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>85200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>82100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1379,222 +1396,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>50700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>72900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-14500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-47900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>150500</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>10300</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>54900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>214000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>52300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>622400</v>
+      </c>
+      <c r="E15" s="3">
         <v>536700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>675500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>641400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>667600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>698800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>664700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>693700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>690400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>676400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>657900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>689600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>701400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>691800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>696100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>684800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>672700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2748500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>775500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>807500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>827200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>912300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>856100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>818700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>810900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>676100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>621700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>644900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>660200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>696900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>684300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>674200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>685500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>695000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,222 +1655,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2881900</v>
+        <v>2639000</v>
       </c>
       <c r="E17" s="3">
+        <v>2944600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3045100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2819900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2959600</v>
       </c>
-      <c r="H17" s="3">
-        <v>3262200</v>
-      </c>
       <c r="I17" s="3">
+        <v>3283400</v>
+      </c>
+      <c r="J17" s="3">
         <v>2902100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2918400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2975200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3117500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2831100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2911000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2960500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3055700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2866500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2797100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2766800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11279900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3367600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3449200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3485400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3664800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3790900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3622600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>172100</v>
+        <v>385200</v>
       </c>
       <c r="E18" s="3">
+        <v>133000</v>
+      </c>
+      <c r="F18" s="3">
         <v>405600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>389400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>369900</v>
       </c>
-      <c r="H18" s="3">
-        <v>229100</v>
-      </c>
       <c r="I18" s="3">
+        <v>229800</v>
+      </c>
+      <c r="J18" s="3">
         <v>368300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>351200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>378100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>178400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>339600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>349300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>332900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>165800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>294800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>296800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>276900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>785900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>275700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>279500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>253100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>81700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>268600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>282000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>293500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>246000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>289300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>272600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>220900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>345000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>368800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>367500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>266100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1882,543 +1915,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-391800</v>
+        <v>40400</v>
       </c>
       <c r="E20" s="3">
+        <v>-430800</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-2000</v>
-      </c>
       <c r="I20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J20" s="3">
         <v>10900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>20300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-19900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-24200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>109100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>188000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>133700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>109700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>265700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>320200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>140700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>130200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>116400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>225300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>607100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>866100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>748000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>552300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>662700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>601900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>355900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>351300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>307600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>967200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1080800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1039400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1032300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>929900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1022100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1040400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1048100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>886300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1001200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1078700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1037300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1019100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1111900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1261900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1175500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4023100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1338100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1435000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1250100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>956400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1291600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1253400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="3">
         <v>272900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>74200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>71900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>78200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>79700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>55200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>57700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>56900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>53300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>216700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>143600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>155100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>84400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>89700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>87900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>87600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>93100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>75000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>57500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>60400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>63100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>68300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>63400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>66100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>66000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>344800</v>
+      </c>
+      <c r="E23" s="3">
         <v>323600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>277700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>347000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>327900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>167600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>297200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>341500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>322800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>108000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>264500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>306100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>251800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>221200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>269300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>433200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>360000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>678900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>397800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>444700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>309400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>311000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>310800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>425700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>507400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>977000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>761900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>815400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>883600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>658600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>651800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>507700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E24" s="3">
         <v>56400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>64400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>92900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>58600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>23100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>68200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>90800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-59800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>85200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>109900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>82100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>62700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>71700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>102700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>96700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>165900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>96100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>94500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>52400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>31400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>66700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>82900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>85700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>108800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>204200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>208900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>179400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>234000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>185800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>112600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>126700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>80500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2524,222 +2573,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E26" s="3">
         <v>267200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>213300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>254100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>269300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>144500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>229000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>264000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>232000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>167800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>179300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>196200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>169700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>158600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>197600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>330500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>263300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>513000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>301700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>350200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>257000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>244200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>228000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>340000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>398600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>850400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>768000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>582400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>581400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>697800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>546000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>525100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>427200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E27" s="3">
         <v>183500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>201000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>241300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>259000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>131900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>217600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>247100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>220000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>156700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>168600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>190100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>159800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>141700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>189900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>313600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>253300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>475400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>292100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>343200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>256100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>240900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>228500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>341700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>404200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>832400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>762900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>583800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>511800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>542500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>530200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>432400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2874,8 +2935,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>91</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>91</v>
@@ -2886,29 +2947,29 @@
       <c r="O29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q29" s="3">
         <v>80000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>395400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>257900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>157000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>641800</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2952,8 +3013,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3166,222 +3233,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>391800</v>
+        <v>-40400</v>
       </c>
       <c r="E32" s="3">
+        <v>430800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5100</v>
       </c>
-      <c r="H32" s="3">
-        <v>2000</v>
-      </c>
       <c r="I32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-10900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-20300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>19900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>24200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-109100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-188000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-133700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-109700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-265700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-320200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-140700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-130200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-116400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E33" s="3">
         <v>196900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>204700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>244900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>262700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>135700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>221300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>249900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>222800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>156700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>168600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>190100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>159800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>221700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>585400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>571600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>410400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1117200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>292100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>343200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>256100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>240900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>228500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>341700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>404200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>832400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>762900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>583800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>511800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>700300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>542500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>530200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>432400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3487,227 +3563,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E35" s="3">
         <v>196900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>204700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>244900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>262700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>135700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>221300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>249900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>222800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>156700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>168600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>190100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>159800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>221700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>585400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>571600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>410400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1117200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>292100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>343200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>256100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>240900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>228500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>341700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>404200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>832400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>762900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>583800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>511800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>700300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>542500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>530200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>432400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3784,971 +3870,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1705500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1369900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1497100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1141900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1279100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1122000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>864900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1182900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1411700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>869800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>876200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>688900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>654500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1118700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1154500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>911200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1027200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1450500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1212500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>938900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1080200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1147800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1277400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>246300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>206100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>159600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>263900</v>
       </c>
-      <c r="H42" s="3">
-        <v>173100</v>
-      </c>
       <c r="I42" s="3">
+        <v>166100</v>
+      </c>
+      <c r="J42" s="3">
         <v>320100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>269700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>170500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>118300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>472700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>523300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>378500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>325600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1264900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1186400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1078700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1109500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>840400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>795000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>903200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>766900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>866400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>728100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>733100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>975400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>318100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>452600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>540900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>590800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>626300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>647200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>612800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>437300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1680700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1701900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1974800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1836300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1897100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1920900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2006600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1790200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1884400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1960600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2052200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2083500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2117900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1957700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2772400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2584400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2644400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2528400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2663000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2649400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2902000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2886300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3122000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2860700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="3">
         <v>142000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>169300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>154700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>156500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>138700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>139200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>126600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>153500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>124800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>143500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>139300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>172000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>153500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>148700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>158800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>163900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>128600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>166300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>165500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>174800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>138400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>178500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>197000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>239900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>242000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>208700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>217800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>213800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>239700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>219000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>231900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>223700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>233900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1825700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1557800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>255400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>250600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>208800</v>
       </c>
-      <c r="H45" s="3">
-        <v>1668800</v>
-      </c>
       <c r="I45" s="3">
+        <v>1675700</v>
+      </c>
+      <c r="J45" s="3">
         <v>1521300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>216000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>336400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1799000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1804400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1744200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1682200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1673200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1685000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1771500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1762000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1787600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1834500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1869300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1904400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2003300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1881800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1612400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>305100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>341700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>228600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>212400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>289400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5211900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5061200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5608100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4978700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5284500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5078500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4913600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5087400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5373300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5414400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5342600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5366500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5039500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4764500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6989700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6855700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6560200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6581300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6954700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6691700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6823200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6875200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7196700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6675700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2839100</v>
+      </c>
+      <c r="E47" s="3">
         <v>2906200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2705000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2687900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2809100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2771800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2678500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2679100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2633400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2823200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2756600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2913200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3235400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3194500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15039700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13968200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12464800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12336800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12316200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12493000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12472300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12502800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12994600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12402900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>10977500</v>
+      </c>
+      <c r="E48" s="3">
         <v>8547100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9225600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8947900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9391300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10037800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9401300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9813700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9833400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10010700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9104400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9648000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9698000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9670700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9855200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9932800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9546300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10032800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9386500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10160800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10069700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10993400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10310700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9942300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>2886700</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>2888700</v>
+      </c>
+      <c r="F49" s="3">
         <v>3367400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3337100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3560700</v>
       </c>
-      <c r="H49" s="3">
-        <v>3795100</v>
-      </c>
       <c r="I49" s="3">
+        <v>3806500</v>
+      </c>
+      <c r="J49" s="3">
         <v>3665700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3867500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4016700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4049900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3968600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4254900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4434400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4456700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5635200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5629100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5622000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5845300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6083200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6545900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6426000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6643300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7011600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7117600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4961,115 +5078,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1288700</v>
+      </c>
+      <c r="E52" s="3">
         <v>488600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1485400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1376800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1465900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>670500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>716100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1526000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1530700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1182900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1114600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1110200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1135100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1097000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1238200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1157300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1150100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1134000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1186500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1333900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1439300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1407300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1632000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1341300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>707400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>521500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>530700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>521800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>693000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5175,115 +5298,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>20317200</v>
+      </c>
+      <c r="E54" s="3">
         <v>20656800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22439900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21372800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22543100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23226500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22195800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23009700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23422300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23481200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22286700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23292800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23542500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23183500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38758100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37543200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35343500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35930200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35927000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37225300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37230600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>38422000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39145600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37479700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5360,650 +5490,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1808200</v>
+      </c>
+      <c r="E57" s="3">
         <v>85600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>126000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>107900</v>
       </c>
       <c r="H57" s="3">
         <v>107900</v>
       </c>
       <c r="I57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="J57" s="3">
         <v>94800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>77200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>106600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>66900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>86000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>116300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>142900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>253700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>228200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>249000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>279700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>285700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>300500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>327300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>372600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>405200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>332700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>283700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>320300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>217500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>221100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>204600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>309500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>226300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>219400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>237100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>362200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1970900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2527000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2131100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1996200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1538200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1232100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1747900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2127500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1872800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2070200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1920500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1409000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1344700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1420900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1244900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1236100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1056900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1029100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>963600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1234000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1198200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1223800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>894000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>856100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>944800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>802000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3916500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3156900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2406500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1952900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2398900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2637100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2406000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2169000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2298100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4095200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3244300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3751200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3814800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3732700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4610800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4393200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4508600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4796900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4594700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4758600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4813200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5103100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4927800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4464800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>5928400</v>
+      </c>
+      <c r="E60" s="3">
         <v>6244200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6188000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5135100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5400800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5393400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4848000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5056000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5524300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6034900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5423100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5757700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5340200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5220300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6285400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5866300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5993700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6133500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5909400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6022700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6374500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6673900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6556800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6107900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4482600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5316200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5490100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5711200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6422800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6678600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6522300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6844600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6729300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6440900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5995600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6304100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6669800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6431400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8165900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8169800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7876200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8059700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7920900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8322200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8551200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8623500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8522600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7920200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1165600</v>
+      </c>
+      <c r="E62" s="3">
         <v>470600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>571200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>759700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>779300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1038900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>997600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1072500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1076600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1889000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1891200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1999600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2085000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2280300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3919000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3702000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3292500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3439900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3368000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3426800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3363300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3730200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3901800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3713300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6323,115 +6478,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>12208300</v>
+      </c>
+      <c r="E66" s="3">
         <v>12650300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12875900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12238800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13277000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13796600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13005600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13599700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13976100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14992500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13887800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14660500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14683200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14498900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19056700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18415600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17659600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18122300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17605800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18193000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18168300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18914300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18899300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17654900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6897,115 +7068,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>15686300</v>
+      </c>
+      <c r="E72" s="3">
         <v>15553300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17451400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16567800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16911400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17582300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16958200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17244300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17294500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16847800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16393600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17006300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17168800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16828000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16730300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16259600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16928100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17236400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17398700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18050600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18362200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18894400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19871700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19470600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7325,115 +7508,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>8027000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7919200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8940700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8548300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8674600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8782700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8579600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8796100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8837600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8488700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8398900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8632300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8859300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8684500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19701400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19127600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17683900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17807900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18321200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19032300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19062300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19507700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20246300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19824800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7539,227 +7728,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E81" s="3">
         <v>196900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>204700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>244900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>262700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>135700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>221300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>249900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>222800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>156700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>168600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>190100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>159800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>221700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>585400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>571600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>410400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1117200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>292100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>343200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>256100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>240900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>228500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>341700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>404200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>832400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>762900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>583800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>511800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>700300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>542500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>530200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>432400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7797,115 +7995,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>693100</v>
+      </c>
+      <c r="E83" s="3">
         <v>560400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>689300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>719900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>716600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>575500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>199500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>726100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>779000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>701100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>681500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>715000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>728600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>744200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>789300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>777100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>764800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3127500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>796700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>835300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>856200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>874600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>892700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>855000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>848400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>711200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>653900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>677500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>692100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>732200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>718700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>707600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>715200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>722200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D89" s="3">
-        <v>860300</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" s="3">
         <v>1086900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>921700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>832400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>936100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>992100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1042400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>786000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1027400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>768900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1095600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>996900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1011600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1053900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1039700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>659400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4366400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1263500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1549000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>816800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>975700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>746100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>907500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>881500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>382000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>829300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>828600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>969400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>776500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>837300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8585,115 +8805,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3">
-        <v>-609400</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="3">
         <v>-375000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-375900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-429000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-707800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-488500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-472100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-595700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-415900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-558800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-742400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-526800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-878200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-969100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-796300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-571500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8906,115 +9133,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="3">
-        <v>-780200</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" s="3">
         <v>-425200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-259200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-478900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-588700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-674000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-682700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-335700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-566700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-595300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-616500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-583300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-874100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-764500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-387600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-907100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-515500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-404700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9052,8 +9285,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -9069,11 +9303,11 @@
       <c r="G96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="3">
         <v>103400</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>91</v>
@@ -9081,39 +9315,39 @@
       <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M96" s="3">
         <v>-135700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-132100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>-133400</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-556600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-56300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -9121,11 +9355,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -9133,11 +9367,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9145,11 +9379,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -9157,10 +9391,13 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9480,325 +9723,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F100" s="3">
         <v>-357300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-771000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-161500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-118700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-612300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-464800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-330200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-164700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-182000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-309700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-364600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-892500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-220900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-43900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-377800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-56600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-725800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>83100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>324500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>120000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>19100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>696800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>30200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>19200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>54400</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>299100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-105600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>196400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>224200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-292500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-104700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-142900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>518100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>196300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-464100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-35800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>231000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-102400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>74100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>297900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>307100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-128600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-144100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-532800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>500800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>783600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>359500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>184400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>63700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>581400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,491 +656,504 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3205900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3024200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3077700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3450600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3209300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3329500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3513200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3270500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3269600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3353300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3295800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3170700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3260300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3293500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3221500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3161300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3093900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3043700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12065800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3643200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3728700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3738500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3746400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4059500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3904600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>836200</v>
+        <v>275500</v>
       </c>
       <c r="E9" s="3">
+        <v>291000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1054000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>355700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>291500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>323200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>871300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>303400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>291300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>317000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>131400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>140800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>145800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>141200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>138100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>137400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>143500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>578000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>155100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>167900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>163800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>162600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>163700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>165200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>172300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>136400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>171900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>183800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>180600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>190800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>197200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>187500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>199000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>153400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2188000</v>
+        <v>2930400</v>
       </c>
       <c r="E10" s="3">
+        <v>2733300</v>
+      </c>
+      <c r="F10" s="3">
         <v>2023700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3094900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2917800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3006200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2641900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2967100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2978300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3036200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3175400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3039300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3119500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3147600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3080300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3023100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2956500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2900200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11487800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3488100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3560800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3574700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3583800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3895800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3739400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1179,118 +1192,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>59100</v>
       </c>
       <c r="E12" s="3">
+        <v>61100</v>
+      </c>
+      <c r="F12" s="3">
         <v>255900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>78000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>70700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>66200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>90600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>67200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>66700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>56400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>61800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>67400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>60100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>75800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>60300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>62000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>61800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>264900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>80700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>85000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>92700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>86500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>83300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>84700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>90800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>88900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>76200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>82500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>75100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>90300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>90800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>83500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>85200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>82100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1399,228 +1416,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>91</v>
+      <c r="D14" s="3">
+        <v>-1600</v>
       </c>
       <c r="E14" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F14" s="3">
         <v>50700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>72900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-14500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-47900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>150500</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>10300</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>54900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>214000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>52300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>5700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>622400</v>
+        <v>639300</v>
       </c>
       <c r="E15" s="3">
+        <v>588900</v>
+      </c>
+      <c r="F15" s="3">
         <v>536700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>675500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>641400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>667600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>698800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>664700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>693700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>690400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>676400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>657900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>689600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>701400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>691800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>696100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>684800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>672700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2748500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>775500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>807500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>827200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>912300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>856100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>818700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>810900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>676100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>621700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>644900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>660200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>696900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>684300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>674200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>685500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>695000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,228 +1682,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2639000</v>
+        <v>2957700</v>
       </c>
       <c r="E17" s="3">
+        <v>2639600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2944600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3045100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2819900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2959600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3283400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2902100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2918400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2975200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3117500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2831100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2911000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2960500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3055700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2866500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2797100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2766800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11279900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3367600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3449200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3485400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3664800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3790900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3622600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>385200</v>
+        <v>248100</v>
       </c>
       <c r="E18" s="3">
+        <v>384700</v>
+      </c>
+      <c r="F18" s="3">
         <v>133000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>405600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>389400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>369900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>229800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>368300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>351200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>378100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>178400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>339600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>349300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>332900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>165800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>294800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>296800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>276900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>785900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>275700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>279500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>253100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>81700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>268600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>282000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>293500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>246000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>289300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>272600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>220900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>345000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>368800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>367500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>266100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1916,558 +1949,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>40400</v>
+        <v>26000</v>
       </c>
       <c r="E20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-430800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-19900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>109100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>27800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>188000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>133700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>109700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>265700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>320200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>140700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>130200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>116400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>225300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>607100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>866100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>748000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>552300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>662700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>601900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>355900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>351300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>307600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>967200</v>
+        <v>861500</v>
       </c>
       <c r="E21" s="3">
+        <v>970800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1100500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1080800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1039400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1032300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>929900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1022100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1040400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1048100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>886300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1001200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1078700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1037300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1019100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1111900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1261900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1175500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4023100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1338100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1435000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1250100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>956400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1291600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1253400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>91</v>
+      <c r="D22" s="3">
+        <v>70200</v>
       </c>
       <c r="E22" s="3">
+        <v>66300</v>
+      </c>
+      <c r="F22" s="3">
         <v>272900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>74200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>78200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>79700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>72800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>71400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>77200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>55200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>57700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>56900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>53600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>53300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>216700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>143600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>155100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>84400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>89700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>87900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>87600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>93100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>75000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>57500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>60400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>63100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>68300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>63400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>66100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>67000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>66000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>344800</v>
+        <v>177600</v>
       </c>
       <c r="E23" s="3">
+        <v>344900</v>
+      </c>
+      <c r="F23" s="3">
         <v>323600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>277700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>347000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>327900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>167600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>297200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>341500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>322800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>108000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>264500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>306100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>251800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>221200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>269300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>433200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>360000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>678900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>397800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>444700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>309400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>311000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>310800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>425700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>507400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>977000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>761900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>815400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>883600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>658600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>651800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>507700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E24" s="3">
         <v>99300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>64400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>92900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>90800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-59800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>85200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>109900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>82100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>62700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>71700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>102700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>96700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>165900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>96100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>94500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>52400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>66700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>82900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>85700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>108800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>204200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>208900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>179400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>234000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>185800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>112600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>126700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>80500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E26" s="3">
         <v>245500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>267200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>213300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>254100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>269300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>144500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>229000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>264000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>232000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>167800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>179300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>196200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>169700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>158600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>197600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>330500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>263300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>513000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>301700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>350200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>257000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-39400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>244200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>228000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>340000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>398600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>850400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>768000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>582400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>581400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>697800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>546000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>525100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>427200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>247400</v>
+        <v>66200</v>
       </c>
       <c r="E27" s="3">
+        <v>247500</v>
+      </c>
+      <c r="F27" s="3">
         <v>183500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>201000</v>
       </c>
-      <c r="G27" s="3">
-        <v>241300</v>
-      </c>
       <c r="H27" s="3">
-        <v>259000</v>
+        <v>244900</v>
       </c>
       <c r="I27" s="3">
+        <v>262700</v>
+      </c>
+      <c r="J27" s="3">
         <v>131900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>217600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>247100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>220000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>156700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>168600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>190100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>159800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>189900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>313600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>253300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>475400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>292100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>343200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>256100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>240900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>228500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>341700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>404200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>832400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>762900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>583800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>511800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>700300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>530200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>432400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2938,8 +2999,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>91</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>91</v>
@@ -2950,29 +3011,29 @@
       <c r="P29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R29" s="3">
         <v>80000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>395400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>257900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>157000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>641800</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -3016,8 +3077,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3236,228 +3303,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-40400</v>
+        <v>-26000</v>
       </c>
       <c r="E32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F32" s="3">
         <v>430800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>19900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>24200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-109100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-27800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-188000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-133700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-109700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-265700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-320200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-140700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-130200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-116400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>247400</v>
+        <v>66200</v>
       </c>
       <c r="E33" s="3">
+        <v>247500</v>
+      </c>
+      <c r="F33" s="3">
         <v>196900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>204700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>244900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>262700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>135700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>221300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>249900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>222800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>156700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>168600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>190100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>159800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>221700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>585400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>571600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>410400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1117200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>292100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>343200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>256100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>240900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>228500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>341700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>404200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>832400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>762900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>583800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>511800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>700300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>530200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>432400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>247400</v>
+        <v>66200</v>
       </c>
       <c r="E35" s="3">
+        <v>247500</v>
+      </c>
+      <c r="F35" s="3">
         <v>196900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>204700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>244900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>262700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>135700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>221300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>249900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>222800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>156700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>168600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>190100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>159800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>221700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>585400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>571600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>410400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1117200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>292100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>343200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>256100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>240900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>228500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>341700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>404200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>832400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>762900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>583800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>511800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>700300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>530200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>432400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3871,998 +3957,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1705500</v>
+        <v>1738700</v>
       </c>
       <c r="E41" s="3">
+        <v>1559900</v>
+      </c>
+      <c r="F41" s="3">
         <v>1369900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1497100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1141900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1279100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1122000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>864900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1182900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1411700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>869800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>876200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>688900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>654500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1118700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1154500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>911200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1027200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1450500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1212500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>938900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1080200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1147800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1277400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>148800</v>
       </c>
       <c r="E42" s="3">
+        <v>172900</v>
+      </c>
+      <c r="F42" s="3">
         <v>246300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>206100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>159600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>263900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>166100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>320100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>269700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>170500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>118300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>472700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>523300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>378500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>325600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1264900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1186400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1078700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1109500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>840400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>795000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>903200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>766900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>866400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>728100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>733100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>975400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>318100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>452600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>540900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>590800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>626300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>647200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>612800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>437300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1680700</v>
+        <v>1883600</v>
       </c>
       <c r="E43" s="3">
+        <v>1734200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1701900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1974800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1836300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1897100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1920900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2006600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1790200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1884400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1960600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2052200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2083500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2117900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1957700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2772400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2584400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2644400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2528400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2663000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2649400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2902000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2886300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3122000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2860700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>91</v>
+      <c r="D44" s="3">
+        <v>142600</v>
       </c>
       <c r="E44" s="3">
+        <v>139800</v>
+      </c>
+      <c r="F44" s="3">
         <v>142000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>169300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>154700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>156500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>138700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>139200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>126600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>153500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>124800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>143500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>139300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>172000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>153500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>148700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>158800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>163900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>128600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>166300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>165500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>174800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>138400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>178500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>197000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>239900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>242000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>208700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>217800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>213800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>239700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>219000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>231900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>223700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>233900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1825700</v>
+        <v>180700</v>
       </c>
       <c r="E45" s="3">
+        <v>216200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1557800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>255400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>250600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>208800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1675700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1521300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>216000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>336400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1799000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1804400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1744200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1682200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1673200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1685000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1771500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1762000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1787600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1834500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1869300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1904400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2003300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1881800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1612400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>305100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>341700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>228600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>212400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>289400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5211900</v>
+        <v>5562500</v>
       </c>
       <c r="E46" s="3">
+        <v>5172400</v>
+      </c>
+      <c r="F46" s="3">
         <v>5061200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5608100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4978700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5284500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5078500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4913600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5087400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5373300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5414400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5342600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5366500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5039500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4764500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6989700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6855700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6560200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6581300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6954700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6691700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6823200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6875200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7196700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6675700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2941600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2839100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2906200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2705000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2687900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2809100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2771800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2678500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2679100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2633400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2823200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2756600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2913200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3235400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3194500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15039700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13968200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12464800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12336800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12316200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12493000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12472300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12502800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12994600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12402900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>10977500</v>
+        <v>8808100</v>
       </c>
       <c r="E48" s="3">
+        <v>8136500</v>
+      </c>
+      <c r="F48" s="3">
         <v>8547100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9225600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8947900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9391300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10037800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9401300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9813700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9833400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10010700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9104400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9648000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9698000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9670700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9855200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9932800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9546300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10032800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9386500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10160800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10069700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10993400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10310700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9942300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>2947100</v>
       </c>
       <c r="E49" s="3">
+        <v>2815400</v>
+      </c>
+      <c r="F49" s="3">
         <v>2888700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3367400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3337100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3560700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3806500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3665700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3867500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4016700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4049900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3968600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4254900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4434400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4456700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5635200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5629100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5622000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5845300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6083200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6545900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6426000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6643300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7011600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7117600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5081,118 +5198,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1288700</v>
+        <v>1366500</v>
       </c>
       <c r="E52" s="3">
+        <v>1329500</v>
+      </c>
+      <c r="F52" s="3">
         <v>488600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1485400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1376800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1465900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>670500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>716100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1526000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1530700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1182900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1114600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1110200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1135100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1097000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1238200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1157300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1150100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1134000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1186500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1333900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1439300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1407300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1632000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1341300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>707400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>521500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>530700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>521800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>693000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>21652700</v>
+      </c>
+      <c r="E54" s="3">
         <v>20317200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20656800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22439900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21372800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22543100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23226500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22195800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23009700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23422300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23481200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22286700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23292800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23542500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23183500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38758100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37543200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35343500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35930200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35927000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37225300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37230600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>38422000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39145600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37479700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5491,668 +5621,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>1808200</v>
+        <v>99000</v>
       </c>
       <c r="E57" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F57" s="3">
         <v>85600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>126000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>107900</v>
       </c>
       <c r="I57" s="3">
         <v>107900</v>
       </c>
       <c r="J57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="K57" s="3">
         <v>94800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>77200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>106600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>66900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>108600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>86000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>116300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>142900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>253700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>228200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>249000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>279700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>285700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>300500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>327300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>372600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>405200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>332700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>283700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>320300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>217500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>221100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>204600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>309500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>226300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>219400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>237100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>362200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>203700</v>
+        <v>1769800</v>
       </c>
       <c r="E58" s="3">
+        <v>2152400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1970900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2527000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2131100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1996200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1538200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1232100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1747900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2127500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1872800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2070200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1920500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1409000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1344700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1420900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1244900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1236100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1056900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1029100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>963600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1234000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1198200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1223800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>894000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>856100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>944800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>802000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3916500</v>
+        <v>2440400</v>
       </c>
       <c r="E59" s="3">
+        <v>2844700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3156900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2406500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1952900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2398900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2637100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2406000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2169000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2298100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4095200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3244300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3751200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3814800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3732700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4610800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4393200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4508600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4796900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4594700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4758600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4813200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5103100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4927800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4464800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>5382700</v>
+      </c>
+      <c r="E60" s="3">
         <v>5928400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6244200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6188000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5135100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5393400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4848000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5056000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5524300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6034900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5423100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5757700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5340200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5220300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6285400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5866300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5993700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6133500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5909400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6022700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6374500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6673900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6556800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6107900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>4482600</v>
+        <v>6403500</v>
       </c>
       <c r="E61" s="3">
+        <v>5339800</v>
+      </c>
+      <c r="F61" s="3">
         <v>5316200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5490100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5711200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6422800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6678600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6522300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6844600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6729300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6440900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5995600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6304100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6669800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6431400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8165900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8169800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7876200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8059700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7920900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8322200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8551200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8623500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8522600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7920200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1165600</v>
+        <v>331200</v>
       </c>
       <c r="E62" s="3">
+        <v>299400</v>
+      </c>
+      <c r="F62" s="3">
         <v>470600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>571200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>759700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>779300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1038900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>997600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1072500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1076600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1889000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1891200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1999600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2085000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2280300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3919000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3702000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3292500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3439900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3368000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3426800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3363300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3730200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3901800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3713300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6481,118 +6636,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>12208300</v>
+        <v>12807100</v>
       </c>
       <c r="E66" s="3">
+        <v>12208200</v>
+      </c>
+      <c r="F66" s="3">
         <v>12650300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12875900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12238800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13277000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13796600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13005600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13599700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13976100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14992500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13887800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14660500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14683200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14498900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19056700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18415600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17659600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18122300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17605800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18193000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18168300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18914300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18899300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17654900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>15686300</v>
+        <v>17034600</v>
       </c>
       <c r="E72" s="3">
+        <v>15677100</v>
+      </c>
+      <c r="F72" s="3">
         <v>15553300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17451400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16567800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16911400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17582300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16958200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17244300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17294500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16847800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16393600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17006300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17168800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16828000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16730300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16259600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16928100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17236400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17398700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18050600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18362200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18894400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19871700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19470600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>8027000</v>
+        <v>8757300</v>
       </c>
       <c r="E76" s="3">
+        <v>8025800</v>
+      </c>
+      <c r="F76" s="3">
         <v>7919200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8940700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8548300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8674600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8782700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8579600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8796100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8837600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8488700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8398900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8632300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8859300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8684500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19701400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19127600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17683900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17807900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18321200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19032300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19062300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19507700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20246300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19824800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>247400</v>
+        <v>66200</v>
       </c>
       <c r="E81" s="3">
+        <v>247500</v>
+      </c>
+      <c r="F81" s="3">
         <v>196900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>204700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>244900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>262700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>135700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>221300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>249900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>222800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>156700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>168600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>190100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>159800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>221700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>585400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>571600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>410400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1117200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>292100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>343200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>256100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>240900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>228500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>341700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>404200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>832400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>762900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>583800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>511800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>700300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>530200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>432400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7996,118 +8194,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>666400</v>
+      </c>
+      <c r="E83" s="3">
         <v>693100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>560400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>689300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>719900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>716600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>575500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>199500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>726100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>779000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>701100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>681500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>715000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>728600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>744200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>789300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>777100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>764800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3127500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>796700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>835300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>856200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>874600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>892700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>855000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>848400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>711200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>653900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>677500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>692100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>732200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>718700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>707600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>715200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>722200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="3">
+        <v>1037700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>850200</v>
+      </c>
+      <c r="F89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1086900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>921700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>832400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>936100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>992100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1042400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>786000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1027400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>768900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1095600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>996900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1011600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1053900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1039700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>659400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4366400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1263500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1549000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>816800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>975700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>746100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>907500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>881500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>382000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>829300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>828600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>969400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>776500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>837300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8806,118 +9026,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-368200</v>
+      </c>
+      <c r="F91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-375000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-375900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-429000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-707800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-488500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-472100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-595700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-415900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-558800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-742400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-526800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-878200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-969100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-796300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-571500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9136,118 +9363,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-314900</v>
+      </c>
+      <c r="F94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-425200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-259200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-478900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-588700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-674000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-682700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-335700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-566700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-595300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-616500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-583300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-874100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-764500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-387600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-907100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-515500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-404700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9286,8 +9519,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -9306,11 +9540,11 @@
       <c r="H96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3">
         <v>103400</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>91</v>
@@ -9318,39 +9552,39 @@
       <c r="L96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N96" s="3">
         <v>-135700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-132100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>-133400</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-556600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-56300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -9358,11 +9592,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -9370,11 +9604,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -9382,11 +9616,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -9394,10 +9628,13 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9726,334 +9969,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-1082400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-357300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-771000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-161500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-118700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-612300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-464800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-330200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-164700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-182000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-309700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-364600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-892500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-220900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-43900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-377800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-56600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-725800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>83100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>324500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>120000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>19100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>696800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>30200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>19200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E101" s="3">
         <v>4500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>7900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-11300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>5600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>41300</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>185700</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>299100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-105600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>196400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>224200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-292500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-104700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-142900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>518100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>196300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-464100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-35800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>231000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-102400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>74100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>297900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>307100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-128600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-144100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-532800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>500800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>783600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>359500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>184400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>63700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>581400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2998700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2831800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3205900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3024200</v>
       </c>
-      <c r="G8" s="3">
-        <v>3077700</v>
-      </c>
       <c r="H8" s="3">
+        <v>3054000</v>
+      </c>
+      <c r="I8" s="3">
         <v>3450600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3209300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3329500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3513200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3270500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3269600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3353300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3295800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3170700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3260300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3293500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3221500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3161300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3093900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3043700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12065800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3643200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3728700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3738500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3746400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4059500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3904600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3492600</v>
+      </c>
+      <c r="E9" s="3">
         <v>330000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>275500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>291000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1054000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>355700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>291500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>323200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>871300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>303400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>291300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>317000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>120500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>131400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>140800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>145800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>141200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>138100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>137400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>143500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>578000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>155100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>167900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>163800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>162600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>163700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>165200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>172300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>136400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>171900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>183800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>180600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>197200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>187500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>199000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>153400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-493900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2501800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2930400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2733300</v>
       </c>
-      <c r="G10" s="3">
-        <v>2023700</v>
-      </c>
       <c r="H10" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="I10" s="3">
         <v>3094900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2917800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3006200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2641900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2967100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2978300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3036200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3175400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3039300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3119500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3147600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3080300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3023100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2956500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11487800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3488100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3560800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3574700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3583800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3895800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3739400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,124 +1219,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E12" s="3">
         <v>69900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>59100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>61100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>255900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>78000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>70700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>66200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>90600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>66700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>56400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>67100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>61800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>67400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>60100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>75800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>60300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>62000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>61800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>264900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>80700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>85000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>92700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>86500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>83300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>84700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>90800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>88900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>76200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>82500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>75100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>90300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>90800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>83500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>85200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>82100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1439,240 +1455,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>50700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>72900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-47900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T14" s="3">
         <v>2400</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>150500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>10300</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>54900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>214000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>52300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>3700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>2000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>5700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2401900</v>
+      </c>
+      <c r="E15" s="3">
         <v>618400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>639300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>588900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>536700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>675500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>641400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>667600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>698800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>664700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>693700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>690400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>676400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>657900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>689600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>701400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>691800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>696100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>684800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>672700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2748500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>775500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>807500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>827200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>912300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>856100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>818700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>810900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>676100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>621700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>644900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>660200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>696900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>684300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>674200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>685500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>695000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2916200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2796900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2957700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2639600</v>
       </c>
-      <c r="G17" s="3">
-        <v>2944600</v>
-      </c>
       <c r="H17" s="3">
+        <v>2881900</v>
+      </c>
+      <c r="I17" s="3">
         <v>3045100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2819900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2959600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3283400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2902100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2918400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2975200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3117500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2831100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2911000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2960500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3055700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2866500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2797100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2766800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11279900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3367600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3449200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3485400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3664800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3790900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3622600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E18" s="3">
         <v>34800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>248100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>384700</v>
       </c>
-      <c r="G18" s="3">
-        <v>133000</v>
-      </c>
       <c r="H18" s="3">
+        <v>172100</v>
+      </c>
+      <c r="I18" s="3">
         <v>405600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>389400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>369900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>229800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>368300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>351200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>378100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>178400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>339600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>349300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>332900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>165800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>294800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>296800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>276900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>785900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>275700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>279500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>253100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>81700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>268600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>282000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>293500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>246000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>289300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>272600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>220900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>345000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>368800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>367500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>266100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1984,588 +2016,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-121600</v>
+      </c>
+      <c r="E20" s="3">
         <v>106900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>26000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-430800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-391800</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-24200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>27800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>188000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>133700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>109700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>265700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>320200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>140700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>130200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>116400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>225300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>607100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>866100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>748000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>552300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>662700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>601900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>355900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>351300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>307600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2606000</v>
+      </c>
+      <c r="E21" s="3">
         <v>546400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>861500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>970800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1100500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1080800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1039400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1032300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>929900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1022100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1040400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1048100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>886300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1001200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1078700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1037300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1019100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1111900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1261900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1175500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4023100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1338100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1435000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1250100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>956400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1291600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1253400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>265500</v>
+      </c>
+      <c r="E22" s="3">
         <v>69300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>70200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>272900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>74200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>71900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>78200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>79700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>72500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>72800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>71400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>55200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>57700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>56900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>53600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>53300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>216700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>143600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>155100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>84400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>89700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>87900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>87600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>93100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>75000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>57500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>60400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>63100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>68300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>63400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>66100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>67000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>66000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-116600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>177600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>344900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>323600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>277700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>347000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>327900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>167600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>297200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>341500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>322800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>108000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>264500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>306100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>251800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>221200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>269300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>433200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>360000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>678900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>397800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>444700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>309400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>311000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>310800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>425700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>507400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>977000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>761900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>815400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>883600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>658600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>651800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>507700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>116100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>99300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>92900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>58600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>68200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>77500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>90800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-59800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>85200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>109900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>82100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>62700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>71700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>102700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>96700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>165900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>96100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>94500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>52400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>31400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>66700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>82900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>85700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>108800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>204200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>208900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>179400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>234000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>185800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>112600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>126700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>80500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-118700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>61500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>245500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>267200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>213300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>254100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>269300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>144500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>229000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>264000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>232000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>167800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>179300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>196200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>169700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>158600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>197600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>330500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>263300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>513000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>301700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>350200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>257000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-39400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>244200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>228000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>340000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>398600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>850400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>768000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>582400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>581400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>697800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>546000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>525100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>427200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-116100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>244100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>183500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>201000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>241300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>259000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>131900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>217600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>247100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>220000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>156700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>168600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>190100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>159800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>141700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>189900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>313600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>253300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>475400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>292100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>343200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>256100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>240900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>228500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>341700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>404200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>832400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>762900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>583800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>511800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>700300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>542500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>530200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>432400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3066,8 +3126,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>91</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>91</v>
@@ -3078,29 +3138,29 @@
       <c r="R29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T29" s="3">
         <v>80000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>395400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>257900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>157000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>641800</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -3144,8 +3204,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3376,240 +3442,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-106900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-26000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
-        <v>430800</v>
-      </c>
       <c r="H32" s="3">
+        <v>391800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>24200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-27800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-188000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-133700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-109700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-265700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-320200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-140700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-130200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-116400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-112600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>66200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>247500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>196900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>204700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>244900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>262700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>135700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>221300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>249900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>222800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>156700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>168600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>190100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>159800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>221700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>585400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>571600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>410400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1117200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>292100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>343200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>256100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>240900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>228500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>341700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>404200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>832400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>762900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>583800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>511800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>700300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>542500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>530200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>432400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-112600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>66200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>247500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>196900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>204700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>244900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>262700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>135700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>221300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>249900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>222800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>156700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>168600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>190100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>159800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>221700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>585400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>571600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>410400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1117200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>292100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>343200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>256100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>240900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>228500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>341700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>404200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>832400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>762900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>583800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>511800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>700300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>542500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>530200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>432400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4045,1052 +4130,1080 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1032200</v>
+      </c>
+      <c r="E41" s="3">
         <v>985700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1738700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1559900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1369900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1497100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1141900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1279100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1122000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>864900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1182900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1300700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1411700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>869800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>876200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>688900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>654500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1118700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1154500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>911200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1027200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1450500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1212500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>938900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1080200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1147800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1277400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E42" s="3">
         <v>214300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>148800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>172900</v>
       </c>
-      <c r="G42" s="3">
-        <v>246300</v>
-      </c>
       <c r="H42" s="3">
+        <v>165400</v>
+      </c>
+      <c r="I42" s="3">
         <v>206100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>159600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>263900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>166100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>320100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>269700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>170500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>118300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>472700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>523300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>378500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>325600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1264900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1186400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1078700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1109500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>840400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>795000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>903200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>766900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>866400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>728100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>733100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>975400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>318100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>452600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>540900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>590800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>626300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>647200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>612800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>437300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1703700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1876800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1883600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1734200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1701900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1974800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1836300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1897100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1920900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2006600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1790200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1884400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1960600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2052200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2083500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2117900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1957700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2772400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2584400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2644400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2528400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2663000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2649400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2902000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2886300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3122000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2860700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E44" s="3">
         <v>160200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>142600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>139800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>142000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>169300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>154700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>156500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>138700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>139200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>126600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>153500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>124800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>143500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>139300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>172000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>153500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>148700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>158800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>163900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>128600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>166300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>165500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>174800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>138400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>178500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>197000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>239900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>242000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>208700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>217800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>213800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>239700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>219000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>231900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>223700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>233900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1690000</v>
+      </c>
+      <c r="E45" s="3">
         <v>176500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>180700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>216200</v>
       </c>
-      <c r="G45" s="3">
-        <v>1557800</v>
-      </c>
       <c r="H45" s="3">
+        <v>1638700</v>
+      </c>
+      <c r="I45" s="3">
         <v>255400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>250600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>208800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1675700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1521300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>216000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>336400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1799000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1804400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1744200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1682200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1673200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1685000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1771500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1762000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1787600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1834500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1869300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1904400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2003300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1881800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1612400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>305100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>341700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>228600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>212400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>289400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4660200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4932100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5562500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5172400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5061200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5608100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4978700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5284500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5078500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4913600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5087400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5373300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5414400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5342600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5366500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5039500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4764500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6989700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6855700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6560200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6581300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6954700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6691700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6823200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6875200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7196700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6675700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>3759600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2937800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2941600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2839100</v>
       </c>
-      <c r="G47" s="3">
-        <v>2906200</v>
-      </c>
       <c r="H47" s="3">
+        <v>2856500</v>
+      </c>
+      <c r="I47" s="3">
         <v>2705000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2687900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2809100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2771800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2678500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2679100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2633400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2823200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2756600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2913200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3235400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3194500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15039700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13968200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12464800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12336800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12316200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12493000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12472300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12502800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12994600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12402900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8249100</v>
+      </c>
+      <c r="E48" s="3">
         <v>8484400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8808100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8136500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8547100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9225600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8947900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9391300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10037800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9401300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9813700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9833400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10010700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9104400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9648000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9698000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9670700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9855200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9932800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9546300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10032800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9386500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10160800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10069700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10993400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10310700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9942300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2620700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2734100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2947100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2815400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2888700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3367400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3337100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3560700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3806500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3665700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3867500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4016700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4049900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3968600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4254900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4434400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4456700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5635200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5629100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5622000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5845300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6083200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6545900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6426000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6643300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7011600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7117600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5321,124 +5437,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>657900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1448600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1366500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1329500</v>
       </c>
-      <c r="G52" s="3">
-        <v>488600</v>
-      </c>
       <c r="H52" s="3">
+        <v>538300</v>
+      </c>
+      <c r="I52" s="3">
         <v>1485400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1376800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1465900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>670500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>716100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1526000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1530700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1182900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1114600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1110200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1135100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1097000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1238200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1157300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1150100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1134000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1186500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1333900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1439300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1407300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1632000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1341300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>707400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>521500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>530700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>521800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>693000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5553,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>20857200</v>
+      </c>
+      <c r="E54" s="3">
         <v>20569000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21652700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20317200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20656800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22439900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21372800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22543100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23226500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22195800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23009700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23422300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23481200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22286700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23292800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23542500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23183500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38758100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37543200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35343500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35930200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35927000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>37225300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37230600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>38422000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>39145600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>37479700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5753,704 +5882,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E57" s="3">
         <v>137000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>99000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>85600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>126000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>67400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>107900</v>
       </c>
       <c r="K57" s="3">
         <v>107900</v>
       </c>
       <c r="L57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="M57" s="3">
         <v>94800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>77200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>106600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>108600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>116300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>142900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>253700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>228200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>249000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>279700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>285700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>327300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>372600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>405200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>332700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>283700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>320300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>217500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>221100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>204600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>309500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>226300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>219400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>237100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>362200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1150300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1445600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1769800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2152400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1970900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2527000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2131100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1996200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1538200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1232100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1747900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2127500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1872800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2070200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1920500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1409000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1344700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1420900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1244900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1236100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1056900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1029100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>963600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1234000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1198200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1223800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>894000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>856100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>944800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>802000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2363900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1852600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2440400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2844700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3156900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2406500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1952900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2398900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2637100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2406000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2169000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2298100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4095200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3244300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3751200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3814800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3732700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4610800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4393200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4508600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4796900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4594700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4758600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4813200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5103100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4927800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4464800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>4523500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4621500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5382700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5928400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6244200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6188000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5135100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5400800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5393400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4848000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5056000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5524300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6034900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5423100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5757700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5340200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5220300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6285400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5866300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5993700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6133500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5909400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6022700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6374500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6673900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6556800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6107900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>6035900</v>
+      </c>
+      <c r="E61" s="3">
         <v>6526100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6403500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5339800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5316200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5490100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5711200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6422800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6678600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6522300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6844600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6729300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6440900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5995600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6304100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6669800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6431400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8165900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8169800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7876200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8059700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7920900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8322200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8551200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8623500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8522600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7920200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>244100</v>
+      </c>
+      <c r="E62" s="3">
         <v>354100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>331200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>299400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>470600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>571200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>759700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>779300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1038900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>997600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1072500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1076600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1889000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1891200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1999600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2085000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2280300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3919000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3702000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3292500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3439900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3368000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3426800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3363300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3730200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3901800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3713300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6797,124 +6951,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>11882400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12162900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12807100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12208200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12650300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12875900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12238800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13277000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13796600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13005600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13599700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13976100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14992500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13887800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14660500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14683200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14498900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19056700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18415600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17659600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18122300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17605800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18193000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18168300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18914300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18899300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17654900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7419,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>15890500</v>
+      </c>
+      <c r="E72" s="3">
         <v>16241200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17034600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15677100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15553300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17451400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16567800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16911400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17582300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16958200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17244300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17294500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16847800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16393600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17006300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17168800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16828000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16730300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16259600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16928100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17236400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17398700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18050600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18362200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18894400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19871700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19470600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7883,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>8910900</v>
+      </c>
+      <c r="E76" s="3">
         <v>8330100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8757300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8025800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7919200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8940700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8548300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8674600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8782700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8579600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8796100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8837600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8488700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8398900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8632300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8859300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8684500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19701400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19127600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17683900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17807900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18321200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19032300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19062300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19507700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20246300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19824800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-112600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>66200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>247500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>196900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>204700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>244900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>262700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>135700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>221300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>249900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>222800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>156700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>168600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>190100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>159800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>221700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>585400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>571600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>410400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1117200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>292100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>343200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>256100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>240900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>228500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>341700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>404200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>832400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>762900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>583800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>511800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>700300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>542500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>530200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>432400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8394,124 +8591,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="3">
         <v>702000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>666400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>693100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>560400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>689300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>719900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>716600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>575500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>199500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>726100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>779000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>701100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>681500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>715000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>728600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>744200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>789300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>777100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>764800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3127500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>796700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>835300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>856200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>874600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>892700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>855000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>848400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>711200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>653900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>677500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>692100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>732200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>718700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>707600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>715200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>722200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9090,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>762800</v>
+      </c>
+      <c r="E89" s="3">
         <v>118400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1037700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>850200</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1086900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>921700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>832400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>936100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>992100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1042400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>786000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1027400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>768900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1095600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>996900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1011600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1053900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1039700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>659400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4366400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1263500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1549000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>816800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>975700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>746100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>907500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>881500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>382000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>829300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>828600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>969400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>776500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>837300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9248,124 +9467,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-512400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-449100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-217000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-368200</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-375000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-375900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-429000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-707800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-488500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-472100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-595700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-415900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-558800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-742400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-526800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-878200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-969100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-796300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-571500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9596,124 +9822,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-285700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-706800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>97400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-314900</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-425200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-259200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-478900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-588700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-674000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-682700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-335700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-566700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-595300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-616500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-583300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-874100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-764500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-387600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-907100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-515500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-404700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -9780,11 +10013,11 @@
       <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L96" s="3">
         <v>103400</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>91</v>
@@ -9792,39 +10025,39 @@
       <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P96" s="3">
         <v>-135700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-132100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-133400</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-556600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-56300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -9832,11 +10065,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-64000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -9844,11 +10077,11 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -9856,11 +10089,11 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
@@ -9868,10 +10101,13 @@
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10218,352 +10460,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-403700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-105700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1082400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-350100</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-357300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-771000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-161500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-118700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-612300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-464800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-330200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-164700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-309700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-364600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-892500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-220900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-377800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-56600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-725800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>83100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>324500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>120000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>19100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>696800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>30200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>19200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-11300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>5600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-689400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>41300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>185700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>299100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-105600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>196400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>224200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-292500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-104700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-142900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>518100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>196300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-464100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-35800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>231000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-102400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>74100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>297900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>307100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-144100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-532800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>500800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>783600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>359500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>184400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>63700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>581400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-216300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,529 +656,542 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2885500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2998700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2831800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3205900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3024200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3054000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3450600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3209300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3329500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3513200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3270500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3269600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3353300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3295800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3170700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3260300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3293500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3221500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3161300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3093900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3043700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12065800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3643200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3728700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3738500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3746400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4059500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3904600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>279400</v>
+      </c>
+      <c r="E9" s="3">
         <v>3492600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>330000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>275500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>291000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1054000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>355700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>291500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>323200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>871300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>303400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>291300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>317000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>131400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>140800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>145800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>141200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>138100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>137400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>143500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>578000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>155100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>167900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>163800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>162600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>163700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>165200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>172300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>136400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>171900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>183800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>180600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>190800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>197200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>187500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>199000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>153400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2606100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-493900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2501800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2930400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2733300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3094900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2917800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3006200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2641900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2967100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2978300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3036200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3175400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3039300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3119500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3147600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3080300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3023100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2956500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2900200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11487800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3488100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3560800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3574700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3583800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3895800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3739400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1220,127 +1233,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E12" s="3">
         <v>235200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>69900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>59100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>61100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>255900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>78000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>70700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>66200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>90600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>66700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>56400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>67100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>61800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>67400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>60100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>75800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>60300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>62000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>61800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>264900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>80700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>85000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>92700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>86500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>83300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>84700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>90800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>88900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>76200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>82500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>90300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>90800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>83500</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>85200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>82100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1458,246 +1475,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-66700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>50700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>72900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-14500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-47900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-8400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-3700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>150500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>10300</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>54900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>214000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>52300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>5700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>556100</v>
+      </c>
+      <c r="E15" s="3">
         <v>2401900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>618400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>639300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>588900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>536700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>675500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>641400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>667600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>698800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>664700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>693700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>690400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>676400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>657900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>689600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>701400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>691800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>696100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>684800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>672700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2748500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>775500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>807500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>827200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>912300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>856100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>818700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>810900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>676100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>621700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>644900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>660200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>696900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>684300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>674200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>685500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>695000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,246 +1762,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2533100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2916200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2796900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2957700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2639600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2881900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3045100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2819900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2959600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3283400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2902100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2918400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2975200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3117500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2831100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2911000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2960500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3055700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2866500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2797100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2766800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11279900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3367600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3449200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3485400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3664800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3790900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3622600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>352400</v>
+      </c>
+      <c r="E18" s="3">
         <v>82500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>248100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>384700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>172100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>405600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>389400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>369900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>229800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>368300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>351200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>378100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>178400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>339600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>349300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>332900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>165800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>294800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>296800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>276900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>785900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>275700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>279500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>253100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>81700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>268600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>282000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>293500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>246000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>289300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>272600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>220900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>345000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>368800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>367500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>266100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2017,603 +2050,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-121600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>106900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-391800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-24200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>109100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>27800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>188000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>133700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>109700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>265700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>320200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>140700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>130200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>116400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>225300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>607100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>866100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>748000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>552300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>662700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>601900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>355900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>351300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>307600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>899100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2606000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>546400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>861500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>970800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1100500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1080800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1039400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1032300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>929900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1022100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1040400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1048100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>886300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1001200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1078700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1037300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1019100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1111900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1261900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1175500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4023100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1338100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1250100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>956400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1291600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1253400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E22" s="3">
         <v>265500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>69300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>70200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>66300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>272900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>74200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>71900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>78200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>79700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>72500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>72800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>71400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>77200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>57700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>56900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>53600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>53300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>50600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>216700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>143600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>155100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>84400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>89700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>87900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>87600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>93100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>75000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>57500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>60400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>63100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>68300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>63400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>66100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>67000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>66000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>305900</v>
+      </c>
+      <c r="E23" s="3">
         <v>95500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-116600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>177600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>344900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>323600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>277700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>347000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>327900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>167600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>297200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>341500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>322800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>108000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>264500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>306100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>251800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>221200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>269300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>433200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>360000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>678900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>397800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>444700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>309400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>311000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>310800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>425700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>507400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>977000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>761900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>815400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>883600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>658600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>651800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>507700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E24" s="3">
         <v>28300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>116100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>99300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>92900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>77500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>90800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-59800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>85200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>109900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>82100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>62700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>71700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>102700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>96700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>165900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>96100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>94500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>52400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>31400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>82900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>85700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>108800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>204200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>208900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>179400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>234000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>185800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>112600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>126700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>80500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2731,246 +2780,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>207900</v>
+      </c>
+      <c r="E26" s="3">
         <v>67200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-118700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>61500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>245500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>267200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>213300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>254100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>269300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>144500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>229000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>264000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>232000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>167800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>179300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>196200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>169700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>158600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>197600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>330500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>263300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>513000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>301700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>350200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>257000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-39400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>244200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>228000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>340000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>398600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>850400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>768000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>582400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>581400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>697800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>546000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>525100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>427200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E27" s="3">
         <v>64200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-116100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>62600</v>
       </c>
-      <c r="G27" s="3">
-        <v>244100</v>
-      </c>
       <c r="H27" s="3">
+        <v>247500</v>
+      </c>
+      <c r="I27" s="3">
         <v>183500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>201000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>241300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>259000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>131900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>217600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>247100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>220000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>156700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>168600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>190100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>159800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>141700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>189900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>313600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>253300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>475400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>292100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>343200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>256100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>240900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>228500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>341700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>404200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>832400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>762900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>583800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>511800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>700300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>542500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>530200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>432400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3088,8 +3146,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3129,8 +3190,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>91</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>91</v>
@@ -3141,29 +3202,29 @@
       <c r="S29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U29" s="3">
         <v>80000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>395400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>257900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>157000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>641800</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3207,8 +3268,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3326,8 +3390,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3445,246 +3512,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E32" s="3">
         <v>121600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-106900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>391800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>24200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-109100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-27800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-188000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-133700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-109700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-265700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-320200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-140700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-130200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-116400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E33" s="3">
         <v>77900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-112600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>66200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>247500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>196900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>204700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>244900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>262700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>135700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>221300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>249900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>222800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>156700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>168600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>190100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>159800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>221700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>585400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>571600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>410400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1117200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>292100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>343200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>256100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>240900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>228500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>341700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>404200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>832400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>762900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>583800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>511800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>700300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>542500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>530200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>432400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3802,251 +3878,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E35" s="3">
         <v>77900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-112600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>66200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>247500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>196900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>204700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>244900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>262700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>135700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>221300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>249900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>222800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>156700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>168600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>190100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>159800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>221700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>585400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>571600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>410400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1117200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>292100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>343200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>256100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>240900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>228500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>341700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>404200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>832400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>762900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>583800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>511800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>700300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>542500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>530200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>432400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4088,8 +4173,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4131,1079 +4217,1107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>968800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1032200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>985700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1738700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1559900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1369900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1497100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1141900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1279100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>864900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1182900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1300700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1411700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>869800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>876200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>688900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>654500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1118700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1154500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>911200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1027200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1450500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1212500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>938900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1080200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1147800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1277400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E42" s="3">
         <v>66800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>214300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>148800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>172900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>165400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>206100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>159600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>263900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>166100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>320100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>269700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>170500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>118300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>472700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>523300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>378500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>325600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1264900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1186400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1078700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1109500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>840400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>795000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>903200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>766900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>866400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>728100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>733100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>975400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>318100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>452600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>540900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>590800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>626300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>647200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>612800</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>437300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1688600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1703700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1876800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1883600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1734200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1701900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1974800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1836300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1897100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1920900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2006600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1790200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1884400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1960600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2052200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2083500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2117900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1957700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2772400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2584400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2644400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2528400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2663000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2649400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2902000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2886300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3122000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2860700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E44" s="3">
         <v>116100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>160200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>142600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>139800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>142000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>169300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>154700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>156500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>138700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>139200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>126600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>153500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>124800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>143500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>139300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>172000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>153500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>148700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>158800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>163900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>128600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>166300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>165500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>174800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>138400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>178500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>197000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>239900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>242000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>208700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>217800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>213800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>239700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>219000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>231900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>223700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>233900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1690000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>176500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>180700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>216200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1638700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>255400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>250600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>208800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1675700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1521300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>216000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>336400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1799000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1804400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1744200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1682200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1673200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1685000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1771500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1762000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1787600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1834500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1869300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1904400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2003300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1881800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1612400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>305100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>341700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>228600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>212400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>289400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4675600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4660200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4932100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5562500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5172400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5061200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5608100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4978700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5284500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5078500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4913600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5087400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5373300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5414400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5342600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5366500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5039500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4764500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6989700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6855700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6560200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6581300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6954700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6691700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6823200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6875200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7196700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6675700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>3652100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3759600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2937800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2941600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2839100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2856500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2705000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2687900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2809100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2771800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2678500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2679100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2633400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2823200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2756600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2913200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3235400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3194500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>15039700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13968200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12464800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12336800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12316200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12493000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12472300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12502800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12994600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12402900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>7455400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8249100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8484400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8808100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8136500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8547100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9225600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8947900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9391300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10037800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9401300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9813700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9833400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10010700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9104400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9648000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9698000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9670700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9855200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9932800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9546300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10032800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9386500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10160800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10069700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10993400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10310700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9942300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2379900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2620700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2734100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2947100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2815400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2888700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3367400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3337100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3560700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3806500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3665700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3867500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4016700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4049900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3968600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4254900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4434400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4456700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5635200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5629100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5622000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5845300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6083200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6545900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6426000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6643300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7011600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7117600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5321,8 +5435,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,127 +5557,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1532900</v>
+      </c>
+      <c r="E52" s="3">
         <v>657900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1448600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1366500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1329500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>538300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1485400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1376800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1465900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>670500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>716100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1526000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1530700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1182900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1114600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1110200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1135100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1097000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1238200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1157300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1150100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1134000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1186500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1333900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1439300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1407300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1632000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1341300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>707400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>521500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>530700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>521800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>693000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5678,127 +5801,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>19722700</v>
+      </c>
+      <c r="E54" s="3">
         <v>20857200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20569000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21652700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20317200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20656800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22439900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21372800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22543100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23226500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22195800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23009700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23422300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23481200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22286700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23292800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23542500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23183500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38758100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37543200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35343500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35930200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35927000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37225300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37230600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>38422000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39145600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37479700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5840,8 +5969,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5883,722 +6013,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E57" s="3">
         <v>76800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>137000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>99000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>85600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>126000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>107900</v>
       </c>
       <c r="L57" s="3">
         <v>107900</v>
       </c>
       <c r="M57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="N57" s="3">
         <v>94800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>77200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>106600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>108600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>86000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>116300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>142900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>253700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>228200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>249000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>279700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>285700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>327300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>372600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>405200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>332700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>283700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>320300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>217500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>221100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>204600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>309500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>226300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>219400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>237100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>362200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1150300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1445600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1769800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2152400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1970900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2527000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2131100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1996200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1538200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1232100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1747900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2127500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1872800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2070200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1920500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1409000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1344700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1420900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1244900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1236100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1056900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1029100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>963600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1198200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1223800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>894000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>856100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>944800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>802000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1947300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2363900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1852600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2440400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2844700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3156900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2406500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1952900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2398900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2637100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2406000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2169000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2298100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4095200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3244300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3751200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3814800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3732700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4610800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4393200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4508600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4796900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4594700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4758600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4813200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5103100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4927800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4464800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3999900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4523500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4621500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5382700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5928400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6244200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6188000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5135100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5400800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5393400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4848000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5056000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5524300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6034900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5423100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5757700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5340200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5220300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6285400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5866300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5993700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6133500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5909400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6022700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6374500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6673900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6556800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6107900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5650400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6035900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6526100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6403500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5339800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5316200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5490100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5711200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6422800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6678600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6522300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6844600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6729300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6440900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5995600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6304100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6669800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6431400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8165900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8169800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7876200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8059700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7920900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8322200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8551200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8623500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8522600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7920200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>353900</v>
+      </c>
+      <c r="E62" s="3">
         <v>244100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>354100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>331200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>299400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>470600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>571200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>759700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>779300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1038900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>997600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1072500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1076600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1889000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1891200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1999600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2085000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2280300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3919000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3702000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3292500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3439900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3368000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3426800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3363300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3730200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3901800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3713300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6716,8 +6865,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6835,8 +6987,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6954,127 +7109,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>10954100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11882400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12162900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12807100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12208200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12650300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12875900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12238800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13277000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13796600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13005600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13599700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13976100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14992500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13887800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14660500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14683200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14498900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19056700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18415600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17659600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18122300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17605800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18193000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18168300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18914300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18899300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17654900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7116,8 +7277,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7235,8 +7397,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7354,8 +7519,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7473,8 +7641,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7592,127 +7763,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>16381000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15890500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16241200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17034600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15677100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15553300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17451400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16567800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16911400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17582300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16958200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17244300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17294500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16847800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16393600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17006300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17168800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16828000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16730300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16259600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>16928100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17236400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17398700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18050600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18362200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18894400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19871700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19470600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7830,8 +8007,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7949,8 +8129,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8068,127 +8251,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>8727400</v>
+      </c>
+      <c r="E76" s="3">
         <v>8910900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8330100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8757300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8025800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7919200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8940700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8548300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8674600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8782700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8579600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8796100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8837600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8488700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8398900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8632300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8859300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8684500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19701400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19127600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17683900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17807900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18321200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19032300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19062300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19507700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20246300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19824800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8306,251 +8495,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E81" s="3">
         <v>77900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-112600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>66200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>247500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>196900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>204700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>244900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>262700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>135700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>221300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>249900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>222800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>156700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>168600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>190100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>159800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>221700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>585400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>571600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>410400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1117200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>292100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>343200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>256100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>240900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>228500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>341700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>404200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>832400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>762900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>583800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>511800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>700300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>542500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>530200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>432400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8592,127 +8790,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>609100</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>702000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>666400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>693100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>560400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>689300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>719900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>716600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>575500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>199500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>726100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>779000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>701100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>681500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>715000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>728600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>744200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>789300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>777100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>764800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3127500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>796700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>835300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>856200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>874600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>892700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>855000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>848400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>711200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>653900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>677500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>692100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>732200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>718700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>707600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>715200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>722200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8830,8 +9032,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8949,8 +9154,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9068,8 +9276,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9187,8 +9398,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9306,127 +9520,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>699100</v>
+      </c>
+      <c r="E89" s="3">
         <v>762800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>118400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1037700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>850200</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1086900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>921700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>832400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>936100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>992100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1042400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>786000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1027400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>768900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1095600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>996900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1011600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1053900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1039700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>659400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4366400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1263500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1549000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>816800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>975700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>746100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>907500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>881500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>382000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>829300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>828600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>969400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>776500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>837300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9468,127 +9688,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-237300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-512400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-449100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-217000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-368200</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="I91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-375000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-375900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-429000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-707800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-488500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-472100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-595700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-415900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-558800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-742400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-526800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-878200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-969100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-796300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-571500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9930,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9825,127 +10052,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-313400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-285700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-706800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>97400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-314900</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-425200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-259200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-478900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-588700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-674000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-682700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-335700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-566700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-595300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-616500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-583300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-874100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-764500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-387600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-907100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-515500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-404700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9987,8 +10220,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -10016,11 +10250,11 @@
       <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M96" s="3">
         <v>103400</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>91</v>
@@ -10028,39 +10262,39 @@
       <c r="O96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-135700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-132100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-133400</v>
       </c>
       <c r="V96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-556600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-56300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10068,11 +10302,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-64000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -10080,11 +10314,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -10092,11 +10326,11 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
@@ -10104,10 +10338,13 @@
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10225,8 +10462,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10344,8 +10584,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10463,361 +10706,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-400900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-403700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-105700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1082400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-350100</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-357300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-771000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-161500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-118700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-612300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-464800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-330200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-164700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-182000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-309700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-364600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-892500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-220900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-377800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-56600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-725800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>83100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>324500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>120000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>19100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>696800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>30200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>19200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>5600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E102" s="3">
         <v>76100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-689400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>41300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>185700</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>299100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-105600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>196400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>224200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-292500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-104700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-142900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>518100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>196300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-464100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-35800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>231000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-102400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>74100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>297900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>307100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-128600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-144100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-532800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>500800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>783600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>359500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>9300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>184400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>63700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>581400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-216300</v>
       </c>
     </row>
